--- a/docs/qa/blackbox-test-log.xlsx
+++ b/docs/qa/blackbox-test-log.xlsx
@@ -10,9 +10,10 @@
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="All issues" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Round 1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Round 2" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All issues'!$A$1:$N$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All issues'!$A$1:$N$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -43,7 +44,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +59,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F3D9C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4D8"/>
       </patternFill>
     </fill>
   </fills>
@@ -87,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -95,6 +101,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -107,6 +116,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -474,11 +486,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -499,6 +512,11 @@
           <t>Round 1</t>
         </is>
       </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Round 2</t>
+        </is>
+      </c>
     </row>
     <row r="4"/>
     <row r="5">
@@ -510,6 +528,9 @@
       <c r="B5" s="4" t="n">
         <v>6</v>
       </c>
+      <c r="C5" s="5" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -520,6 +541,9 @@
       <c r="B6" s="4" t="n">
         <v>5</v>
       </c>
+      <c r="C6" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -530,6 +554,9 @@
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
+      <c r="C7" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -540,6 +567,9 @@
       <c r="B8" s="4" t="n">
         <v>2</v>
       </c>
+      <c r="C8" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -550,6 +580,9 @@
       <c r="B9" s="4" t="n">
         <v>4</v>
       </c>
+      <c r="C9" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -560,6 +593,9 @@
       <c r="B10" s="4" t="n">
         <v>6</v>
       </c>
+      <c r="C10" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -570,6 +606,9 @@
       <c r="B11" s="4" t="n">
         <v>6</v>
       </c>
+      <c r="C11" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -580,6 +619,9 @@
       <c r="B12" s="4" t="n">
         <v>4</v>
       </c>
+      <c r="C12" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -590,6 +632,9 @@
       <c r="B13" s="4" t="n">
         <v>7</v>
       </c>
+      <c r="C13" s="5" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -600,6 +645,9 @@
       <c r="B14" s="4" t="n">
         <v>4</v>
       </c>
+      <c r="C14" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -610,9 +658,12 @@
       <c r="B15" s="4" t="n">
         <v>4</v>
       </c>
+      <c r="C15" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Lowest score</t>
         </is>
@@ -620,9 +671,12 @@
       <c r="B16" s="3" t="n">
         <v>2</v>
       </c>
+      <c r="C16" s="3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Issues reported</t>
         </is>
@@ -630,9 +684,12 @@
       <c r="B17" s="3" t="n">
         <v>17</v>
       </c>
+      <c r="C17" s="3" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Issues fixed</t>
         </is>
@@ -640,16 +697,31 @@
       <c r="B18" s="3" t="n">
         <v>14</v>
       </c>
+      <c r="C18" s="3" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>Round 1 (2026-10-23)</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Local: frontend :5174, API :3100 with AI_PROVIDER=nvidia but no NVIDIA_API_KEY yet; Claude ai-service not running. Seeded account with 6 books (one sample EPUB).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Round 2 (2026-10-23)</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Local: frontend :5174, API :3100; assistant model not configured (no NVIDIA_API_KEY), tester told so. Fresh seeded account with an original 5-chapter EPUB.</t>
         </is>
       </c>
     </row>
@@ -664,7 +736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -757,1061 +829,2789 @@
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="8" t="n">
+      <c r="A3" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>R1-01</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>Reading experience</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>blocker</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>No way to open the digital reader, even for a book with an EPUB</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>Library &gt; 'A Bunko Sample Book' &gt; 'Open Digital Reader'; clicked the EPUB edition row; tried status Reading, reload, and 'Start / Resume Reading Session'.</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>The EPUB opens in the reader.</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>Every path lands on the book details page; the EPUB edition row has no read button.</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>QA seed attached the EPUB with the upload id instead of the stored file id, so no copy existed; and the app gave a digital edition without its file no way forward.</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>Seed fixed (uses the id /files/:id/confirm returns) and now ships an original 5-chapter novella. A digital edition with no file shows 'Upload file'; the quick-action modal only offers actions that work.</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>backend/scripts/seed-qa-reader.ts, backend/scripts/qa-sample-book.ts, frontend/src/features/library/BookDetailPage.tsx, frontend/src/features/library/AddEditionDialog.tsx, frontend/src/features/library/BookQuickActionModal.tsx</t>
         </is>
       </c>
-      <c r="L3" s="8" t="inlineStr"/>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr"/>
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr"/>
+      <c r="N3" s="9" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n">
+      <c r="A4" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>R1-02</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>Library adding finding books</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Most covers are for completely different books</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>Open Library (also Shelves, modal, book page).</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>The real cover for each book.</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="H4" s="9" t="inlineStr">
         <is>
           <t>The Left Hand of Darkness and the sample book show 'Their Eyes Were Watching God'; Circe, Piranesi and Klara show unrelated books; a hand-added zine got a random cover. There's no way to change or remove a cover.</t>
         </is>
       </c>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t>Three code paths took the first search result with any cover regardless of title; the seed also used guessed cover ids. Wikidata series discovery filed books under their own title.</t>
         </is>
       </c>
-      <c r="J4" s="8" t="inlineStr">
+      <c r="J4" s="9" t="inlineStr">
         <is>
           <t>Covers only from a result with the same main title and a shared author surname (pickMatchingCover), looked up in the background; self-named series ignored and cleared. Changing/removing a cover by hand is not built yet (covers live on the shared catalogue entry).</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="K4" s="9" t="inlineStr">
         <is>
           <t>backend/src/modules/library/library.service.ts, backend/scripts/seed-qa-reader.ts</t>
         </is>
       </c>
-      <c r="L4" s="8" t="inlineStr"/>
-      <c r="M4" s="8" t="inlineStr">
+      <c r="L4" s="9" t="inlineStr"/>
+      <c r="M4" s="9" t="inlineStr">
         <is>
           <t>Partly fixed</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr"/>
+      <c r="N4" s="9" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>R1-03</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>Assistant chat</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>Many assistant messages fail with a generic error</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>'no i meant the zevin one...', 'I started Tomorrow, and Tomorrow, and Tomorrow' (the app's own example), 'ok i started the first one. and dnf'd circe tbh', 'and add it to my comfort reads shelf', 'rate it 5 stars actually'.</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>The change is made, or a clarifying question.</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="H5" s="9" t="inlineStr">
         <is>
           <t>'An unexpected error occurred' each time, no reason, no retry. Short single-book commands worked.</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr">
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>No NVIDIA key on the test server: NIM's 401 became a plain Error and surfaced as a 500. Separately, titles with commas, filler words ('ok', 'and', 'tbh', 'actually') and 'it' defeated the fast paths, so those messages needed the model.</t>
         </is>
       </c>
-      <c r="J5" s="8" t="inlineStr">
+      <c r="J5" s="9" t="inlineStr">
         <is>
           <t>Rejected key / rate limit are 'unavailable'; a missing key is detected at startup and answered with a plain message; any other failure is a friendly logged reply. Owned titles with commas are masked before clause splitting; filler words stripped.</t>
         </is>
       </c>
-      <c r="K5" s="8" t="inlineStr">
+      <c r="K5" s="9" t="inlineStr">
         <is>
           <t>backend/src/modules/assistant/clients/NvidiaNimClient.ts, backend/src/modules/assistant/aiController.ts, backend/src/modules/assistant/domains/books/conversation/quickCommands.ts</t>
         </is>
       </c>
-      <c r="L5" s="8" t="inlineStr"/>
-      <c r="M5" s="8" t="inlineStr">
+      <c r="L5" s="9" t="inlineStr"/>
+      <c r="M5" s="9" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr"/>
+      <c r="N5" s="9" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>R1-04</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Assistant chat</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>A typo in an owned title makes it search the catalogue for junk</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>'started tomorow and tomorrow last night, its so good already' (the book is in the library).</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>It matches the owned book.</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>"I couldn't find a book called \"tomorow\". The closest were \"Notes on the History of Fort George\"..."</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>Title matching needed exact words; the list splitter split 'tomorow and tomorrow' into two books.</t>
         </is>
       </c>
-      <c r="J6" s="8" t="inlineStr">
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>Typo-tolerant word matching on owned titles; lists split only into books the reader owns.</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="K6" s="9" t="inlineStr">
         <is>
           <t>backend/src/modules/assistant/domains/books/text/match.ts, backend/src/modules/assistant/domains/books/conversation/quickCommands.ts</t>
         </is>
       </c>
-      <c r="L6" s="8" t="inlineStr"/>
-      <c r="M6" s="8" t="inlineStr">
+      <c r="L6" s="9" t="inlineStr"/>
+      <c r="M6" s="9" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="9" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>R1-05</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>Assistant chat</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>Recommendations made up a sequel and ignored 'something like Piranesi'</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>'what should i read next? something like piranesi'</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>Books like Piranesi, and accurate facts.</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="H7" s="9" t="inlineStr">
         <is>
           <t>Listed the Want to Read list only, and said 'the series continues with Dune II by Frank Herbert' (no such book).</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>The 'series continues' line came from a Wikidata lookup that returned non-books ('Dune II'); 'like X' wasn't used.</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr">
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>Series continuation removed; 'something like X' ranks the list by X's authors and genres with reasons, and asks the model for books beyond the list.</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="K7" s="9" t="inlineStr">
         <is>
           <t>backend/src/modules/assistant/domains/books/actions/readTools.ts, backend/src/modules/assistant/domains/books/pipeline/preRoute.ts, backend/src/modules/assistant/domains/books/prompts/answerPrompt.ts</t>
         </is>
       </c>
-      <c r="L7" s="8" t="inlineStr"/>
-      <c r="M7" s="8" t="inlineStr">
+      <c r="L7" s="9" t="inlineStr"/>
+      <c r="M7" s="9" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr"/>
+      <c r="N7" s="9" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>R1-06</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Tracking journal statistics</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>Journal entries don't say which book</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>Piranesi &gt; physical edition &gt; session &gt; end with 'p 112' and a reflection &gt; Journal.</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>Entry shows the book, page and time, and links to it.</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="H8" s="9" t="inlineStr">
         <is>
           <t>'Oct 23, 2026 · 0 min · “the other is kinda sus now”': no title, no page, not clickable; no way to add an entry from the Journal.</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>Journal entries carried no book.</t>
         </is>
       </c>
-      <c r="J8" s="8" t="inlineStr">
+      <c r="J8" s="9" t="inlineStr">
         <is>
           <t>Each entry names and links its book with its cover and format; 'Log reading' on the Journal.</t>
         </is>
       </c>
-      <c r="K8" s="8" t="inlineStr">
+      <c r="K8" s="9" t="inlineStr">
         <is>
           <t>backend/src/modules/journal/journal.service.ts, frontend/src/features/journal/JournalPage.tsx</t>
         </is>
       </c>
-      <c r="L8" s="8" t="inlineStr"/>
-      <c r="M8" s="8" t="inlineStr">
+      <c r="L8" s="9" t="inlineStr"/>
+      <c r="M8" s="9" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N8" s="8" t="inlineStr"/>
+      <c r="N8" s="9" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>R1-07</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>Tracking journal statistics</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>Reading can only be logged live, and pages aren't counted</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>Started and immediately ended a session with 'p 112'.</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>Log a past session (time, date, page), and pages count.</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="H9" s="9" t="inlineStr">
         <is>
           <t>'Session saved — 0 min. Nice reading.' Stats: 'Pages read 0'. No manual duration/date, no progress on the book, no finish date.</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I9" s="9" t="inlineStr">
         <is>
           <t>Only live timed sessions existed; a physical session with only an end page can't count pages.</t>
         </is>
       </c>
-      <c r="J9" s="8" t="inlineStr">
+      <c r="J9" s="9" t="inlineStr">
         <is>
           <t>POST /reading-sessions/log and a 'Log reading' form (book, day, minutes, from/to page, reflection) on the Journal and book page; both pages make them count.</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="K9" s="9" t="inlineStr">
         <is>
           <t>backend/src/modules/reading-sessions/*, frontend/src/features/journal/LogSessionDialog.tsx</t>
         </is>
       </c>
-      <c r="L9" s="8" t="inlineStr"/>
-      <c r="M9" s="8" t="inlineStr">
+      <c r="L9" s="9" t="inlineStr"/>
+      <c r="M9" s="9" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="N9" s="9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>R1-08</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Book page and details</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>Modal buttons silently do nothing without a matching edition</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>Circe (no editions) &gt; 'Start / Resume Reading Session'; Piranesi (physical only) &gt; 'Open Digital Reader'.</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>Hidden, disabled, or explained.</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="H10" s="9" t="inlineStr">
         <is>
           <t>Both silently go to the book page.</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="I10" s="9" t="inlineStr">
         <is>
           <t>Modal buttons fell back to navigating to the book page.</t>
         </is>
       </c>
-      <c r="J10" s="8" t="inlineStr">
+      <c r="J10" s="9" t="inlineStr">
         <is>
           <t>Modal shows only working actions and explains/offers to add a copy otherwise.</t>
         </is>
       </c>
-      <c r="K10" s="8" t="inlineStr">
+      <c r="K10" s="9" t="inlineStr">
         <is>
           <t>frontend/src/features/library/BookQuickActionModal.tsx</t>
         </is>
       </c>
-      <c r="L10" s="8" t="inlineStr"/>
-      <c r="M10" s="8" t="inlineStr">
+      <c r="L10" s="9" t="inlineStr"/>
+      <c r="M10" s="9" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="9" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>R1-09</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>Tracking journal statistics</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>Statistics contradict themselves; language data messy</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>Statistics &gt; Daily.</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>Consistent numbers.</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="H11" s="9" t="inlineStr">
         <is>
           <t>Summary counts 1 session while the chart says 'No reading sessions in this period yet'; languages 'Unknown 6' and lowercase 'english 2'; 'Bunko' listed as an author.</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>The chart's empty state keyed on minutes, not sessions; language labels weren't normalised.</t>
         </is>
       </c>
-      <c r="J11" s="8" t="inlineStr">
+      <c r="J11" s="9" t="inlineStr">
         <is>
           <t>Chart distinguishes 'no sessions' from 'sessions under a minute'; languages shown as names. ('Bunko' as author was seed data; reading goals aren't in the SRS.)</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr">
+      <c r="K11" s="9" t="inlineStr">
         <is>
           <t>frontend/src/features/statistics/ActivityChart.tsx, backend/src/modules/statistics/statistics.service.ts</t>
         </is>
       </c>
-      <c r="L11" s="8" t="inlineStr"/>
-      <c r="M11" s="8" t="inlineStr">
+      <c r="L11" s="9" t="inlineStr"/>
+      <c r="M11" s="9" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N11" s="8" t="inlineStr"/>
+      <c r="N11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>R1-10</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Library adding finding books</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Catalogue search isn't typo-tolerant and is slow; no status on add</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>Add a book &gt; 'tomorow and tomorrow and tomorrow'.</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="9" t="inlineStr">
         <is>
           <t>The right book near the top.</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="H12" s="9" t="inlineStr">
         <is>
           <t>After 6-8s: unrelated results. Confusing language chips; manual form lacks page count/cover; always added as Want to Read.</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="9" t="inlineStr">
         <is>
           <t>Google Books answered first with poor relevance; the universe check could hijack results; no caching; original language defaulted to 'Japanese'.</t>
         </is>
       </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="J12" s="9" t="inlineStr">
         <is>
           <t>Open Library title search merged in; results ranked by title match; universe check only for named universes; searches cached an hour; choose Want to read / Reading now / Already read when adding; calm metadata line replaces off-palette chips. (Catalogue-side typo tolerance depends on the providers.)</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K12" s="9" t="inlineStr">
         <is>
           <t>backend/src/modules/metadata/metadata.service.ts, frontend/src/features/library/AddBookDialog.tsx</t>
         </is>
       </c>
-      <c r="L12" s="8" t="inlineStr"/>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="L12" s="9" t="inlineStr"/>
+      <c r="M12" s="9" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="N12" s="9" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>R1-11</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Library adding finding books</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>'Remove from library' gave no visible response</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>Book page &gt; 'Remove from library'.</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="G13" s="9" t="inlineStr">
         <is>
           <t>A confirmation, then the book is gone.</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="H13" s="9" t="inlineStr">
         <is>
           <t>Nothing visible; the book stayed.</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="I13" s="9" t="inlineStr">
         <is>
           <t>Used the browser's native confirm(), which the tester never saw.</t>
         </is>
       </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="J13" s="9" t="inlineStr">
         <is>
           <t>In-app confirmation dialog that says what's kept.</t>
         </is>
       </c>
-      <c r="K13" s="8" t="inlineStr">
+      <c r="K13" s="9" t="inlineStr">
         <is>
           <t>frontend/src/features/library/BookDetailPage.tsx</t>
         </is>
       </c>
-      <c r="L13" s="8" t="inlineStr"/>
-      <c r="M13" s="8" t="inlineStr">
+      <c r="L13" s="9" t="inlineStr"/>
+      <c r="M13" s="9" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="9" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>R1-12</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Shelves organizing</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>Odd shelf grouping, per-row scrollbars, inverted toggle</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>Shelves &gt; All Volumes; Covers/Spines toggle; mobile.</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>Books share shelves; the active view is clear.</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t>One book per tall row under its own title; every row has a scrollbar; the active toggle option is the dim one; the choice doesn't stick; arrows cover art on mobile.</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr">
+      <c r="I14" s="9" t="inlineStr">
         <is>
           <t>Rows per one-book series/genre; overflow-x-auto made rows scroll vertically; active toggle was the dark pill; arrows forced visible on mobile.</t>
         </is>
       </c>
-      <c r="J14" s="8" t="inlineStr">
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>Rows need two books; overflow-y hidden with a thin themed scrollbar; light active pill with aria-pressed, remembered; arrows on focus/hover only.</t>
         </is>
       </c>
-      <c r="K14" s="8" t="inlineStr">
+      <c r="K14" s="9" t="inlineStr">
         <is>
           <t>frontend/src/features/shelves/*</t>
         </is>
       </c>
-      <c r="L14" s="8" t="inlineStr"/>
-      <c r="M14" s="8" t="inlineStr">
+      <c r="L14" s="9" t="inlineStr"/>
+      <c r="M14" s="9" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr"/>
+      <c r="N14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="n">
+      <c r="A15" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>R1-13</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Speed reliability</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>Slow loads with little feedback</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>Library, Shelves, book pages; status dropdown.</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>Fast, with placeholders.</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t>Covers blank for 3-5s on every visit; a big modal spinner; status change ~3s while the old value still shows.</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="I15" s="9" t="inlineStr">
         <is>
           <t>Opening a book ran series discovery and a cover search synchronously (2-3s); covers had no placeholder; status change waited for the server.</t>
         </is>
       </c>
-      <c r="J15" s="8" t="inlineStr">
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>Both moved to the background (book fetch ~72 ms); lazy covers on a paper tint; skeleton in the modal; optimistic status updates.</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr">
+      <c r="K15" s="9" t="inlineStr">
         <is>
           <t>backend/src/modules/library/library.service.ts, frontend/src/features/library/BookCover.tsx, frontend/src/lib/api/works.ts</t>
         </is>
       </c>
-      <c r="L15" s="8" t="inlineStr"/>
-      <c r="M15" s="8" t="inlineStr">
+      <c r="L15" s="9" t="inlineStr"/>
+      <c r="M15" s="9" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N15" s="8" t="inlineStr"/>
+      <c r="N15" s="9" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>R1-14</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Notes highlights reviews</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>Reviews and notes are basic</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t>Rated, reviewed, added and edited a note.</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
         <is>
           <t>Half stars, dated notes, spoiler/private options.</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="H16" s="9" t="inlineStr">
         <is>
           <t>Whole stars only; notes undated with only a 'Book' tag; highlights impossible (R1-01).</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="I16" s="9" t="inlineStr">
         <is>
           <t>Notes showed no date; ratings are whole stars by SRS §14.</t>
         </is>
       </c>
-      <c r="J16" s="8" t="inlineStr">
+      <c r="J16" s="9" t="inlineStr">
         <is>
           <t>Notes show their date (and position); the review box says reviews and notes are private. Half stars not added: SRS §14 sets whole 5-star ratings.</t>
         </is>
       </c>
-      <c r="K16" s="8" t="inlineStr">
+      <c r="K16" s="9" t="inlineStr">
         <is>
           <t>frontend/src/features/notes/NotesPanel.tsx, frontend/src/features/reviews/ReviewPanel.tsx</t>
         </is>
       </c>
-      <c r="L16" s="8" t="inlineStr"/>
-      <c r="M16" s="8" t="inlineStr">
+      <c r="L16" s="9" t="inlineStr"/>
+      <c r="M16" s="9" t="inlineStr">
         <is>
           <t>Partly fixed</t>
         </is>
       </c>
-      <c r="N16" s="8" t="inlineStr"/>
+      <c r="N16" s="9" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>R1-15</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>Assistant chat</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>polish</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>Odd reply after declining a follow-up</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>'rate piranesi 5 stars' &gt; asked to mark Finished &gt; 'nah not yet'.</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>'Okay, I'll leave it as Reading.'</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="H17" s="9" t="inlineStr">
         <is>
           <t>'Okay, I kept Piranesi.' (sounds like it nearly removed it).</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
+      <c r="I17" s="9" t="inlineStr">
         <is>
           <t>The decline message was the generic 'Okay, I kept X.'</t>
         </is>
       </c>
-      <c r="J17" s="8" t="inlineStr">
+      <c r="J17" s="9" t="inlineStr">
         <is>
           <t>Follow-up offers can say what 'no' means (general core hook): 'Okay, Piranesi stays as Reading.'</t>
         </is>
       </c>
-      <c r="K17" s="8" t="inlineStr">
+      <c r="K17" s="9" t="inlineStr">
         <is>
           <t>backend/src/modules/assistant/domain/DomainPack.ts, backend/src/modules/assistant/AIRuntime.ts, backend/src/modules/assistant/domains/books/pipeline/replies.ts</t>
         </is>
       </c>
-      <c r="L17" s="8" t="inlineStr"/>
-      <c r="M17" s="8" t="inlineStr">
+      <c r="L17" s="9" t="inlineStr"/>
+      <c r="M17" s="9" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N17" s="8" t="inlineStr"/>
+      <c r="N17" s="9" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>R1-16</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>First impression onboarding</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>polish</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>No forgot-password, no import of an existing history</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t>Login and register pages; Settings.</t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="G18" s="9" t="inlineStr">
         <is>
           <t>Forgot password; Goodreads/StoryGraph import.</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="H18" s="9" t="inlineStr">
         <is>
           <t>Neither exists.</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="I18" s="9" t="inlineStr">
         <is>
           <t>Password reset needs email delivery (none configured); importing other platforms is SRS §37, which needs product approval.</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="J18" s="9" t="inlineStr">
         <is>
           <t>Not built. A first-run welcome now explains the three ways to start (add, read/log, assistant).</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr">
+      <c r="K18" s="9" t="inlineStr">
         <is>
           <t>frontend/src/features/library/LibraryPage.tsx</t>
         </is>
       </c>
-      <c r="L18" s="8" t="inlineStr"/>
-      <c r="M18" s="8" t="inlineStr">
+      <c r="L18" s="9" t="inlineStr"/>
+      <c r="M18" s="9" t="inlineStr">
         <is>
           <t>Won't fix (needs approval)</t>
         </is>
       </c>
-      <c r="N18" s="8" t="inlineStr"/>
+      <c r="N18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="n">
+      <c r="A19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>R1-17</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>Look and feel</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>polish</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>Sidebar scrolls away on long pages</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>Scrolled a long book page on desktop.</t>
         </is>
       </c>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>Navigation and Sign out stay in reach.</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="H19" s="9" t="inlineStr">
         <is>
           <t>The sidebar scrolls with the content.</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="I19" s="9" t="inlineStr">
         <is>
           <t>Sidebar wasn't sticky.</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="J19" s="9" t="inlineStr">
         <is>
           <t>Sticky full-height sidebar on desktop.</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr">
+      <c r="K19" s="9" t="inlineStr">
         <is>
           <t>frontend/src/components/layout/AppShell.tsx</t>
         </is>
       </c>
-      <c r="L19" s="8" t="inlineStr"/>
-      <c r="M19" s="8" t="inlineStr">
+      <c r="L19" s="9" t="inlineStr"/>
+      <c r="M19" s="9" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N19" s="8" t="inlineStr"/>
+      <c r="N19" s="9" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>R2-01</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Notes highlights reviews</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>Highlights are saved but never drawn on the page text</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>Paginated mode, selected a passage, chose green; reopened the book.</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>The passage shows green highlighting.</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>Listed in the Highlights panel, but the text stays plain.</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>Highlights were stored with their text and chapter but the reflowed pages were plain strings; nothing located the saved text on a page.</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>Each page now keeps the character offsets of its text, saved highlights are found in the chapter (forgiving line breaks) and drawn in their colour, stronger on light paper.</t>
+        </is>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/flow-layout.ts, frontend/src/features/reader/FlowReaderPage.tsx</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr"/>
+      <c r="M20" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N20" s="9" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>R2-02</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>Reflowed text has no paragraph breaks and repeats each chapter title</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>Opened the novella and turned pages.</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>Proper paragraphs; title once.</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>Each chapter is one block starting 'The Last Lantern The Last Lantern Aldmere had...' under a heading saying the same.</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>EPUB extraction stripped every tag and collapsed whitespace, so &lt;title&gt; + &lt;h1&gt; + paragraphs became one run ('The Last Lantern The Last Lantern Aldmere...').</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>Body only, one paragraph per block element, entities decoded, a heading that repeats the chapter title dropped; chapter graph v4 re-indexes existing books.</t>
+        </is>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>backend/src/modules/reader/epub-indexer.ts, backend/src/modules/reader/chapter-graph.ts</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr"/>
+      <c r="M21" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N21" s="9" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>R2-03</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Assistant chat</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>'dnf'd klara' added a different book</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>'dnf'd klara, the robot pov wasnt for me' with Klara and the Sun owned.</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>Mark Klara and the Sun DNF, or ask.</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>'I've added Klāre by Otto Hinnerk to your library as Did Not Finish.'</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>'klara' covered 1 of 4 title words (score 75 &lt; 80), so it wasn't treated as the owned book and the auto-add searched the catalogue.</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>A title's opening words name it (score 88); a near match to an owned title never auto-adds a stranger's book, the tool asks instead.</t>
+        </is>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>backend/src/modules/assistant/domains/books/text/match.ts, backend/src/modules/assistant/domains/books/pipeline/planChecks.ts</t>
+        </is>
+      </c>
+      <c r="L22" s="9" t="inlineStr"/>
+      <c r="M22" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N22" s="9" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>R2-04</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Tracking journal statistics</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>Reflection 'Save' after a session does nothing</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>Reader X &gt; typed a reflection &gt; Save (x3).</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>Saves and closes.</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>Dialog stays open, no message; the reflection never reaches the Journal.</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>Save sent the end call again with a reflection; the server treated the already-ended session's new reflection as 'different data' (409) and the error was swallowed.</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>A reflection can follow the end (only when none exists); errors are shown; Save/Skip return to the book page.</t>
+        </is>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>backend/src/modules/reading-sessions/reading-sessions.service.ts, frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/reader/ReflectionPrompt.tsx</t>
+        </is>
+      </c>
+      <c r="L23" s="9" t="inlineStr"/>
+      <c r="M23" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N23" s="9" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>R2-05</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Tracking journal statistics</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>A stale reader session blocks new sessions with a developer-style error</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>Left the reader by navigating away; later 'Start a reading session' on another book.</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>Start a timer, or offer to end the old one.</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>'Another session is already active for this user' and nothing shows or ends it.</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>Leaving the reader without closing it left the session ACTIVE; the 409 text was developer wording with no way out.</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>Leaving the reader pauses its session; the clash names the book ('You're still in a reading session for ...') and offers 'Pause that one and start here'.</t>
+        </is>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/library/SessionConflict.tsx, backend/src/modules/reading-sessions/reading-sessions.service.ts</t>
+        </is>
+      </c>
+      <c r="L24" s="9" t="inlineStr"/>
+      <c r="M24" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N24" s="9" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>R2-06</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Tracking journal statistics</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>Session time includes time away from the reader</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>Left the reader open in the background, came back, closed it.</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>Only active reading time.</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>'6 min of reading' for about a minute.</t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>Duration was end minus start, including time away.</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>Sessions record paused time (pausedAt, pausedSeconds); a hidden tab pauses and resumes; the idle sweep pauses from the last page turn; paused time is subtracted.</t>
+        </is>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>backend/prisma/schema.prisma, backend/src/modules/reading-sessions/*, frontend/src/features/reader/FlowReaderPage.tsx</t>
+        </is>
+      </c>
+      <c r="L25" s="9" t="inlineStr"/>
+      <c r="M25" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N25" s="9" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>R2-07</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Tracking journal statistics</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>Journal shows a raw internal position</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>Journal after a reader session.</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>'Chapter 4, 67%'.</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>'6 min · EPUB · epubcfi(/6/2!/4/2/1:0) → ch4'</t>
+        </is>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>The journal printed stored positions (CFI, chapter ids) as-is.</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="inlineStr">
+        <is>
+          <t>Entries carry startLabel/endLabel: chapter titles (from the chapter graph, CFIs by spine step), 'p. N' for pages.</t>
+        </is>
+      </c>
+      <c r="K26" s="9" t="inlineStr">
+        <is>
+          <t>backend/src/modules/journal/journal.service.ts, frontend/src/features/journal/JournalPage.tsx</t>
+        </is>
+      </c>
+      <c r="L26" s="9" t="inlineStr"/>
+      <c r="M26" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N26" s="9" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>R2-08</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>Can't select text in the default 3D Flip mode</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>Drag-select and double-click in 3D Flip.</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>Text selects; highlight popover appears.</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>Dragging starts a page curl; only works after switching to Paginated, with no hint.</t>
+        </is>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>react-pageflip took mouse and touch input in 3D Flip mode, so a drag curled the page instead of selecting.</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="inlineStr">
+        <is>
+          <t>The flipbook no longer takes pointer input: text selects in every mode; pages turn with the buttons, arrow keys or a swipe.</t>
+        </is>
+      </c>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/FlowReaderPage.tsx</t>
+        </is>
+      </c>
+      <c r="L27" s="9" t="inlineStr"/>
+      <c r="M27" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N27" s="9" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>R2-09</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>Phone reader shows ~6 lines in a tiny inset card</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>Mobile 375x812, reader.</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>Text fills the screen.</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>Small inner card, ~6 lines per page; bookmark and View Original missing from the toolbar.</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>Pages were always A4 halves of a two-page spread, tiny on a phone; ten toolbar icons overflowed.</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="inlineStr">
+        <is>
+          <t>Below 768px one page fills the screen; Note, Translate, Music, View Original and 'Not where you left off?' move into a More menu.</t>
+        </is>
+      </c>
+      <c r="K28" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/ai/TranslatePanel.tsx</t>
+        </is>
+      </c>
+      <c r="L28" s="9" t="inlineStr"/>
+      <c r="M28" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N28" s="9" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>R2-10</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Book page and details</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>Rating and Favourite silently lost without 'Save review'</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>Clicked 5 stars and Favourite, refreshed.</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>Saved instantly or warned.</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>All empty after refresh; no 'Saved' confirmation even when saving works.</t>
+        </is>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>Stars and Favourite only changed the form; nothing saved until 'Save review'.</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="inlineStr">
+        <is>
+          <t>Rating, favourite and reread save on click with a 'Saved.' note; unsaved review text is kept.</t>
+        </is>
+      </c>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reviews/ReviewPanel.tsx</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="inlineStr"/>
+      <c r="M29" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N29" s="9" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>R2-11</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Speed reliability</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>Logged out on refresh mid-session</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>~6 min after sign-in, refreshed the reader.</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>Stay signed in.</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>Sent to /login, then landed on Library.</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>Refresh tokens rotate on every use; two refreshes with the same cookie (StrictMode's double restore, parallel 401s, several tabs reloading) made the loser look like token reuse and signed the reader out.</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="inlineStr">
+        <is>
+          <t>One refresh at a time: shared within a tab and serialised across tabs with a Web Lock; a failed refresh never clears a newer token.</t>
+        </is>
+      </c>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/lib/api/client.ts, frontend/src/lib/auth-context.tsx</t>
+        </is>
+      </c>
+      <c r="L30" s="9" t="inlineStr"/>
+      <c r="M30" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N30" s="9" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>R2-12</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>Changing font size resets to the start</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>Page 2 of 8 &gt; font +2.</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>Same passage.</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>'Page 1 of 10', back at chapter 1.</t>
+        </is>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>Re-pagination re-anchored to the chapter's first page, and the flipbook wasn't remounted at the new index.</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t>Position is chapter + character offset; after any re-layout the reader lands on the page holding that passage.</t>
+        </is>
+      </c>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/reader/flow-layout.ts</t>
+        </is>
+      </c>
+      <c r="L31" s="9" t="inlineStr"/>
+      <c r="M31" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N31" s="9" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>R2-13</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>'View Original' loses your place and has no way back</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>At 67% &gt; View Original.</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>Same position; toggle back.</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>Opens at chapter 1, 0%; no side padding, default Times; only Close.</t>
+        </is>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>The original view ignored the reading view's position (epub.js only finds an idref with '#') and had only Close.</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="inlineStr">
+        <is>
+          <t>Opens at the chapter you were on; 'Back to reading view' button.</t>
+        </is>
+      </c>
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/ReaderPage.tsx, frontend/src/features/reader/EpubReader.tsx</t>
+        </is>
+      </c>
+      <c r="L32" s="9" t="inlineStr"/>
+      <c r="M32" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N32" s="9" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>R2-14</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>Reader renders shrunken after closing a session</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>X &gt; Session ended &gt; Skip.</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>Back to the library, or a normal reader.</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>A small card mid-screen; X vs Skip inconsistent.</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>The reflection prompt replaced the reader, and Save/Skip went 'back' in history, sometimes into the reading view of the ended session.</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="inlineStr">
+        <is>
+          <t>The prompt sits over the book; both readers return to the book page afterwards.</t>
+        </is>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/reader/ReaderPage.tsx</t>
+        </is>
+      </c>
+      <c r="L33" s="9" t="inlineStr"/>
+      <c r="M33" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N33" s="9" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>R2-15</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>Pages half empty; first spread's left page blank</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>Read the first spreads on desktop.</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>Pages fill.</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>Text stops two-thirds down; next spread has one line then a new chapter.</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>Pagination estimated characters per page (deliberately conservative) and the first page was laid out as a lone 'cover'.</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>Pages are measured with the real fonts in an offscreen copy of the page (about 97% full, nothing clipped); the cover slot is used only for a real cover.</t>
+        </is>
+      </c>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/flow-layout.ts, frontend/src/features/reader/FlowReaderPage.tsx</t>
+        </is>
+      </c>
+      <c r="L34" s="9" t="inlineStr"/>
+      <c r="M34" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N34" s="9" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>R2-16</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>'mins left' estimate depends on layout</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>Changed font size, chapter list, mobile.</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>Stable estimate.</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>~32, ~40, ~68, ~50 at the same spot.</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>'mins left' was pages left x 4.</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="inlineStr">
+        <is>
+          <t>Progress and time left come from characters read (about 230 words a minute), the same at any font size.</t>
+        </is>
+      </c>
+      <c r="K35" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/reader/ReaderProgressScrubber.tsx</t>
+        </is>
+      </c>
+      <c r="L35" s="9" t="inlineStr"/>
+      <c r="M35" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N35" s="9" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>R2-17</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>Arrow keys don't turn pages</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>Right arrow in the reader.</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>Next page.</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>No keyboard handling in the reading view.</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="inlineStr">
+        <is>
+          <t>Left/Right arrows and Page Up/Down turn pages (not while typing or in a dialog).</t>
+        </is>
+      </c>
+      <c r="K36" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/FlowReaderPage.tsx</t>
+        </is>
+      </c>
+      <c r="L36" s="9" t="inlineStr"/>
+      <c r="M36" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N36" s="9" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>R2-18</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Notes highlights reviews</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>Reader highlights/notes absent from the book page; no central notes view</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>Highlight with a margin note &gt; book page.</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>Listed on the book page.</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>'Notes: No notes yet.'</t>
+        </is>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>The book page listed notes only; highlights lived in the reader.</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>'Highlights &amp; quotes' on the book page, newest first, with colour, margin note and a link back into the book. (A separate all-books notes page isn't built.)</t>
+        </is>
+      </c>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/features/notes/BookHighlights.tsx, frontend/src/features/library/BookDetailPage.tsx</t>
+        </is>
+      </c>
+      <c r="L37" s="9" t="inlineStr"/>
+      <c r="M37" s="9" t="inlineStr">
+        <is>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="N37" s="9" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>R2-19</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Assistant chat</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>Natural follow-ups and phrasing variants fail</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>'finsihed circe, 4 stars and put it on comfort reads', 'put it on comfort reads', 'put circe on comfort reads', 'actually undo that'.</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>Handled, or each simple command.</t>
+        </is>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>The same canned 'not set up' reply each time; a message typed while pending wasn't sent on Enter.</t>
+        </is>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>'put X on Y' needed the word 'shelf'; 'it' was bound to the previous turn's subject; 'actually undo that' wasn't recognised.</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="inlineStr">
+        <is>
+          <t>Shelves named without 'shelf' (and 'add X to Y' when Y is a shelf or X is theirs); 'it' is the book named in the same message; undo accepts fillers. The tester's sentence now does status, rating and shelf without a model.</t>
+        </is>
+      </c>
+      <c r="K38" s="9" t="inlineStr">
+        <is>
+          <t>backend/src/modules/assistant/domains/books/conversation/quickCommands.ts, backend/src/modules/assistant/domains/books/pipeline/preRoute.ts, backend/src/modules/assistant/domains/books/pipeline/undo.ts</t>
+        </is>
+      </c>
+      <c r="L38" s="9" t="inlineStr"/>
+      <c r="M38" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N38" s="9" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>R2-20</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Tracking journal statistics</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>No finish dates, so 'this year' can't be answered</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>Marked books Finished; asked 'how many books did i read this year'.</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>Finish dates; yearly count.</t>
+        </is>
+      </c>
+      <c r="H39" s="9" t="inlineStr">
+        <is>
+          <t>'Bunko can only tell which were this year from logged reading sessions...'</t>
+        </is>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>No completion date was stored.</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="inlineStr">
+        <is>
+          <t>UserWork.finishedAt (SRS §18.2), set when marked Finished, backfilled from the last session; shown on the book page; 'this year' uses it.</t>
+        </is>
+      </c>
+      <c r="K39" s="9" t="inlineStr">
+        <is>
+          <t>backend/prisma/schema.prisma, backend/src/modules/library/library.service.ts, backend/src/modules/assistant/domains/books/conversation/libraryAnswers.ts, frontend/src/features/library/BookDetailPage.tsx</t>
+        </is>
+      </c>
+      <c r="L39" s="9" t="inlineStr"/>
+      <c r="M39" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N39" s="9" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>R2-21</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Library adding finding books</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>Book search slow and typo-intolerant</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>'tomorow and tomorrow and tomorrow'.</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>Right book within a couple of seconds.</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>10-15s spinner, unrelated results.</t>
+        </is>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>Catalogue providers are slow on a cold query and have no fuzzy matching; results are cached for an hour after the first search.</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="inlineStr">
+        <is>
+          <t>Not changed this round (needs a provider-side change).</t>
+        </is>
+      </c>
+      <c r="K40" s="9" t="inlineStr"/>
+      <c r="L40" s="9" t="inlineStr"/>
+      <c r="M40" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N40" s="9" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>R2-22</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>Library adding finding books</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>Status doesn't follow reading; no progress shown</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>Read to 67%, back to Library.</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>Status Reading; progress on the card.</t>
+        </is>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>Still Want to Read; no progress; 'Continue Reading' before ever opening.</t>
+        </is>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>Opening a book never changed its status; the button always said 'Continue Reading'.</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="inlineStr">
+        <is>
+          <t>Starting or logging a session moves Want to Read to Reading (never Finished/DNF); 'Start reading' until the first session. (Progress on cards not built.)</t>
+        </is>
+      </c>
+      <c r="K41" s="9" t="inlineStr">
+        <is>
+          <t>backend/src/modules/library/library.service.ts, backend/src/modules/reading-sessions/reading-sessions.service.ts, frontend/src/features/library/ContinueReadingButton.tsx</t>
+        </is>
+      </c>
+      <c r="L41" s="9" t="inlineStr"/>
+      <c r="M41" s="9" t="inlineStr">
+        <is>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="N41" s="9" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>R2-23</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Tracking journal statistics</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>Languages 'Unknown 6' and lowercase 'english'; EPUB reading added no pages</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>Statistics &gt; Languages.</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="inlineStr">
+        <is>
+          <t>'English'; EPUB pages counted.</t>
+        </is>
+      </c>
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t>'Unknown 6 books', 'english 1 book'; pages read only from the manual log.</t>
+        </is>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>The page passed language names through Intl.DisplayNames, which reads 'english' as a valid code and returns it lowercased; books with no language said 'Unknown'.</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="inlineStr">
+        <is>
+          <t>Only codes are looked up, names are capitalised; missing language reads 'Not recorded'. (EPUB pages need a start position; unchanged.)</t>
+        </is>
+      </c>
+      <c r="K42" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/features/statistics/chart-format.ts, frontend/src/features/statistics/StatisticsPage.tsx</t>
+        </is>
+      </c>
+      <c r="L42" s="9" t="inlineStr"/>
+      <c r="M42" s="9" t="inlineStr">
+        <is>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="N42" s="9" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>R2-24</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Shelves organizing</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>An empty shelf offers no way to add books</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>New shelf '2026 faves'.</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>An 'Add books' picker.</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>Text only, no button.</t>
+        </is>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>No way to add books from a shelf.</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="inlineStr">
+        <is>
+          <t>'Add books' on custom shelves and in the empty state: a searchable picker of library books.</t>
+        </is>
+      </c>
+      <c r="K43" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/features/shelves/AddToShelfDialog.tsx, frontend/src/features/shelves/ShelvesPage.tsx</t>
+        </is>
+      </c>
+      <c r="L43" s="9" t="inlineStr"/>
+      <c r="M43" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N43" s="9" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>R2-25</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>Shelves organizing</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>polish</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>Low-contrast toggle and unlabeled shelf tabs</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>Shelves page.</t>
+        </is>
+      </c>
+      <c r="G44" s="9" t="inlineStr">
+        <is>
+          <t>Readable toggle; named tabs.</t>
+        </is>
+      </c>
+      <c r="H44" s="9" t="inlineStr">
+        <is>
+          <t>'Covers' dark brown on near-black; tabs read as unnamed buttons; odd brown scrollbar strip.</t>
+        </is>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>Inactive toggle text at 70% opacity on near-black; dark wood scrollbar on the paper background.</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="inlineStr">
+        <is>
+          <t>Full-strength toggle text; shelf tabs say their name and count and report pressed state; light paper scrollbar.</t>
+        </is>
+      </c>
+      <c r="K44" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/features/shelves/ShelvesPage.tsx, frontend/src/index.css</t>
+        </is>
+      </c>
+      <c r="L44" s="9" t="inlineStr"/>
+      <c r="M44" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N44" s="9" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>R2-26</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>Tracking journal statistics</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>polish</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>Journal order wrong; entries can't be edited</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>Logged a session after another the same day.</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>Newest first; edit/delete.</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="inlineStr">
+        <is>
+          <t>Newer entry below the older; clicking opens the book.</t>
+        </is>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>Journal sorted by start time, so a session logged after the fact sorted by when it began.</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="inlineStr">
+        <is>
+          <t>Sorted by when sessions ended. (Editing an entry isn't built.)</t>
+        </is>
+      </c>
+      <c r="K45" s="9" t="inlineStr">
+        <is>
+          <t>backend/src/modules/journal/journal.service.ts</t>
+        </is>
+      </c>
+      <c r="L45" s="9" t="inlineStr"/>
+      <c r="M45" s="9" t="inlineStr">
+        <is>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="N45" s="9" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>R2-27</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>Book page and details</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>polish</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>Duplicate status, marketing-blurb synopsis, small icon issues</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>Book pages and reader toolbar.</t>
+        </is>
+      </c>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>One status control, clean synopsis, labelled icons.</t>
+        </is>
+      </c>
+      <c r="H46" s="9" t="inlineStr">
+        <is>
+          <t>Pill plus dropdown; synopsis starts with press quotes; unlabeled icon; bookmark icon never fills.</t>
+        </is>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>Status showed as a pill and a dropdown; catalogue copy opens with press quotes; bookmark icon never reflected state.</t>
+        </is>
+      </c>
+      <c r="J46" s="9" t="inlineStr">
+        <is>
+          <t>One labelled status control; leading press quotes and ALL-CAPS banners trimmed for display; the bookmark fills when the chapter is bookmarked.</t>
+        </is>
+      </c>
+      <c r="K46" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/features/library/BookDetailPage.tsx, frontend/src/features/library/synopsis.ts, frontend/src/features/reader/FlowReaderPage.tsx</t>
+        </is>
+      </c>
+      <c r="L46" s="9" t="inlineStr"/>
+      <c r="M46" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N46" s="9" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>R2-28</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>First impression onboarding</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>polish</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>No import or account basics for switchers</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>Welcome screen and Settings.</t>
+        </is>
+      </c>
+      <c r="G47" s="9" t="inlineStr">
+        <is>
+          <t>Import, yearly goal, export, change password.</t>
+        </is>
+      </c>
+      <c r="H47" s="9" t="inlineStr">
+        <is>
+          <t>None present.</t>
+        </is>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>Import (SRS §37), reading goals, export and password change aren't in the MVP scope.</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="inlineStr">
+        <is>
+          <t>Not built; needs product approval.</t>
+        </is>
+      </c>
+      <c r="K47" s="9" t="inlineStr"/>
+      <c r="L47" s="9" t="inlineStr"/>
+      <c r="M47" s="9" t="inlineStr">
+        <is>
+          <t>Won't fix (needs approval)</t>
+        </is>
+      </c>
+      <c r="N47" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N19"/>
+  <autoFilter ref="A1:N47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1842,7 +3642,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Round 1</t>
         </is>
@@ -1884,172 +3684,172 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>First impression onboarding</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
+      <c r="B6" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Calm, bookish login with a clear error, but no forgot-password, onboarding or import, and the first library screen shows wrong covers.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Library adding finding books</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>Exact search works and doesn't duplicate, but a single typo gives junk, search takes 6-8s, covers are wrong, there's no sort and no status choice when adding.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Book page and details</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B8" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Tidy single screen, but no description, pages or publication info, no way to fix a cover, and modal buttons that do nothing.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Reading experience</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>The sample EPUB couldn't be opened from any path.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Tracking journal statistics</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n">
+      <c r="B10" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Timer-only sessions, pages not counted, journal entries don't name the book, stats contradict themselves.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Shelves organizing</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>Charming bookcase and inline shelf creation, but odd one-book rows, per-row scrollbars, an inverted toggle and overlapping arrows on mobile.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Notes highlights reviews</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n">
+      <c r="B12" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Fast and pleasant, but whole stars only, notes undated, and highlights impossible without the reader.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Assistant chat</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n">
+      <c r="B13" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Good when phrased exactly, but about half the messages failed with 'An unexpected error occurred'; it can't handle 'it' or typos, and it invented 'Dune II'.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Look and feel</t>
         </is>
       </c>
-      <c r="B14" s="10" t="n">
+      <c r="B14" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Feels made by book people; wrong covers undercut it.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Speed reliability</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n">
+      <c r="B15" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Slow covers and search, status changes take ~3s with no feedback, assistant failures, remove seemed to do nothing.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Overall</t>
         </is>
       </c>
-      <c r="B16" s="10" t="n">
+      <c r="B16" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Good bones and taste, but I can't read a book, covers are wrong, the journal doesn't name books, and the assistant fails half the time.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>Issues and fixes</t>
         </is>
@@ -2128,1061 +3928,1061 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>R1-01</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>Reading experience</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>blocker</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>No way to open the digital reader, even for a book with an EPUB</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="9" t="inlineStr">
         <is>
           <t>Library &gt; 'A Bunko Sample Book' &gt; 'Open Digital Reader'; clicked the EPUB edition row; tried status Reading, reload, and 'Start / Resume Reading Session'.</t>
         </is>
       </c>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="G20" s="9" t="inlineStr">
         <is>
           <t>The EPUB opens in the reader.</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
+      <c r="H20" s="9" t="inlineStr">
         <is>
           <t>Every path lands on the book details page; the EPUB edition row has no read button.</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="I20" s="9" t="inlineStr">
         <is>
           <t>QA seed attached the EPUB with the upload id instead of the stored file id, so no copy existed; and the app gave a digital edition without its file no way forward.</t>
         </is>
       </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="J20" s="9" t="inlineStr">
         <is>
           <t>Seed fixed (uses the id /files/:id/confirm returns) and now ships an original 5-chapter novella. A digital edition with no file shows 'Upload file'; the quick-action modal only offers actions that work.</t>
         </is>
       </c>
-      <c r="K20" s="8" t="inlineStr">
+      <c r="K20" s="9" t="inlineStr">
         <is>
           <t>backend/scripts/seed-qa-reader.ts, backend/scripts/qa-sample-book.ts, frontend/src/features/library/BookDetailPage.tsx, frontend/src/features/library/AddEditionDialog.tsx, frontend/src/features/library/BookQuickActionModal.tsx</t>
         </is>
       </c>
-      <c r="L20" s="8" t="inlineStr"/>
-      <c r="M20" s="8" t="inlineStr">
+      <c r="L20" s="9" t="inlineStr"/>
+      <c r="M20" s="9" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N20" s="8" t="inlineStr"/>
+      <c r="N20" s="9" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="n">
+      <c r="A21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>R1-02</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>Library adding finding books</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>Most covers are for completely different books</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr">
         <is>
           <t>Open Library (also Shelves, modal, book page).</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>The real cover for each book.</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
+      <c r="H21" s="9" t="inlineStr">
         <is>
           <t>The Left Hand of Darkness and the sample book show 'Their Eyes Were Watching God'; Circe, Piranesi and Klara show unrelated books; a hand-added zine got a random cover. There's no way to change or remove a cover.</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="I21" s="9" t="inlineStr">
         <is>
           <t>Three code paths took the first search result with any cover regardless of title; the seed also used guessed cover ids. Wikidata series discovery filed books under their own title.</t>
         </is>
       </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="J21" s="9" t="inlineStr">
         <is>
           <t>Covers only from a result with the same main title and a shared author surname (pickMatchingCover), looked up in the background; self-named series ignored and cleared. Changing/removing a cover by hand is not built yet (covers live on the shared catalogue entry).</t>
         </is>
       </c>
-      <c r="K21" s="8" t="inlineStr">
+      <c r="K21" s="9" t="inlineStr">
         <is>
           <t>backend/src/modules/library/library.service.ts, backend/scripts/seed-qa-reader.ts</t>
         </is>
       </c>
-      <c r="L21" s="8" t="inlineStr"/>
-      <c r="M21" s="8" t="inlineStr">
+      <c r="L21" s="9" t="inlineStr"/>
+      <c r="M21" s="9" t="inlineStr">
         <is>
           <t>Partly fixed</t>
         </is>
       </c>
-      <c r="N21" s="8" t="inlineStr"/>
+      <c r="N21" s="9" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>R1-03</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>Assistant chat</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>Many assistant messages fail with a generic error</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F22" s="9" t="inlineStr">
         <is>
           <t>'no i meant the zevin one...', 'I started Tomorrow, and Tomorrow, and Tomorrow' (the app's own example), 'ok i started the first one. and dnf'd circe tbh', 'and add it to my comfort reads shelf', 'rate it 5 stars actually'.</t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="G22" s="9" t="inlineStr">
         <is>
           <t>The change is made, or a clarifying question.</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
+      <c r="H22" s="9" t="inlineStr">
         <is>
           <t>'An unexpected error occurred' each time, no reason, no retry. Short single-book commands worked.</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="I22" s="9" t="inlineStr">
         <is>
           <t>No NVIDIA key on the test server: NIM's 401 became a plain Error and surfaced as a 500. Separately, titles with commas, filler words ('ok', 'and', 'tbh', 'actually') and 'it' defeated the fast paths, so those messages needed the model.</t>
         </is>
       </c>
-      <c r="J22" s="8" t="inlineStr">
+      <c r="J22" s="9" t="inlineStr">
         <is>
           <t>Rejected key / rate limit are 'unavailable'; a missing key is detected at startup and answered with a plain message; any other failure is a friendly logged reply. Owned titles with commas are masked before clause splitting; filler words stripped.</t>
         </is>
       </c>
-      <c r="K22" s="8" t="inlineStr">
+      <c r="K22" s="9" t="inlineStr">
         <is>
           <t>backend/src/modules/assistant/clients/NvidiaNimClient.ts, backend/src/modules/assistant/aiController.ts, backend/src/modules/assistant/domains/books/conversation/quickCommands.ts</t>
         </is>
       </c>
-      <c r="L22" s="8" t="inlineStr"/>
-      <c r="M22" s="8" t="inlineStr">
+      <c r="L22" s="9" t="inlineStr"/>
+      <c r="M22" s="9" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N22" s="8" t="inlineStr"/>
+      <c r="N22" s="9" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="n">
+      <c r="A23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>R1-04</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>Assistant chat</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>A typo in an owned title makes it search the catalogue for junk</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>'started tomorow and tomorrow last night, its so good already' (the book is in the library).</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>It matches the owned book.</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
+      <c r="H23" s="9" t="inlineStr">
         <is>
           <t>"I couldn't find a book called \"tomorow\". The closest were \"Notes on the History of Fort George\"..."</t>
         </is>
       </c>
-      <c r="I23" s="8" t="inlineStr">
+      <c r="I23" s="9" t="inlineStr">
         <is>
           <t>Title matching needed exact words; the list splitter split 'tomorow and tomorrow' into two books.</t>
         </is>
       </c>
-      <c r="J23" s="8" t="inlineStr">
+      <c r="J23" s="9" t="inlineStr">
         <is>
           <t>Typo-tolerant word matching on owned titles; lists split only into books the reader owns.</t>
         </is>
       </c>
-      <c r="K23" s="8" t="inlineStr">
+      <c r="K23" s="9" t="inlineStr">
         <is>
           <t>backend/src/modules/assistant/domains/books/text/match.ts, backend/src/modules/assistant/domains/books/conversation/quickCommands.ts</t>
         </is>
       </c>
-      <c r="L23" s="8" t="inlineStr"/>
-      <c r="M23" s="8" t="inlineStr">
+      <c r="L23" s="9" t="inlineStr"/>
+      <c r="M23" s="9" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N23" s="8" t="inlineStr"/>
+      <c r="N23" s="9" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n">
+      <c r="A24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>R1-05</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>Assistant chat</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>Recommendations made up a sequel and ignored 'something like Piranesi'</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F24" s="9" t="inlineStr">
         <is>
           <t>'what should i read next? something like piranesi'</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="G24" s="9" t="inlineStr">
         <is>
           <t>Books like Piranesi, and accurate facts.</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="H24" s="9" t="inlineStr">
         <is>
           <t>Listed the Want to Read list only, and said 'the series continues with Dune II by Frank Herbert' (no such book).</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="I24" s="9" t="inlineStr">
         <is>
           <t>The 'series continues' line came from a Wikidata lookup that returned non-books ('Dune II'); 'like X' wasn't used.</t>
         </is>
       </c>
-      <c r="J24" s="8" t="inlineStr">
+      <c r="J24" s="9" t="inlineStr">
         <is>
           <t>Series continuation removed; 'something like X' ranks the list by X's authors and genres with reasons, and asks the model for books beyond the list.</t>
         </is>
       </c>
-      <c r="K24" s="8" t="inlineStr">
+      <c r="K24" s="9" t="inlineStr">
         <is>
           <t>backend/src/modules/assistant/domains/books/actions/readTools.ts, backend/src/modules/assistant/domains/books/pipeline/preRoute.ts, backend/src/modules/assistant/domains/books/prompts/answerPrompt.ts</t>
         </is>
       </c>
-      <c r="L24" s="8" t="inlineStr"/>
-      <c r="M24" s="8" t="inlineStr">
+      <c r="L24" s="9" t="inlineStr"/>
+      <c r="M24" s="9" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N24" s="8" t="inlineStr"/>
+      <c r="N24" s="9" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="n">
+      <c r="A25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>R1-06</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>Tracking journal statistics</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>Journal entries don't say which book</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>Piranesi &gt; physical edition &gt; session &gt; end with 'p 112' and a reflection &gt; Journal.</t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="G25" s="9" t="inlineStr">
         <is>
           <t>Entry shows the book, page and time, and links to it.</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="H25" s="9" t="inlineStr">
         <is>
           <t>'Oct 23, 2026 · 0 min · “the other is kinda sus now”': no title, no page, not clickable; no way to add an entry from the Journal.</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr">
+      <c r="I25" s="9" t="inlineStr">
         <is>
           <t>Journal entries carried no book.</t>
         </is>
       </c>
-      <c r="J25" s="8" t="inlineStr">
+      <c r="J25" s="9" t="inlineStr">
         <is>
           <t>Each entry names and links its book with its cover and format; 'Log reading' on the Journal.</t>
         </is>
       </c>
-      <c r="K25" s="8" t="inlineStr">
+      <c r="K25" s="9" t="inlineStr">
         <is>
           <t>backend/src/modules/journal/journal.service.ts, frontend/src/features/journal/JournalPage.tsx</t>
         </is>
       </c>
-      <c r="L25" s="8" t="inlineStr"/>
-      <c r="M25" s="8" t="inlineStr">
+      <c r="L25" s="9" t="inlineStr"/>
+      <c r="M25" s="9" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N25" s="8" t="inlineStr"/>
+      <c r="N25" s="9" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="n">
+      <c r="A26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>R1-07</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Tracking journal statistics</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>Reading can only be logged live, and pages aren't counted</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="F26" s="9" t="inlineStr">
         <is>
           <t>Started and immediately ended a session with 'p 112'.</t>
         </is>
       </c>
-      <c r="G26" s="8" t="inlineStr">
+      <c r="G26" s="9" t="inlineStr">
         <is>
           <t>Log a past session (time, date, page), and pages count.</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
+      <c r="H26" s="9" t="inlineStr">
         <is>
           <t>'Session saved — 0 min. Nice reading.' Stats: 'Pages read 0'. No manual duration/date, no progress on the book, no finish date.</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
+      <c r="I26" s="9" t="inlineStr">
         <is>
           <t>Only live timed sessions existed; a physical session with only an end page can't count pages.</t>
         </is>
       </c>
-      <c r="J26" s="8" t="inlineStr">
+      <c r="J26" s="9" t="inlineStr">
         <is>
           <t>POST /reading-sessions/log and a 'Log reading' form (book, day, minutes, from/to page, reflection) on the Journal and book page; both pages make them count.</t>
         </is>
       </c>
-      <c r="K26" s="8" t="inlineStr">
+      <c r="K26" s="9" t="inlineStr">
         <is>
           <t>backend/src/modules/reading-sessions/*, frontend/src/features/journal/LogSessionDialog.tsx</t>
         </is>
       </c>
-      <c r="L26" s="8" t="inlineStr"/>
-      <c r="M26" s="8" t="inlineStr">
+      <c r="L26" s="9" t="inlineStr"/>
+      <c r="M26" s="9" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N26" s="8" t="inlineStr"/>
+      <c r="N26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="n">
+      <c r="A27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>R1-08</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>Book page and details</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>Modal buttons silently do nothing without a matching edition</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F27" s="9" t="inlineStr">
         <is>
           <t>Circe (no editions) &gt; 'Start / Resume Reading Session'; Piranesi (physical only) &gt; 'Open Digital Reader'.</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>Hidden, disabled, or explained.</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="H27" s="9" t="inlineStr">
         <is>
           <t>Both silently go to the book page.</t>
         </is>
       </c>
-      <c r="I27" s="8" t="inlineStr">
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>Modal buttons fell back to navigating to the book page.</t>
         </is>
       </c>
-      <c r="J27" s="8" t="inlineStr">
+      <c r="J27" s="9" t="inlineStr">
         <is>
           <t>Modal shows only working actions and explains/offers to add a copy otherwise.</t>
         </is>
       </c>
-      <c r="K27" s="8" t="inlineStr">
+      <c r="K27" s="9" t="inlineStr">
         <is>
           <t>frontend/src/features/library/BookQuickActionModal.tsx</t>
         </is>
       </c>
-      <c r="L27" s="8" t="inlineStr"/>
-      <c r="M27" s="8" t="inlineStr">
+      <c r="L27" s="9" t="inlineStr"/>
+      <c r="M27" s="9" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N27" s="8" t="inlineStr"/>
+      <c r="N27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="n">
+      <c r="A28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>R1-09</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>Tracking journal statistics</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>Statistics contradict themselves; language data messy</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="F28" s="9" t="inlineStr">
         <is>
           <t>Statistics &gt; Daily.</t>
         </is>
       </c>
-      <c r="G28" s="8" t="inlineStr">
+      <c r="G28" s="9" t="inlineStr">
         <is>
           <t>Consistent numbers.</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
+      <c r="H28" s="9" t="inlineStr">
         <is>
           <t>Summary counts 1 session while the chart says 'No reading sessions in this period yet'; languages 'Unknown 6' and lowercase 'english 2'; 'Bunko' listed as an author.</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
+      <c r="I28" s="9" t="inlineStr">
         <is>
           <t>The chart's empty state keyed on minutes, not sessions; language labels weren't normalised.</t>
         </is>
       </c>
-      <c r="J28" s="8" t="inlineStr">
+      <c r="J28" s="9" t="inlineStr">
         <is>
           <t>Chart distinguishes 'no sessions' from 'sessions under a minute'; languages shown as names. ('Bunko' as author was seed data; reading goals aren't in the SRS.)</t>
         </is>
       </c>
-      <c r="K28" s="8" t="inlineStr">
+      <c r="K28" s="9" t="inlineStr">
         <is>
           <t>frontend/src/features/statistics/ActivityChart.tsx, backend/src/modules/statistics/statistics.service.ts</t>
         </is>
       </c>
-      <c r="L28" s="8" t="inlineStr"/>
-      <c r="M28" s="8" t="inlineStr">
+      <c r="L28" s="9" t="inlineStr"/>
+      <c r="M28" s="9" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N28" s="8" t="inlineStr"/>
+      <c r="N28" s="9" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="n">
+      <c r="A29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>R1-10</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>Library adding finding books</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>Catalogue search isn't typo-tolerant and is slow; no status on add</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
+      <c r="F29" s="9" t="inlineStr">
         <is>
           <t>Add a book &gt; 'tomorow and tomorrow and tomorrow'.</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
+      <c r="G29" s="9" t="inlineStr">
         <is>
           <t>The right book near the top.</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
+      <c r="H29" s="9" t="inlineStr">
         <is>
           <t>After 6-8s: unrelated results. Confusing language chips; manual form lacks page count/cover; always added as Want to Read.</t>
         </is>
       </c>
-      <c r="I29" s="8" t="inlineStr">
+      <c r="I29" s="9" t="inlineStr">
         <is>
           <t>Google Books answered first with poor relevance; the universe check could hijack results; no caching; original language defaulted to 'Japanese'.</t>
         </is>
       </c>
-      <c r="J29" s="8" t="inlineStr">
+      <c r="J29" s="9" t="inlineStr">
         <is>
           <t>Open Library title search merged in; results ranked by title match; universe check only for named universes; searches cached an hour; choose Want to read / Reading now / Already read when adding; calm metadata line replaces off-palette chips. (Catalogue-side typo tolerance depends on the providers.)</t>
         </is>
       </c>
-      <c r="K29" s="8" t="inlineStr">
+      <c r="K29" s="9" t="inlineStr">
         <is>
           <t>backend/src/modules/metadata/metadata.service.ts, frontend/src/features/library/AddBookDialog.tsx</t>
         </is>
       </c>
-      <c r="L29" s="8" t="inlineStr"/>
-      <c r="M29" s="8" t="inlineStr">
+      <c r="L29" s="9" t="inlineStr"/>
+      <c r="M29" s="9" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N29" s="8" t="inlineStr"/>
+      <c r="N29" s="9" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="n">
+      <c r="A30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>R1-11</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>Library adding finding books</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>'Remove from library' gave no visible response</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
+      <c r="F30" s="9" t="inlineStr">
         <is>
           <t>Book page &gt; 'Remove from library'.</t>
         </is>
       </c>
-      <c r="G30" s="8" t="inlineStr">
+      <c r="G30" s="9" t="inlineStr">
         <is>
           <t>A confirmation, then the book is gone.</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="H30" s="9" t="inlineStr">
         <is>
           <t>Nothing visible; the book stayed.</t>
         </is>
       </c>
-      <c r="I30" s="8" t="inlineStr">
+      <c r="I30" s="9" t="inlineStr">
         <is>
           <t>Used the browser's native confirm(), which the tester never saw.</t>
         </is>
       </c>
-      <c r="J30" s="8" t="inlineStr">
+      <c r="J30" s="9" t="inlineStr">
         <is>
           <t>In-app confirmation dialog that says what's kept.</t>
         </is>
       </c>
-      <c r="K30" s="8" t="inlineStr">
+      <c r="K30" s="9" t="inlineStr">
         <is>
           <t>frontend/src/features/library/BookDetailPage.tsx</t>
         </is>
       </c>
-      <c r="L30" s="8" t="inlineStr"/>
-      <c r="M30" s="8" t="inlineStr">
+      <c r="L30" s="9" t="inlineStr"/>
+      <c r="M30" s="9" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N30" s="8" t="inlineStr"/>
+      <c r="N30" s="9" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="n">
+      <c r="A31" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>R1-12</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>Shelves organizing</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>Odd shelf grouping, per-row scrollbars, inverted toggle</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
+      <c r="F31" s="9" t="inlineStr">
         <is>
           <t>Shelves &gt; All Volumes; Covers/Spines toggle; mobile.</t>
         </is>
       </c>
-      <c r="G31" s="8" t="inlineStr">
+      <c r="G31" s="9" t="inlineStr">
         <is>
           <t>Books share shelves; the active view is clear.</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
+      <c r="H31" s="9" t="inlineStr">
         <is>
           <t>One book per tall row under its own title; every row has a scrollbar; the active toggle option is the dim one; the choice doesn't stick; arrows cover art on mobile.</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="I31" s="9" t="inlineStr">
         <is>
           <t>Rows per one-book series/genre; overflow-x-auto made rows scroll vertically; active toggle was the dark pill; arrows forced visible on mobile.</t>
         </is>
       </c>
-      <c r="J31" s="8" t="inlineStr">
+      <c r="J31" s="9" t="inlineStr">
         <is>
           <t>Rows need two books; overflow-y hidden with a thin themed scrollbar; light active pill with aria-pressed, remembered; arrows on focus/hover only.</t>
         </is>
       </c>
-      <c r="K31" s="8" t="inlineStr">
+      <c r="K31" s="9" t="inlineStr">
         <is>
           <t>frontend/src/features/shelves/*</t>
         </is>
       </c>
-      <c r="L31" s="8" t="inlineStr"/>
-      <c r="M31" s="8" t="inlineStr">
+      <c r="L31" s="9" t="inlineStr"/>
+      <c r="M31" s="9" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N31" s="8" t="inlineStr"/>
+      <c r="N31" s="9" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="n">
+      <c r="A32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>R1-13</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>Speed reliability</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>Slow loads with little feedback</t>
         </is>
       </c>
-      <c r="F32" s="8" t="inlineStr">
+      <c r="F32" s="9" t="inlineStr">
         <is>
           <t>Library, Shelves, book pages; status dropdown.</t>
         </is>
       </c>
-      <c r="G32" s="8" t="inlineStr">
+      <c r="G32" s="9" t="inlineStr">
         <is>
           <t>Fast, with placeholders.</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="H32" s="9" t="inlineStr">
         <is>
           <t>Covers blank for 3-5s on every visit; a big modal spinner; status change ~3s while the old value still shows.</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="I32" s="9" t="inlineStr">
         <is>
           <t>Opening a book ran series discovery and a cover search synchronously (2-3s); covers had no placeholder; status change waited for the server.</t>
         </is>
       </c>
-      <c r="J32" s="8" t="inlineStr">
+      <c r="J32" s="9" t="inlineStr">
         <is>
           <t>Both moved to the background (book fetch ~72 ms); lazy covers on a paper tint; skeleton in the modal; optimistic status updates.</t>
         </is>
       </c>
-      <c r="K32" s="8" t="inlineStr">
+      <c r="K32" s="9" t="inlineStr">
         <is>
           <t>backend/src/modules/library/library.service.ts, frontend/src/features/library/BookCover.tsx, frontend/src/lib/api/works.ts</t>
         </is>
       </c>
-      <c r="L32" s="8" t="inlineStr"/>
-      <c r="M32" s="8" t="inlineStr">
+      <c r="L32" s="9" t="inlineStr"/>
+      <c r="M32" s="9" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N32" s="8" t="inlineStr"/>
+      <c r="N32" s="9" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="n">
+      <c r="A33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>R1-14</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>Notes highlights reviews</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>Reviews and notes are basic</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="F33" s="9" t="inlineStr">
         <is>
           <t>Rated, reviewed, added and edited a note.</t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="G33" s="9" t="inlineStr">
         <is>
           <t>Half stars, dated notes, spoiler/private options.</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr">
+      <c r="H33" s="9" t="inlineStr">
         <is>
           <t>Whole stars only; notes undated with only a 'Book' tag; highlights impossible (R1-01).</t>
         </is>
       </c>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="I33" s="9" t="inlineStr">
         <is>
           <t>Notes showed no date; ratings are whole stars by SRS §14.</t>
         </is>
       </c>
-      <c r="J33" s="8" t="inlineStr">
+      <c r="J33" s="9" t="inlineStr">
         <is>
           <t>Notes show their date (and position); the review box says reviews and notes are private. Half stars not added: SRS §14 sets whole 5-star ratings.</t>
         </is>
       </c>
-      <c r="K33" s="8" t="inlineStr">
+      <c r="K33" s="9" t="inlineStr">
         <is>
           <t>frontend/src/features/notes/NotesPanel.tsx, frontend/src/features/reviews/ReviewPanel.tsx</t>
         </is>
       </c>
-      <c r="L33" s="8" t="inlineStr"/>
-      <c r="M33" s="8" t="inlineStr">
+      <c r="L33" s="9" t="inlineStr"/>
+      <c r="M33" s="9" t="inlineStr">
         <is>
           <t>Partly fixed</t>
         </is>
       </c>
-      <c r="N33" s="8" t="inlineStr"/>
+      <c r="N33" s="9" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="n">
+      <c r="A34" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>R1-15</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>Assistant chat</t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>polish</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t>Odd reply after declining a follow-up</t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
+      <c r="F34" s="9" t="inlineStr">
         <is>
           <t>'rate piranesi 5 stars' &gt; asked to mark Finished &gt; 'nah not yet'.</t>
         </is>
       </c>
-      <c r="G34" s="8" t="inlineStr">
+      <c r="G34" s="9" t="inlineStr">
         <is>
           <t>'Okay, I'll leave it as Reading.'</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr">
+      <c r="H34" s="9" t="inlineStr">
         <is>
           <t>'Okay, I kept Piranesi.' (sounds like it nearly removed it).</t>
         </is>
       </c>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="I34" s="9" t="inlineStr">
         <is>
           <t>The decline message was the generic 'Okay, I kept X.'</t>
         </is>
       </c>
-      <c r="J34" s="8" t="inlineStr">
+      <c r="J34" s="9" t="inlineStr">
         <is>
           <t>Follow-up offers can say what 'no' means (general core hook): 'Okay, Piranesi stays as Reading.'</t>
         </is>
       </c>
-      <c r="K34" s="8" t="inlineStr">
+      <c r="K34" s="9" t="inlineStr">
         <is>
           <t>backend/src/modules/assistant/domain/DomainPack.ts, backend/src/modules/assistant/AIRuntime.ts, backend/src/modules/assistant/domains/books/pipeline/replies.ts</t>
         </is>
       </c>
-      <c r="L34" s="8" t="inlineStr"/>
-      <c r="M34" s="8" t="inlineStr">
+      <c r="L34" s="9" t="inlineStr"/>
+      <c r="M34" s="9" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N34" s="8" t="inlineStr"/>
+      <c r="N34" s="9" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="n">
+      <c r="A35" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>R1-16</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>First impression onboarding</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t>polish</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>No forgot-password, no import of an existing history</t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr">
+      <c r="F35" s="9" t="inlineStr">
         <is>
           <t>Login and register pages; Settings.</t>
         </is>
       </c>
-      <c r="G35" s="8" t="inlineStr">
+      <c r="G35" s="9" t="inlineStr">
         <is>
           <t>Forgot password; Goodreads/StoryGraph import.</t>
         </is>
       </c>
-      <c r="H35" s="8" t="inlineStr">
+      <c r="H35" s="9" t="inlineStr">
         <is>
           <t>Neither exists.</t>
         </is>
       </c>
-      <c r="I35" s="8" t="inlineStr">
+      <c r="I35" s="9" t="inlineStr">
         <is>
           <t>Password reset needs email delivery (none configured); importing other platforms is SRS §37, which needs product approval.</t>
         </is>
       </c>
-      <c r="J35" s="8" t="inlineStr">
+      <c r="J35" s="9" t="inlineStr">
         <is>
           <t>Not built. A first-run welcome now explains the three ways to start (add, read/log, assistant).</t>
         </is>
       </c>
-      <c r="K35" s="8" t="inlineStr">
+      <c r="K35" s="9" t="inlineStr">
         <is>
           <t>frontend/src/features/library/LibraryPage.tsx</t>
         </is>
       </c>
-      <c r="L35" s="8" t="inlineStr"/>
-      <c r="M35" s="8" t="inlineStr">
+      <c r="L35" s="9" t="inlineStr"/>
+      <c r="M35" s="9" t="inlineStr">
         <is>
           <t>Won't fix (needs approval)</t>
         </is>
       </c>
-      <c r="N35" s="8" t="inlineStr"/>
+      <c r="N35" s="9" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="n">
+      <c r="A36" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>R1-17</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>Look and feel</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="D36" s="9" t="inlineStr">
         <is>
           <t>polish</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E36" s="9" t="inlineStr">
         <is>
           <t>Sidebar scrolls away on long pages</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="F36" s="9" t="inlineStr">
         <is>
           <t>Scrolled a long book page on desktop.</t>
         </is>
       </c>
-      <c r="G36" s="8" t="inlineStr">
+      <c r="G36" s="9" t="inlineStr">
         <is>
           <t>Navigation and Sign out stay in reach.</t>
         </is>
       </c>
-      <c r="H36" s="8" t="inlineStr">
+      <c r="H36" s="9" t="inlineStr">
         <is>
           <t>The sidebar scrolls with the content.</t>
         </is>
       </c>
-      <c r="I36" s="8" t="inlineStr">
+      <c r="I36" s="9" t="inlineStr">
         <is>
           <t>Sidebar wasn't sticky.</t>
         </is>
       </c>
-      <c r="J36" s="8" t="inlineStr">
+      <c r="J36" s="9" t="inlineStr">
         <is>
           <t>Sticky full-height sidebar on desktop.</t>
         </is>
       </c>
-      <c r="K36" s="8" t="inlineStr">
+      <c r="K36" s="9" t="inlineStr">
         <is>
           <t>frontend/src/components/layout/AppShell.tsx</t>
         </is>
       </c>
-      <c r="L36" s="8" t="inlineStr"/>
-      <c r="M36" s="8" t="inlineStr">
+      <c r="L36" s="9" t="inlineStr"/>
+      <c r="M36" s="9" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N36" s="8" t="inlineStr"/>
+      <c r="N36" s="9" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>What the tester liked</t>
         </is>
@@ -3220,6 +5020,2092 @@
       <c r="A43" t="inlineStr">
         <is>
           <t>Solid mobile layout: bottom tab bar, two-column cover grid, full-width search, and a cleanly stacked book page.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="52" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Round 2</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Meera, book-lover persona (code-blind agent; browser only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Local: frontend :5174, API :3100; assistant model not configured (no NVIDIA_API_KEY), tester told so. Fresh seeded account with an original 5-chapter EPUB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Tester's reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>First impression onboarding</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Calm login and a 3-step welcome for a new account; quick sign-up. No Goodreads/StoryGraph import.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Library adding finding books</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Rich results and the status choice on add are lovely, but search took 10-15s, a one-letter typo found nothing, covers slow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Book page and details</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Clean, nice privacy line, but rating/favourite silently lost without 'Save review'; no progress, dates or highlights on the page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Strong appearance panel, search, chapter jumps, resume; but no paragraph breaks, titles printed three times, highlights not drawn, no selection in 3D Flip, font change resets position, broken phone layout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Tracking journal statistics</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Excellent manual log; but reflection Save does nothing, raw 'epubcfi(...)' in the journal, inflated session time, a stale session blocks new ones, no finish dates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Shelves organizing</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Charming bookcase with genre rows, instant shelf creation; empty shelf can't add books, faint 'Covers' toggle, unlabeled tabs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Notes highlights reviews</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Good selection popover and margin notes; highlights not drawn, reader notes absent from the book page, no central notes view, no review confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Assistant chat</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Exact commands and undo work, honest about the missing model, excellent privacy text; brittle with natural phrasing; 'dnf'd klara' added a different book.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Look and feel</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Feels hand-crafted for book lovers; some developer text and low-contrast controls.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Speed reliability</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Slow search and covers, logged out once on refresh, dead reflection save, stuck active session, shrunken reader after closing a session.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Has the soul of a reader's app; reading/highlighting and session tracking still have rough edges.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Issues and fixes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Round</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Root cause</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Fix</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Verified in round</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>R2-01</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Notes highlights reviews</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>Highlights are saved but never drawn on the page text</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>Paginated mode, selected a passage, chose green; reopened the book.</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>The passage shows green highlighting.</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>Listed in the Highlights panel, but the text stays plain.</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>Highlights were stored with their text and chapter but the reflowed pages were plain strings; nothing located the saved text on a page.</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>Each page now keeps the character offsets of its text, saved highlights are found in the chapter (forgiving line breaks) and drawn in their colour, stronger on light paper.</t>
+        </is>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/flow-layout.ts, frontend/src/features/reader/FlowReaderPage.tsx</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr"/>
+      <c r="M20" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N20" s="9" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>R2-02</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>Reflowed text has no paragraph breaks and repeats each chapter title</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>Opened the novella and turned pages.</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>Proper paragraphs; title once.</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>Each chapter is one block starting 'The Last Lantern The Last Lantern Aldmere had...' under a heading saying the same.</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>EPUB extraction stripped every tag and collapsed whitespace, so &lt;title&gt; + &lt;h1&gt; + paragraphs became one run ('The Last Lantern The Last Lantern Aldmere...').</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>Body only, one paragraph per block element, entities decoded, a heading that repeats the chapter title dropped; chapter graph v4 re-indexes existing books.</t>
+        </is>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>backend/src/modules/reader/epub-indexer.ts, backend/src/modules/reader/chapter-graph.ts</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr"/>
+      <c r="M21" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N21" s="9" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>R2-03</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Assistant chat</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>'dnf'd klara' added a different book</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>'dnf'd klara, the robot pov wasnt for me' with Klara and the Sun owned.</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>Mark Klara and the Sun DNF, or ask.</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>'I've added Klāre by Otto Hinnerk to your library as Did Not Finish.'</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>'klara' covered 1 of 4 title words (score 75 &lt; 80), so it wasn't treated as the owned book and the auto-add searched the catalogue.</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>A title's opening words name it (score 88); a near match to an owned title never auto-adds a stranger's book, the tool asks instead.</t>
+        </is>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>backend/src/modules/assistant/domains/books/text/match.ts, backend/src/modules/assistant/domains/books/pipeline/planChecks.ts</t>
+        </is>
+      </c>
+      <c r="L22" s="9" t="inlineStr"/>
+      <c r="M22" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N22" s="9" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>R2-04</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Tracking journal statistics</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>Reflection 'Save' after a session does nothing</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>Reader X &gt; typed a reflection &gt; Save (x3).</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>Saves and closes.</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>Dialog stays open, no message; the reflection never reaches the Journal.</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>Save sent the end call again with a reflection; the server treated the already-ended session's new reflection as 'different data' (409) and the error was swallowed.</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>A reflection can follow the end (only when none exists); errors are shown; Save/Skip return to the book page.</t>
+        </is>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>backend/src/modules/reading-sessions/reading-sessions.service.ts, frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/reader/ReflectionPrompt.tsx</t>
+        </is>
+      </c>
+      <c r="L23" s="9" t="inlineStr"/>
+      <c r="M23" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N23" s="9" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>R2-05</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Tracking journal statistics</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>A stale reader session blocks new sessions with a developer-style error</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>Left the reader by navigating away; later 'Start a reading session' on another book.</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>Start a timer, or offer to end the old one.</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>'Another session is already active for this user' and nothing shows or ends it.</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>Leaving the reader without closing it left the session ACTIVE; the 409 text was developer wording with no way out.</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>Leaving the reader pauses its session; the clash names the book ('You're still in a reading session for ...') and offers 'Pause that one and start here'.</t>
+        </is>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/library/SessionConflict.tsx, backend/src/modules/reading-sessions/reading-sessions.service.ts</t>
+        </is>
+      </c>
+      <c r="L24" s="9" t="inlineStr"/>
+      <c r="M24" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N24" s="9" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>R2-06</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Tracking journal statistics</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>Session time includes time away from the reader</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>Left the reader open in the background, came back, closed it.</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>Only active reading time.</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>'6 min of reading' for about a minute.</t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>Duration was end minus start, including time away.</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>Sessions record paused time (pausedAt, pausedSeconds); a hidden tab pauses and resumes; the idle sweep pauses from the last page turn; paused time is subtracted.</t>
+        </is>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>backend/prisma/schema.prisma, backend/src/modules/reading-sessions/*, frontend/src/features/reader/FlowReaderPage.tsx</t>
+        </is>
+      </c>
+      <c r="L25" s="9" t="inlineStr"/>
+      <c r="M25" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N25" s="9" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>R2-07</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Tracking journal statistics</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>Journal shows a raw internal position</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>Journal after a reader session.</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>'Chapter 4, 67%'.</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>'6 min · EPUB · epubcfi(/6/2!/4/2/1:0) → ch4'</t>
+        </is>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>The journal printed stored positions (CFI, chapter ids) as-is.</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="inlineStr">
+        <is>
+          <t>Entries carry startLabel/endLabel: chapter titles (from the chapter graph, CFIs by spine step), 'p. N' for pages.</t>
+        </is>
+      </c>
+      <c r="K26" s="9" t="inlineStr">
+        <is>
+          <t>backend/src/modules/journal/journal.service.ts, frontend/src/features/journal/JournalPage.tsx</t>
+        </is>
+      </c>
+      <c r="L26" s="9" t="inlineStr"/>
+      <c r="M26" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N26" s="9" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>R2-08</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>Can't select text in the default 3D Flip mode</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>Drag-select and double-click in 3D Flip.</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>Text selects; highlight popover appears.</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>Dragging starts a page curl; only works after switching to Paginated, with no hint.</t>
+        </is>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>react-pageflip took mouse and touch input in 3D Flip mode, so a drag curled the page instead of selecting.</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="inlineStr">
+        <is>
+          <t>The flipbook no longer takes pointer input: text selects in every mode; pages turn with the buttons, arrow keys or a swipe.</t>
+        </is>
+      </c>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/FlowReaderPage.tsx</t>
+        </is>
+      </c>
+      <c r="L27" s="9" t="inlineStr"/>
+      <c r="M27" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N27" s="9" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>R2-09</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>Phone reader shows ~6 lines in a tiny inset card</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>Mobile 375x812, reader.</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>Text fills the screen.</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>Small inner card, ~6 lines per page; bookmark and View Original missing from the toolbar.</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>Pages were always A4 halves of a two-page spread, tiny on a phone; ten toolbar icons overflowed.</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="inlineStr">
+        <is>
+          <t>Below 768px one page fills the screen; Note, Translate, Music, View Original and 'Not where you left off?' move into a More menu.</t>
+        </is>
+      </c>
+      <c r="K28" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/ai/TranslatePanel.tsx</t>
+        </is>
+      </c>
+      <c r="L28" s="9" t="inlineStr"/>
+      <c r="M28" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N28" s="9" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>R2-10</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Book page and details</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>Rating and Favourite silently lost without 'Save review'</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>Clicked 5 stars and Favourite, refreshed.</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>Saved instantly or warned.</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>All empty after refresh; no 'Saved' confirmation even when saving works.</t>
+        </is>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>Stars and Favourite only changed the form; nothing saved until 'Save review'.</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="inlineStr">
+        <is>
+          <t>Rating, favourite and reread save on click with a 'Saved.' note; unsaved review text is kept.</t>
+        </is>
+      </c>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reviews/ReviewPanel.tsx</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="inlineStr"/>
+      <c r="M29" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N29" s="9" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>R2-11</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Speed reliability</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>Logged out on refresh mid-session</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>~6 min after sign-in, refreshed the reader.</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>Stay signed in.</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>Sent to /login, then landed on Library.</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>Refresh tokens rotate on every use; two refreshes with the same cookie (StrictMode's double restore, parallel 401s, several tabs reloading) made the loser look like token reuse and signed the reader out.</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="inlineStr">
+        <is>
+          <t>One refresh at a time: shared within a tab and serialised across tabs with a Web Lock; a failed refresh never clears a newer token.</t>
+        </is>
+      </c>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/lib/api/client.ts, frontend/src/lib/auth-context.tsx</t>
+        </is>
+      </c>
+      <c r="L30" s="9" t="inlineStr"/>
+      <c r="M30" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N30" s="9" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>R2-12</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>Changing font size resets to the start</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>Page 2 of 8 &gt; font +2.</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>Same passage.</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>'Page 1 of 10', back at chapter 1.</t>
+        </is>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>Re-pagination re-anchored to the chapter's first page, and the flipbook wasn't remounted at the new index.</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t>Position is chapter + character offset; after any re-layout the reader lands on the page holding that passage.</t>
+        </is>
+      </c>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/reader/flow-layout.ts</t>
+        </is>
+      </c>
+      <c r="L31" s="9" t="inlineStr"/>
+      <c r="M31" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N31" s="9" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>R2-13</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>'View Original' loses your place and has no way back</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>At 67% &gt; View Original.</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>Same position; toggle back.</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>Opens at chapter 1, 0%; no side padding, default Times; only Close.</t>
+        </is>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>The original view ignored the reading view's position (epub.js only finds an idref with '#') and had only Close.</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="inlineStr">
+        <is>
+          <t>Opens at the chapter you were on; 'Back to reading view' button.</t>
+        </is>
+      </c>
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/ReaderPage.tsx, frontend/src/features/reader/EpubReader.tsx</t>
+        </is>
+      </c>
+      <c r="L32" s="9" t="inlineStr"/>
+      <c r="M32" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N32" s="9" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>R2-14</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>Reader renders shrunken after closing a session</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>X &gt; Session ended &gt; Skip.</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>Back to the library, or a normal reader.</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>A small card mid-screen; X vs Skip inconsistent.</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>The reflection prompt replaced the reader, and Save/Skip went 'back' in history, sometimes into the reading view of the ended session.</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="inlineStr">
+        <is>
+          <t>The prompt sits over the book; both readers return to the book page afterwards.</t>
+        </is>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/reader/ReaderPage.tsx</t>
+        </is>
+      </c>
+      <c r="L33" s="9" t="inlineStr"/>
+      <c r="M33" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N33" s="9" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>R2-15</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>Pages half empty; first spread's left page blank</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>Read the first spreads on desktop.</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>Pages fill.</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>Text stops two-thirds down; next spread has one line then a new chapter.</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>Pagination estimated characters per page (deliberately conservative) and the first page was laid out as a lone 'cover'.</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>Pages are measured with the real fonts in an offscreen copy of the page (about 97% full, nothing clipped); the cover slot is used only for a real cover.</t>
+        </is>
+      </c>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/flow-layout.ts, frontend/src/features/reader/FlowReaderPage.tsx</t>
+        </is>
+      </c>
+      <c r="L34" s="9" t="inlineStr"/>
+      <c r="M34" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N34" s="9" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>R2-16</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>'mins left' estimate depends on layout</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>Changed font size, chapter list, mobile.</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>Stable estimate.</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>~32, ~40, ~68, ~50 at the same spot.</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>'mins left' was pages left x 4.</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="inlineStr">
+        <is>
+          <t>Progress and time left come from characters read (about 230 words a minute), the same at any font size.</t>
+        </is>
+      </c>
+      <c r="K35" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/reader/ReaderProgressScrubber.tsx</t>
+        </is>
+      </c>
+      <c r="L35" s="9" t="inlineStr"/>
+      <c r="M35" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N35" s="9" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>R2-17</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>Arrow keys don't turn pages</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>Right arrow in the reader.</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>Next page.</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>No keyboard handling in the reading view.</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="inlineStr">
+        <is>
+          <t>Left/Right arrows and Page Up/Down turn pages (not while typing or in a dialog).</t>
+        </is>
+      </c>
+      <c r="K36" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/FlowReaderPage.tsx</t>
+        </is>
+      </c>
+      <c r="L36" s="9" t="inlineStr"/>
+      <c r="M36" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N36" s="9" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>R2-18</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Notes highlights reviews</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>Reader highlights/notes absent from the book page; no central notes view</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>Highlight with a margin note &gt; book page.</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>Listed on the book page.</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>'Notes: No notes yet.'</t>
+        </is>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>The book page listed notes only; highlights lived in the reader.</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>'Highlights &amp; quotes' on the book page, newest first, with colour, margin note and a link back into the book. (A separate all-books notes page isn't built.)</t>
+        </is>
+      </c>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/features/notes/BookHighlights.tsx, frontend/src/features/library/BookDetailPage.tsx</t>
+        </is>
+      </c>
+      <c r="L37" s="9" t="inlineStr"/>
+      <c r="M37" s="9" t="inlineStr">
+        <is>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="N37" s="9" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>R2-19</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Assistant chat</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>Natural follow-ups and phrasing variants fail</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>'finsihed circe, 4 stars and put it on comfort reads', 'put it on comfort reads', 'put circe on comfort reads', 'actually undo that'.</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>Handled, or each simple command.</t>
+        </is>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>The same canned 'not set up' reply each time; a message typed while pending wasn't sent on Enter.</t>
+        </is>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>'put X on Y' needed the word 'shelf'; 'it' was bound to the previous turn's subject; 'actually undo that' wasn't recognised.</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="inlineStr">
+        <is>
+          <t>Shelves named without 'shelf' (and 'add X to Y' when Y is a shelf or X is theirs); 'it' is the book named in the same message; undo accepts fillers. The tester's sentence now does status, rating and shelf without a model.</t>
+        </is>
+      </c>
+      <c r="K38" s="9" t="inlineStr">
+        <is>
+          <t>backend/src/modules/assistant/domains/books/conversation/quickCommands.ts, backend/src/modules/assistant/domains/books/pipeline/preRoute.ts, backend/src/modules/assistant/domains/books/pipeline/undo.ts</t>
+        </is>
+      </c>
+      <c r="L38" s="9" t="inlineStr"/>
+      <c r="M38" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N38" s="9" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>R2-20</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Tracking journal statistics</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>No finish dates, so 'this year' can't be answered</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>Marked books Finished; asked 'how many books did i read this year'.</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>Finish dates; yearly count.</t>
+        </is>
+      </c>
+      <c r="H39" s="9" t="inlineStr">
+        <is>
+          <t>'Bunko can only tell which were this year from logged reading sessions...'</t>
+        </is>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>No completion date was stored.</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="inlineStr">
+        <is>
+          <t>UserWork.finishedAt (SRS §18.2), set when marked Finished, backfilled from the last session; shown on the book page; 'this year' uses it.</t>
+        </is>
+      </c>
+      <c r="K39" s="9" t="inlineStr">
+        <is>
+          <t>backend/prisma/schema.prisma, backend/src/modules/library/library.service.ts, backend/src/modules/assistant/domains/books/conversation/libraryAnswers.ts, frontend/src/features/library/BookDetailPage.tsx</t>
+        </is>
+      </c>
+      <c r="L39" s="9" t="inlineStr"/>
+      <c r="M39" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N39" s="9" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>R2-21</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Library adding finding books</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>Book search slow and typo-intolerant</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>'tomorow and tomorrow and tomorrow'.</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>Right book within a couple of seconds.</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>10-15s spinner, unrelated results.</t>
+        </is>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>Catalogue providers are slow on a cold query and have no fuzzy matching; results are cached for an hour after the first search.</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="inlineStr">
+        <is>
+          <t>Not changed this round (needs a provider-side change).</t>
+        </is>
+      </c>
+      <c r="K40" s="9" t="inlineStr"/>
+      <c r="L40" s="9" t="inlineStr"/>
+      <c r="M40" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N40" s="9" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>R2-22</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>Library adding finding books</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>Status doesn't follow reading; no progress shown</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>Read to 67%, back to Library.</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>Status Reading; progress on the card.</t>
+        </is>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>Still Want to Read; no progress; 'Continue Reading' before ever opening.</t>
+        </is>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>Opening a book never changed its status; the button always said 'Continue Reading'.</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="inlineStr">
+        <is>
+          <t>Starting or logging a session moves Want to Read to Reading (never Finished/DNF); 'Start reading' until the first session. (Progress on cards not built.)</t>
+        </is>
+      </c>
+      <c r="K41" s="9" t="inlineStr">
+        <is>
+          <t>backend/src/modules/library/library.service.ts, backend/src/modules/reading-sessions/reading-sessions.service.ts, frontend/src/features/library/ContinueReadingButton.tsx</t>
+        </is>
+      </c>
+      <c r="L41" s="9" t="inlineStr"/>
+      <c r="M41" s="9" t="inlineStr">
+        <is>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="N41" s="9" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>R2-23</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Tracking journal statistics</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>Languages 'Unknown 6' and lowercase 'english'; EPUB reading added no pages</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>Statistics &gt; Languages.</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="inlineStr">
+        <is>
+          <t>'English'; EPUB pages counted.</t>
+        </is>
+      </c>
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t>'Unknown 6 books', 'english 1 book'; pages read only from the manual log.</t>
+        </is>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>The page passed language names through Intl.DisplayNames, which reads 'english' as a valid code and returns it lowercased; books with no language said 'Unknown'.</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="inlineStr">
+        <is>
+          <t>Only codes are looked up, names are capitalised; missing language reads 'Not recorded'. (EPUB pages need a start position; unchanged.)</t>
+        </is>
+      </c>
+      <c r="K42" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/features/statistics/chart-format.ts, frontend/src/features/statistics/StatisticsPage.tsx</t>
+        </is>
+      </c>
+      <c r="L42" s="9" t="inlineStr"/>
+      <c r="M42" s="9" t="inlineStr">
+        <is>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="N42" s="9" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>R2-24</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Shelves organizing</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>An empty shelf offers no way to add books</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>New shelf '2026 faves'.</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>An 'Add books' picker.</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>Text only, no button.</t>
+        </is>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>No way to add books from a shelf.</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="inlineStr">
+        <is>
+          <t>'Add books' on custom shelves and in the empty state: a searchable picker of library books.</t>
+        </is>
+      </c>
+      <c r="K43" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/features/shelves/AddToShelfDialog.tsx, frontend/src/features/shelves/ShelvesPage.tsx</t>
+        </is>
+      </c>
+      <c r="L43" s="9" t="inlineStr"/>
+      <c r="M43" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N43" s="9" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>R2-25</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>Shelves organizing</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>polish</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>Low-contrast toggle and unlabeled shelf tabs</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>Shelves page.</t>
+        </is>
+      </c>
+      <c r="G44" s="9" t="inlineStr">
+        <is>
+          <t>Readable toggle; named tabs.</t>
+        </is>
+      </c>
+      <c r="H44" s="9" t="inlineStr">
+        <is>
+          <t>'Covers' dark brown on near-black; tabs read as unnamed buttons; odd brown scrollbar strip.</t>
+        </is>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>Inactive toggle text at 70% opacity on near-black; dark wood scrollbar on the paper background.</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="inlineStr">
+        <is>
+          <t>Full-strength toggle text; shelf tabs say their name and count and report pressed state; light paper scrollbar.</t>
+        </is>
+      </c>
+      <c r="K44" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/features/shelves/ShelvesPage.tsx, frontend/src/index.css</t>
+        </is>
+      </c>
+      <c r="L44" s="9" t="inlineStr"/>
+      <c r="M44" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N44" s="9" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>R2-26</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>Tracking journal statistics</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>polish</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>Journal order wrong; entries can't be edited</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>Logged a session after another the same day.</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>Newest first; edit/delete.</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="inlineStr">
+        <is>
+          <t>Newer entry below the older; clicking opens the book.</t>
+        </is>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>Journal sorted by start time, so a session logged after the fact sorted by when it began.</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="inlineStr">
+        <is>
+          <t>Sorted by when sessions ended. (Editing an entry isn't built.)</t>
+        </is>
+      </c>
+      <c r="K45" s="9" t="inlineStr">
+        <is>
+          <t>backend/src/modules/journal/journal.service.ts</t>
+        </is>
+      </c>
+      <c r="L45" s="9" t="inlineStr"/>
+      <c r="M45" s="9" t="inlineStr">
+        <is>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="N45" s="9" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>R2-27</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>Book page and details</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>polish</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>Duplicate status, marketing-blurb synopsis, small icon issues</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>Book pages and reader toolbar.</t>
+        </is>
+      </c>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>One status control, clean synopsis, labelled icons.</t>
+        </is>
+      </c>
+      <c r="H46" s="9" t="inlineStr">
+        <is>
+          <t>Pill plus dropdown; synopsis starts with press quotes; unlabeled icon; bookmark icon never fills.</t>
+        </is>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>Status showed as a pill and a dropdown; catalogue copy opens with press quotes; bookmark icon never reflected state.</t>
+        </is>
+      </c>
+      <c r="J46" s="9" t="inlineStr">
+        <is>
+          <t>One labelled status control; leading press quotes and ALL-CAPS banners trimmed for display; the bookmark fills when the chapter is bookmarked.</t>
+        </is>
+      </c>
+      <c r="K46" s="9" t="inlineStr">
+        <is>
+          <t>frontend/src/features/library/BookDetailPage.tsx, frontend/src/features/library/synopsis.ts, frontend/src/features/reader/FlowReaderPage.tsx</t>
+        </is>
+      </c>
+      <c r="L46" s="9" t="inlineStr"/>
+      <c r="M46" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N46" s="9" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>R2-28</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>First impression onboarding</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>polish</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>No import or account basics for switchers</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>Welcome screen and Settings.</t>
+        </is>
+      </c>
+      <c r="G47" s="9" t="inlineStr">
+        <is>
+          <t>Import, yearly goal, export, change password.</t>
+        </is>
+      </c>
+      <c r="H47" s="9" t="inlineStr">
+        <is>
+          <t>None present.</t>
+        </is>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>Import (SRS §37), reading goals, export and password change aren't in the MVP scope.</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="inlineStr">
+        <is>
+          <t>Not built; needs product approval.</t>
+        </is>
+      </c>
+      <c r="K47" s="9" t="inlineStr"/>
+      <c r="L47" s="9" t="inlineStr"/>
+      <c r="M47" s="9" t="inlineStr">
+        <is>
+          <t>Won't fix (needs approval)</t>
+        </is>
+      </c>
+      <c r="N47" s="9" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>What the tester liked</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Feels made by people who love books: the wooden bookcase with genre rows, the sepia reader with a warmth slider, serif headings, 'Session ended... Nice work.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Plain, excellent privacy wording around AI (translation and the assistant).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Manual 'Log reading' is great: current read first, page-order validation, a clear confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Adding a book flows well: the status choice is part of adding, then 'Add a copy'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>The assistant does what it can reliably and reversibly, with a working undo.</t>
         </is>
       </c>
     </row>

--- a/docs/qa/blackbox-test-log.xlsx
+++ b/docs/qa/blackbox-test-log.xlsx
@@ -11,9 +11,10 @@
     <sheet name="All issues" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Round 1" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Round 2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Round 3" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All issues'!$A$1:$N$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All issues'!$A$1:$N$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -93,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -104,6 +105,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -486,12 +490,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -517,6 +522,11 @@
           <t>Round 2</t>
         </is>
       </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Round 3</t>
+        </is>
+      </c>
     </row>
     <row r="4"/>
     <row r="5">
@@ -531,6 +541,9 @@
       <c r="C5" s="5" t="n">
         <v>8</v>
       </c>
+      <c r="D5" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -544,6 +557,9 @@
       <c r="C6" s="4" t="n">
         <v>7</v>
       </c>
+      <c r="D6" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -557,6 +573,9 @@
       <c r="C7" s="4" t="n">
         <v>6</v>
       </c>
+      <c r="D7" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -570,6 +589,11 @@
       <c r="C8" s="4" t="n">
         <v>5</v>
       </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>not tested</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -583,6 +607,9 @@
       <c r="C9" s="4" t="n">
         <v>6</v>
       </c>
+      <c r="D9" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -596,6 +623,9 @@
       <c r="C10" s="4" t="n">
         <v>7</v>
       </c>
+      <c r="D10" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -609,6 +639,9 @@
       <c r="C11" s="4" t="n">
         <v>5</v>
       </c>
+      <c r="D11" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -622,6 +655,9 @@
       <c r="C12" s="4" t="n">
         <v>6</v>
       </c>
+      <c r="D12" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -635,6 +671,9 @@
       <c r="C13" s="5" t="n">
         <v>8</v>
       </c>
+      <c r="D13" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -648,6 +687,9 @@
       <c r="C14" s="4" t="n">
         <v>5</v>
       </c>
+      <c r="D14" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -661,9 +703,12 @@
       <c r="C15" s="4" t="n">
         <v>6</v>
       </c>
+      <c r="D15" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>Lowest score</t>
         </is>
@@ -674,9 +719,12 @@
       <c r="C16" s="3" t="n">
         <v>5</v>
       </c>
+      <c r="D16" s="3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Issues reported</t>
         </is>
@@ -687,9 +735,12 @@
       <c r="C17" s="3" t="n">
         <v>28</v>
       </c>
+      <c r="D17" s="3" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>Issues fixed</t>
         </is>
@@ -700,28 +751,43 @@
       <c r="C18" s="3" t="n">
         <v>22</v>
       </c>
+      <c r="D18" s="3" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Round 1 (2026-10-23)</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>Local: frontend :5174, API :3100 with AI_PROVIDER=nvidia but no NVIDIA_API_KEY yet; Claude ai-service not running. Seeded account with 6 books (one sample EPUB).</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Round 2 (2026-10-23)</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>Local: frontend :5174, API :3100; assistant model not configured (no NVIDIA_API_KEY), tester told so. Fresh seeded account with an original 5-chapter EPUB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Round 3 (2026-10-23)</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Local: frontend :5174, API :3100; assistant model not configured (no NVIDIA_API_KEY). The seeded account's password reached the tester in a follow-up message, which its safety check refused to type, so it tested with a fresh account that had no EPUB: the reader was not tested this round.</t>
         </is>
       </c>
     </row>
@@ -736,7 +802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -829,2789 +895,3715 @@
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="9" t="n">
+      <c r="A3" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>R1-01</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>Reading experience</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>blocker</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>No way to open the digital reader, even for a book with an EPUB</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>Library &gt; 'A Bunko Sample Book' &gt; 'Open Digital Reader'; clicked the EPUB edition row; tried status Reading, reload, and 'Start / Resume Reading Session'.</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>The EPUB opens in the reader.</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>Every path lands on the book details page; the EPUB edition row has no read button.</t>
         </is>
       </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="I3" s="10" t="inlineStr">
         <is>
           <t>QA seed attached the EPUB with the upload id instead of the stored file id, so no copy existed; and the app gave a digital edition without its file no way forward.</t>
         </is>
       </c>
-      <c r="J3" s="9" t="inlineStr">
+      <c r="J3" s="10" t="inlineStr">
         <is>
           <t>Seed fixed (uses the id /files/:id/confirm returns) and now ships an original 5-chapter novella. A digital edition with no file shows 'Upload file'; the quick-action modal only offers actions that work.</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="K3" s="10" t="inlineStr">
         <is>
           <t>backend/scripts/seed-qa-reader.ts, backend/scripts/qa-sample-book.ts, frontend/src/features/library/BookDetailPage.tsx, frontend/src/features/library/AddEditionDialog.tsx, frontend/src/features/library/BookQuickActionModal.tsx</t>
         </is>
       </c>
-      <c r="L3" s="9" t="inlineStr"/>
-      <c r="M3" s="9" t="inlineStr">
+      <c r="L3" s="10" t="inlineStr"/>
+      <c r="M3" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N3" s="9" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="n">
+      <c r="A4" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>R1-02</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Library adding finding books</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Most covers are for completely different books</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>Open Library (also Shelves, modal, book page).</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>The real cover for each book.</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>The Left Hand of Darkness and the sample book show 'Their Eyes Were Watching God'; Circe, Piranesi and Klara show unrelated books; a hand-added zine got a random cover. There's no way to change or remove a cover.</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t>Three code paths took the first search result with any cover regardless of title; the seed also used guessed cover ids. Wikidata series discovery filed books under their own title.</t>
         </is>
       </c>
-      <c r="J4" s="9" t="inlineStr">
+      <c r="J4" s="10" t="inlineStr">
         <is>
           <t>Covers only from a result with the same main title and a shared author surname (pickMatchingCover), looked up in the background; self-named series ignored and cleared. Changing/removing a cover by hand is not built yet (covers live on the shared catalogue entry).</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="10" t="inlineStr">
         <is>
           <t>backend/src/modules/library/library.service.ts, backend/scripts/seed-qa-reader.ts</t>
         </is>
       </c>
-      <c r="L4" s="9" t="inlineStr"/>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="L4" s="10" t="inlineStr"/>
+      <c r="M4" s="10" t="inlineStr">
         <is>
           <t>Partly fixed</t>
         </is>
       </c>
-      <c r="N4" s="9" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="n">
+      <c r="A5" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>R1-03</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Assistant chat</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>Many assistant messages fail with a generic error</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>'no i meant the zevin one...', 'I started Tomorrow, and Tomorrow, and Tomorrow' (the app's own example), 'ok i started the first one. and dnf'd circe tbh', 'and add it to my comfort reads shelf', 'rate it 5 stars actually'.</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>The change is made, or a clarifying question.</t>
         </is>
       </c>
-      <c r="H5" s="9" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>'An unexpected error occurred' each time, no reason, no retry. Short single-book commands worked.</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="I5" s="10" t="inlineStr">
         <is>
           <t>No NVIDIA key on the test server: NIM's 401 became a plain Error and surfaced as a 500. Separately, titles with commas, filler words ('ok', 'and', 'tbh', 'actually') and 'it' defeated the fast paths, so those messages needed the model.</t>
         </is>
       </c>
-      <c r="J5" s="9" t="inlineStr">
+      <c r="J5" s="10" t="inlineStr">
         <is>
           <t>Rejected key / rate limit are 'unavailable'; a missing key is detected at startup and answered with a plain message; any other failure is a friendly logged reply. Owned titles with commas are masked before clause splitting; filler words stripped.</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="K5" s="10" t="inlineStr">
         <is>
           <t>backend/src/modules/assistant/clients/NvidiaNimClient.ts, backend/src/modules/assistant/aiController.ts, backend/src/modules/assistant/domains/books/conversation/quickCommands.ts</t>
         </is>
       </c>
-      <c r="L5" s="9" t="inlineStr"/>
-      <c r="M5" s="9" t="inlineStr">
+      <c r="L5" s="10" t="inlineStr"/>
+      <c r="M5" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N5" s="9" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="n">
+      <c r="A6" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>R1-04</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Assistant chat</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>A typo in an owned title makes it search the catalogue for junk</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>'started tomorow and tomorrow last night, its so good already' (the book is in the library).</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>It matches the owned book.</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>"I couldn't find a book called \"tomorow\". The closest were \"Notes on the History of Fort George\"..."</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>Title matching needed exact words; the list splitter split 'tomorow and tomorrow' into two books.</t>
         </is>
       </c>
-      <c r="J6" s="9" t="inlineStr">
+      <c r="J6" s="10" t="inlineStr">
         <is>
           <t>Typo-tolerant word matching on owned titles; lists split only into books the reader owns.</t>
         </is>
       </c>
-      <c r="K6" s="9" t="inlineStr">
+      <c r="K6" s="10" t="inlineStr">
         <is>
           <t>backend/src/modules/assistant/domains/books/text/match.ts, backend/src/modules/assistant/domains/books/conversation/quickCommands.ts</t>
         </is>
       </c>
-      <c r="L6" s="9" t="inlineStr"/>
-      <c r="M6" s="9" t="inlineStr">
+      <c r="L6" s="10" t="inlineStr"/>
+      <c r="M6" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N6" s="9" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="n">
+      <c r="A7" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>R1-05</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Assistant chat</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>Recommendations made up a sequel and ignored 'something like Piranesi'</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>'what should i read next? something like piranesi'</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>Books like Piranesi, and accurate facts.</t>
         </is>
       </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>Listed the Want to Read list only, and said 'the series continues with Dune II by Frank Herbert' (no such book).</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>The 'series continues' line came from a Wikidata lookup that returned non-books ('Dune II'); 'like X' wasn't used.</t>
         </is>
       </c>
-      <c r="J7" s="9" t="inlineStr">
+      <c r="J7" s="10" t="inlineStr">
         <is>
           <t>Series continuation removed; 'something like X' ranks the list by X's authors and genres with reasons, and asks the model for books beyond the list.</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="K7" s="10" t="inlineStr">
         <is>
           <t>backend/src/modules/assistant/domains/books/actions/readTools.ts, backend/src/modules/assistant/domains/books/pipeline/preRoute.ts, backend/src/modules/assistant/domains/books/prompts/answerPrompt.ts</t>
         </is>
       </c>
-      <c r="L7" s="9" t="inlineStr"/>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="L7" s="10" t="inlineStr"/>
+      <c r="M7" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N7" s="9" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="n">
+      <c r="A8" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>R1-06</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Tracking journal statistics</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>Journal entries don't say which book</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>Piranesi &gt; physical edition &gt; session &gt; end with 'p 112' and a reflection &gt; Journal.</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>Entry shows the book, page and time, and links to it.</t>
         </is>
       </c>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>'Oct 23, 2026 · 0 min · “the other is kinda sus now”': no title, no page, not clickable; no way to add an entry from the Journal.</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>Journal entries carried no book.</t>
         </is>
       </c>
-      <c r="J8" s="9" t="inlineStr">
+      <c r="J8" s="10" t="inlineStr">
         <is>
           <t>Each entry names and links its book with its cover and format; 'Log reading' on the Journal.</t>
         </is>
       </c>
-      <c r="K8" s="9" t="inlineStr">
+      <c r="K8" s="10" t="inlineStr">
         <is>
           <t>backend/src/modules/journal/journal.service.ts, frontend/src/features/journal/JournalPage.tsx</t>
         </is>
       </c>
-      <c r="L8" s="9" t="inlineStr"/>
-      <c r="M8" s="9" t="inlineStr">
+      <c r="L8" s="10" t="inlineStr"/>
+      <c r="M8" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N8" s="9" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="n">
+      <c r="A9" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>R1-07</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Tracking journal statistics</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>Reading can only be logged live, and pages aren't counted</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>Started and immediately ended a session with 'p 112'.</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>Log a past session (time, date, page), and pages count.</t>
         </is>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>'Session saved — 0 min. Nice reading.' Stats: 'Pages read 0'. No manual duration/date, no progress on the book, no finish date.</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>Only live timed sessions existed; a physical session with only an end page can't count pages.</t>
         </is>
       </c>
-      <c r="J9" s="9" t="inlineStr">
+      <c r="J9" s="10" t="inlineStr">
         <is>
           <t>POST /reading-sessions/log and a 'Log reading' form (book, day, minutes, from/to page, reflection) on the Journal and book page; both pages make them count.</t>
         </is>
       </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="K9" s="10" t="inlineStr">
         <is>
           <t>backend/src/modules/reading-sessions/*, frontend/src/features/journal/LogSessionDialog.tsx</t>
         </is>
       </c>
-      <c r="L9" s="9" t="inlineStr"/>
-      <c r="M9" s="9" t="inlineStr">
+      <c r="L9" s="10" t="inlineStr"/>
+      <c r="M9" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N9" s="9" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="n">
+      <c r="A10" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>R1-08</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Book page and details</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>Modal buttons silently do nothing without a matching edition</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>Circe (no editions) &gt; 'Start / Resume Reading Session'; Piranesi (physical only) &gt; 'Open Digital Reader'.</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>Hidden, disabled, or explained.</t>
         </is>
       </c>
-      <c r="H10" s="9" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>Both silently go to the book page.</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>Modal buttons fell back to navigating to the book page.</t>
         </is>
       </c>
-      <c r="J10" s="9" t="inlineStr">
+      <c r="J10" s="10" t="inlineStr">
         <is>
           <t>Modal shows only working actions and explains/offers to add a copy otherwise.</t>
         </is>
       </c>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="K10" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/library/BookQuickActionModal.tsx</t>
         </is>
       </c>
-      <c r="L10" s="9" t="inlineStr"/>
-      <c r="M10" s="9" t="inlineStr">
+      <c r="L10" s="10" t="inlineStr"/>
+      <c r="M10" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N10" s="9" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="n">
+      <c r="A11" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>R1-09</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>Tracking journal statistics</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>Statistics contradict themselves; language data messy</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>Statistics &gt; Daily.</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Consistent numbers.</t>
         </is>
       </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>Summary counts 1 session while the chart says 'No reading sessions in this period yet'; languages 'Unknown 6' and lowercase 'english 2'; 'Bunko' listed as an author.</t>
         </is>
       </c>
-      <c r="I11" s="9" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>The chart's empty state keyed on minutes, not sessions; language labels weren't normalised.</t>
         </is>
       </c>
-      <c r="J11" s="9" t="inlineStr">
+      <c r="J11" s="10" t="inlineStr">
         <is>
           <t>Chart distinguishes 'no sessions' from 'sessions under a minute'; languages shown as names. ('Bunko' as author was seed data; reading goals aren't in the SRS.)</t>
         </is>
       </c>
-      <c r="K11" s="9" t="inlineStr">
+      <c r="K11" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/statistics/ActivityChart.tsx, backend/src/modules/statistics/statistics.service.ts</t>
         </is>
       </c>
-      <c r="L11" s="9" t="inlineStr"/>
-      <c r="M11" s="9" t="inlineStr">
+      <c r="L11" s="10" t="inlineStr"/>
+      <c r="M11" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N11" s="9" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="n">
+      <c r="A12" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>R1-10</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>Library adding finding books</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>Catalogue search isn't typo-tolerant and is slow; no status on add</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>Add a book &gt; 'tomorow and tomorrow and tomorrow'.</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>The right book near the top.</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>After 6-8s: unrelated results. Confusing language chips; manual form lacks page count/cover; always added as Want to Read.</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>Google Books answered first with poor relevance; the universe check could hijack results; no caching; original language defaulted to 'Japanese'.</t>
         </is>
       </c>
-      <c r="J12" s="9" t="inlineStr">
+      <c r="J12" s="10" t="inlineStr">
         <is>
           <t>Open Library title search merged in; results ranked by title match; universe check only for named universes; searches cached an hour; choose Want to read / Reading now / Already read when adding; calm metadata line replaces off-palette chips. (Catalogue-side typo tolerance depends on the providers.)</t>
         </is>
       </c>
-      <c r="K12" s="9" t="inlineStr">
+      <c r="K12" s="10" t="inlineStr">
         <is>
           <t>backend/src/modules/metadata/metadata.service.ts, frontend/src/features/library/AddBookDialog.tsx</t>
         </is>
       </c>
-      <c r="L12" s="9" t="inlineStr"/>
-      <c r="M12" s="9" t="inlineStr">
+      <c r="L12" s="10" t="inlineStr"/>
+      <c r="M12" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N12" s="9" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="n">
+      <c r="A13" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>R1-11</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>Library adding finding books</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>'Remove from library' gave no visible response</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>Book page &gt; 'Remove from library'.</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>A confirmation, then the book is gone.</t>
         </is>
       </c>
-      <c r="H13" s="9" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>Nothing visible; the book stayed.</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>Used the browser's native confirm(), which the tester never saw.</t>
         </is>
       </c>
-      <c r="J13" s="9" t="inlineStr">
+      <c r="J13" s="10" t="inlineStr">
         <is>
           <t>In-app confirmation dialog that says what's kept.</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K13" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/library/BookDetailPage.tsx</t>
         </is>
       </c>
-      <c r="L13" s="9" t="inlineStr"/>
-      <c r="M13" s="9" t="inlineStr">
+      <c r="L13" s="10" t="inlineStr"/>
+      <c r="M13" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N13" s="9" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="n">
+      <c r="A14" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>R1-12</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>Shelves organizing</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>Odd shelf grouping, per-row scrollbars, inverted toggle</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>Shelves &gt; All Volumes; Covers/Spines toggle; mobile.</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>Books share shelves; the active view is clear.</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>One book per tall row under its own title; every row has a scrollbar; the active toggle option is the dim one; the choice doesn't stick; arrows cover art on mobile.</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>Rows per one-book series/genre; overflow-x-auto made rows scroll vertically; active toggle was the dark pill; arrows forced visible on mobile.</t>
         </is>
       </c>
-      <c r="J14" s="9" t="inlineStr">
+      <c r="J14" s="10" t="inlineStr">
         <is>
           <t>Rows need two books; overflow-y hidden with a thin themed scrollbar; light active pill with aria-pressed, remembered; arrows on focus/hover only.</t>
         </is>
       </c>
-      <c r="K14" s="9" t="inlineStr">
+      <c r="K14" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/shelves/*</t>
         </is>
       </c>
-      <c r="L14" s="9" t="inlineStr"/>
-      <c r="M14" s="9" t="inlineStr">
+      <c r="L14" s="10" t="inlineStr"/>
+      <c r="M14" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N14" s="9" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="n">
+      <c r="A15" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>R1-13</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>Speed reliability</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>Slow loads with little feedback</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>Library, Shelves, book pages; status dropdown.</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>Fast, with placeholders.</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>Covers blank for 3-5s on every visit; a big modal spinner; status change ~3s while the old value still shows.</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>Opening a book ran series discovery and a cover search synchronously (2-3s); covers had no placeholder; status change waited for the server.</t>
         </is>
       </c>
-      <c r="J15" s="9" t="inlineStr">
+      <c r="J15" s="10" t="inlineStr">
         <is>
           <t>Both moved to the background (book fetch ~72 ms); lazy covers on a paper tint; skeleton in the modal; optimistic status updates.</t>
         </is>
       </c>
-      <c r="K15" s="9" t="inlineStr">
+      <c r="K15" s="10" t="inlineStr">
         <is>
           <t>backend/src/modules/library/library.service.ts, frontend/src/features/library/BookCover.tsx, frontend/src/lib/api/works.ts</t>
         </is>
       </c>
-      <c r="L15" s="9" t="inlineStr"/>
-      <c r="M15" s="9" t="inlineStr">
+      <c r="L15" s="10" t="inlineStr"/>
+      <c r="M15" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N15" s="9" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="n">
+      <c r="A16" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>R1-14</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>Notes highlights reviews</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>Reviews and notes are basic</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>Rated, reviewed, added and edited a note.</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>Half stars, dated notes, spoiler/private options.</t>
         </is>
       </c>
-      <c r="H16" s="9" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>Whole stars only; notes undated with only a 'Book' tag; highlights impossible (R1-01).</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>Notes showed no date; ratings are whole stars by SRS §14.</t>
         </is>
       </c>
-      <c r="J16" s="9" t="inlineStr">
+      <c r="J16" s="10" t="inlineStr">
         <is>
           <t>Notes show their date (and position); the review box says reviews and notes are private. Half stars not added: SRS §14 sets whole 5-star ratings.</t>
         </is>
       </c>
-      <c r="K16" s="9" t="inlineStr">
+      <c r="K16" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/notes/NotesPanel.tsx, frontend/src/features/reviews/ReviewPanel.tsx</t>
         </is>
       </c>
-      <c r="L16" s="9" t="inlineStr"/>
-      <c r="M16" s="9" t="inlineStr">
+      <c r="L16" s="10" t="inlineStr"/>
+      <c r="M16" s="10" t="inlineStr">
         <is>
           <t>Partly fixed</t>
         </is>
       </c>
-      <c r="N16" s="9" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="n">
+      <c r="A17" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>R1-15</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>Assistant chat</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>polish</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>Odd reply after declining a follow-up</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>'rate piranesi 5 stars' &gt; asked to mark Finished &gt; 'nah not yet'.</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>'Okay, I'll leave it as Reading.'</t>
         </is>
       </c>
-      <c r="H17" s="9" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>'Okay, I kept Piranesi.' (sounds like it nearly removed it).</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>The decline message was the generic 'Okay, I kept X.'</t>
         </is>
       </c>
-      <c r="J17" s="9" t="inlineStr">
+      <c r="J17" s="10" t="inlineStr">
         <is>
           <t>Follow-up offers can say what 'no' means (general core hook): 'Okay, Piranesi stays as Reading.'</t>
         </is>
       </c>
-      <c r="K17" s="9" t="inlineStr">
+      <c r="K17" s="10" t="inlineStr">
         <is>
           <t>backend/src/modules/assistant/domain/DomainPack.ts, backend/src/modules/assistant/AIRuntime.ts, backend/src/modules/assistant/domains/books/pipeline/replies.ts</t>
         </is>
       </c>
-      <c r="L17" s="9" t="inlineStr"/>
-      <c r="M17" s="9" t="inlineStr">
+      <c r="L17" s="10" t="inlineStr"/>
+      <c r="M17" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N17" s="9" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="n">
+      <c r="A18" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>R1-16</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>First impression onboarding</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>polish</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>No forgot-password, no import of an existing history</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>Login and register pages; Settings.</t>
         </is>
       </c>
-      <c r="G18" s="9" t="inlineStr">
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>Forgot password; Goodreads/StoryGraph import.</t>
         </is>
       </c>
-      <c r="H18" s="9" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>Neither exists.</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr">
         <is>
           <t>Password reset needs email delivery (none configured); importing other platforms is SRS §37, which needs product approval.</t>
         </is>
       </c>
-      <c r="J18" s="9" t="inlineStr">
+      <c r="J18" s="10" t="inlineStr">
         <is>
           <t>Not built. A first-run welcome now explains the three ways to start (add, read/log, assistant).</t>
         </is>
       </c>
-      <c r="K18" s="9" t="inlineStr">
+      <c r="K18" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/library/LibraryPage.tsx</t>
         </is>
       </c>
-      <c r="L18" s="9" t="inlineStr"/>
-      <c r="M18" s="9" t="inlineStr">
+      <c r="L18" s="10" t="inlineStr"/>
+      <c r="M18" s="10" t="inlineStr">
         <is>
           <t>Won't fix (needs approval)</t>
         </is>
       </c>
-      <c r="N18" s="9" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="n">
+      <c r="A19" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>R1-17</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>Look and feel</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>polish</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>Sidebar scrolls away on long pages</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>Scrolled a long book page on desktop.</t>
         </is>
       </c>
-      <c r="G19" s="9" t="inlineStr">
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>Navigation and Sign out stay in reach.</t>
         </is>
       </c>
-      <c r="H19" s="9" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>The sidebar scrolls with the content.</t>
         </is>
       </c>
-      <c r="I19" s="9" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>Sidebar wasn't sticky.</t>
         </is>
       </c>
-      <c r="J19" s="9" t="inlineStr">
+      <c r="J19" s="10" t="inlineStr">
         <is>
           <t>Sticky full-height sidebar on desktop.</t>
         </is>
       </c>
-      <c r="K19" s="9" t="inlineStr">
+      <c r="K19" s="10" t="inlineStr">
         <is>
           <t>frontend/src/components/layout/AppShell.tsx</t>
         </is>
       </c>
-      <c r="L19" s="9" t="inlineStr"/>
-      <c r="M19" s="9" t="inlineStr">
+      <c r="L19" s="10" t="inlineStr"/>
+      <c r="M19" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N19" s="9" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="n">
+      <c r="A20" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>R2-01</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>Notes highlights reviews</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>Highlights are saved but never drawn on the page text</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>Paginated mode, selected a passage, chose green; reopened the book.</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>The passage shows green highlighting.</t>
         </is>
       </c>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>Listed in the Highlights panel, but the text stays plain.</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>Highlights were stored with their text and chapter but the reflowed pages were plain strings; nothing located the saved text on a page.</t>
         </is>
       </c>
-      <c r="J20" s="9" t="inlineStr">
+      <c r="J20" s="10" t="inlineStr">
         <is>
           <t>Each page now keeps the character offsets of its text, saved highlights are found in the chapter (forgiving line breaks) and drawn in their colour, stronger on light paper.</t>
         </is>
       </c>
-      <c r="K20" s="9" t="inlineStr">
+      <c r="K20" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/reader/flow-layout.ts, frontend/src/features/reader/FlowReaderPage.tsx</t>
         </is>
       </c>
-      <c r="L20" s="9" t="inlineStr"/>
-      <c r="M20" s="9" t="inlineStr">
+      <c r="L20" s="10" t="inlineStr"/>
+      <c r="M20" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N20" s="9" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="n">
+      <c r="A21" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>R2-02</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>Reading experience</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>Reflowed text has no paragraph breaks and repeats each chapter title</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>Opened the novella and turned pages.</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>Proper paragraphs; title once.</t>
         </is>
       </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>Each chapter is one block starting 'The Last Lantern The Last Lantern Aldmere had...' under a heading saying the same.</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>EPUB extraction stripped every tag and collapsed whitespace, so &lt;title&gt; + &lt;h1&gt; + paragraphs became one run ('The Last Lantern The Last Lantern Aldmere...').</t>
         </is>
       </c>
-      <c r="J21" s="9" t="inlineStr">
+      <c r="J21" s="10" t="inlineStr">
         <is>
           <t>Body only, one paragraph per block element, entities decoded, a heading that repeats the chapter title dropped; chapter graph v4 re-indexes existing books.</t>
         </is>
       </c>
-      <c r="K21" s="9" t="inlineStr">
+      <c r="K21" s="10" t="inlineStr">
         <is>
           <t>backend/src/modules/reader/epub-indexer.ts, backend/src/modules/reader/chapter-graph.ts</t>
         </is>
       </c>
-      <c r="L21" s="9" t="inlineStr"/>
-      <c r="M21" s="9" t="inlineStr">
+      <c r="L21" s="10" t="inlineStr"/>
+      <c r="M21" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N21" s="9" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="n">
+      <c r="A22" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>R2-03</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>Assistant chat</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>'dnf'd klara' added a different book</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F22" s="10" t="inlineStr">
         <is>
           <t>'dnf'd klara, the robot pov wasnt for me' with Klara and the Sun owned.</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>Mark Klara and the Sun DNF, or ask.</t>
         </is>
       </c>
-      <c r="H22" s="9" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>'I've added Klāre by Otto Hinnerk to your library as Did Not Finish.'</t>
         </is>
       </c>
-      <c r="I22" s="9" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>'klara' covered 1 of 4 title words (score 75 &lt; 80), so it wasn't treated as the owned book and the auto-add searched the catalogue.</t>
         </is>
       </c>
-      <c r="J22" s="9" t="inlineStr">
+      <c r="J22" s="10" t="inlineStr">
         <is>
           <t>A title's opening words name it (score 88); a near match to an owned title never auto-adds a stranger's book, the tool asks instead.</t>
         </is>
       </c>
-      <c r="K22" s="9" t="inlineStr">
+      <c r="K22" s="10" t="inlineStr">
         <is>
           <t>backend/src/modules/assistant/domains/books/text/match.ts, backend/src/modules/assistant/domains/books/pipeline/planChecks.ts</t>
         </is>
       </c>
-      <c r="L22" s="9" t="inlineStr"/>
-      <c r="M22" s="9" t="inlineStr">
+      <c r="L22" s="10" t="inlineStr"/>
+      <c r="M22" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N22" s="9" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="n">
+      <c r="A23" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>R2-04</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>Tracking journal statistics</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E23" s="10" t="inlineStr">
         <is>
           <t>Reflection 'Save' after a session does nothing</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F23" s="10" t="inlineStr">
         <is>
           <t>Reader X &gt; typed a reflection &gt; Save (x3).</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>Saves and closes.</t>
         </is>
       </c>
-      <c r="H23" s="9" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>Dialog stays open, no message; the reflection never reaches the Journal.</t>
         </is>
       </c>
-      <c r="I23" s="9" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>Save sent the end call again with a reflection; the server treated the already-ended session's new reflection as 'different data' (409) and the error was swallowed.</t>
         </is>
       </c>
-      <c r="J23" s="9" t="inlineStr">
+      <c r="J23" s="10" t="inlineStr">
         <is>
           <t>A reflection can follow the end (only when none exists); errors are shown; Save/Skip return to the book page.</t>
         </is>
       </c>
-      <c r="K23" s="9" t="inlineStr">
+      <c r="K23" s="10" t="inlineStr">
         <is>
           <t>backend/src/modules/reading-sessions/reading-sessions.service.ts, frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/reader/ReflectionPrompt.tsx</t>
         </is>
       </c>
-      <c r="L23" s="9" t="inlineStr"/>
-      <c r="M23" s="9" t="inlineStr">
+      <c r="L23" s="10" t="inlineStr"/>
+      <c r="M23" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N23" s="9" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="n">
+      <c r="A24" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>R2-05</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>Tracking journal statistics</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>A stale reader session blocks new sessions with a developer-style error</t>
         </is>
       </c>
-      <c r="F24" s="9" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>Left the reader by navigating away; later 'Start a reading session' on another book.</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>Start a timer, or offer to end the old one.</t>
         </is>
       </c>
-      <c r="H24" s="9" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>'Another session is already active for this user' and nothing shows or ends it.</t>
         </is>
       </c>
-      <c r="I24" s="9" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>Leaving the reader without closing it left the session ACTIVE; the 409 text was developer wording with no way out.</t>
         </is>
       </c>
-      <c r="J24" s="9" t="inlineStr">
+      <c r="J24" s="10" t="inlineStr">
         <is>
           <t>Leaving the reader pauses its session; the clash names the book ('You're still in a reading session for ...') and offers 'Pause that one and start here'.</t>
         </is>
       </c>
-      <c r="K24" s="9" t="inlineStr">
+      <c r="K24" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/library/SessionConflict.tsx, backend/src/modules/reading-sessions/reading-sessions.service.ts</t>
         </is>
       </c>
-      <c r="L24" s="9" t="inlineStr"/>
-      <c r="M24" s="9" t="inlineStr">
+      <c r="L24" s="10" t="inlineStr"/>
+      <c r="M24" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N24" s="9" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="n">
+      <c r="A25" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>R2-06</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>Tracking journal statistics</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="E25" s="10" t="inlineStr">
         <is>
           <t>Session time includes time away from the reader</t>
         </is>
       </c>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>Left the reader open in the background, came back, closed it.</t>
         </is>
       </c>
-      <c r="G25" s="9" t="inlineStr">
+      <c r="G25" s="10" t="inlineStr">
         <is>
           <t>Only active reading time.</t>
         </is>
       </c>
-      <c r="H25" s="9" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>'6 min of reading' for about a minute.</t>
         </is>
       </c>
-      <c r="I25" s="9" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>Duration was end minus start, including time away.</t>
         </is>
       </c>
-      <c r="J25" s="9" t="inlineStr">
+      <c r="J25" s="10" t="inlineStr">
         <is>
           <t>Sessions record paused time (pausedAt, pausedSeconds); a hidden tab pauses and resumes; the idle sweep pauses from the last page turn; paused time is subtracted.</t>
         </is>
       </c>
-      <c r="K25" s="9" t="inlineStr">
+      <c r="K25" s="10" t="inlineStr">
         <is>
           <t>backend/prisma/schema.prisma, backend/src/modules/reading-sessions/*, frontend/src/features/reader/FlowReaderPage.tsx</t>
         </is>
       </c>
-      <c r="L25" s="9" t="inlineStr"/>
-      <c r="M25" s="9" t="inlineStr">
+      <c r="L25" s="10" t="inlineStr"/>
+      <c r="M25" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N25" s="9" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="n">
+      <c r="A26" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>R2-07</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>Tracking journal statistics</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E26" s="10" t="inlineStr">
         <is>
           <t>Journal shows a raw internal position</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>Journal after a reader session.</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>'Chapter 4, 67%'.</t>
         </is>
       </c>
-      <c r="H26" s="9" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>'6 min · EPUB · epubcfi(/6/2!/4/2/1:0) → ch4'</t>
         </is>
       </c>
-      <c r="I26" s="9" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>The journal printed stored positions (CFI, chapter ids) as-is.</t>
         </is>
       </c>
-      <c r="J26" s="9" t="inlineStr">
+      <c r="J26" s="10" t="inlineStr">
         <is>
           <t>Entries carry startLabel/endLabel: chapter titles (from the chapter graph, CFIs by spine step), 'p. N' for pages.</t>
         </is>
       </c>
-      <c r="K26" s="9" t="inlineStr">
+      <c r="K26" s="10" t="inlineStr">
         <is>
           <t>backend/src/modules/journal/journal.service.ts, frontend/src/features/journal/JournalPage.tsx</t>
         </is>
       </c>
-      <c r="L26" s="9" t="inlineStr"/>
-      <c r="M26" s="9" t="inlineStr">
+      <c r="L26" s="10" t="inlineStr"/>
+      <c r="M26" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N26" s="9" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="n">
+      <c r="A27" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>R2-08</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>Reading experience</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E27" s="10" t="inlineStr">
         <is>
           <t>Can't select text in the default 3D Flip mode</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>Drag-select and double-click in 3D Flip.</t>
         </is>
       </c>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="G27" s="10" t="inlineStr">
         <is>
           <t>Text selects; highlight popover appears.</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>Dragging starts a page curl; only works after switching to Paginated, with no hint.</t>
         </is>
       </c>
-      <c r="I27" s="9" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>react-pageflip took mouse and touch input in 3D Flip mode, so a drag curled the page instead of selecting.</t>
         </is>
       </c>
-      <c r="J27" s="9" t="inlineStr">
+      <c r="J27" s="10" t="inlineStr">
         <is>
           <t>The flipbook no longer takes pointer input: text selects in every mode; pages turn with the buttons, arrow keys or a swipe.</t>
         </is>
       </c>
-      <c r="K27" s="9" t="inlineStr">
+      <c r="K27" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/reader/FlowReaderPage.tsx</t>
         </is>
       </c>
-      <c r="L27" s="9" t="inlineStr"/>
-      <c r="M27" s="9" t="inlineStr">
+      <c r="L27" s="10" t="inlineStr"/>
+      <c r="M27" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N27" s="9" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="n">
+      <c r="A28" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>R2-09</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>Reading experience</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D28" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E28" s="10" t="inlineStr">
         <is>
           <t>Phone reader shows ~6 lines in a tiny inset card</t>
         </is>
       </c>
-      <c r="F28" s="9" t="inlineStr">
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>Mobile 375x812, reader.</t>
         </is>
       </c>
-      <c r="G28" s="9" t="inlineStr">
+      <c r="G28" s="10" t="inlineStr">
         <is>
           <t>Text fills the screen.</t>
         </is>
       </c>
-      <c r="H28" s="9" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>Small inner card, ~6 lines per page; bookmark and View Original missing from the toolbar.</t>
         </is>
       </c>
-      <c r="I28" s="9" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>Pages were always A4 halves of a two-page spread, tiny on a phone; ten toolbar icons overflowed.</t>
         </is>
       </c>
-      <c r="J28" s="9" t="inlineStr">
+      <c r="J28" s="10" t="inlineStr">
         <is>
           <t>Below 768px one page fills the screen; Note, Translate, Music, View Original and 'Not where you left off?' move into a More menu.</t>
         </is>
       </c>
-      <c r="K28" s="9" t="inlineStr">
+      <c r="K28" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/ai/TranslatePanel.tsx</t>
         </is>
       </c>
-      <c r="L28" s="9" t="inlineStr"/>
-      <c r="M28" s="9" t="inlineStr">
+      <c r="L28" s="10" t="inlineStr"/>
+      <c r="M28" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N28" s="9" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="n">
+      <c r="A29" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>R2-10</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>Book page and details</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E29" s="10" t="inlineStr">
         <is>
           <t>Rating and Favourite silently lost without 'Save review'</t>
         </is>
       </c>
-      <c r="F29" s="9" t="inlineStr">
+      <c r="F29" s="10" t="inlineStr">
         <is>
           <t>Clicked 5 stars and Favourite, refreshed.</t>
         </is>
       </c>
-      <c r="G29" s="9" t="inlineStr">
+      <c r="G29" s="10" t="inlineStr">
         <is>
           <t>Saved instantly or warned.</t>
         </is>
       </c>
-      <c r="H29" s="9" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>All empty after refresh; no 'Saved' confirmation even when saving works.</t>
         </is>
       </c>
-      <c r="I29" s="9" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>Stars and Favourite only changed the form; nothing saved until 'Save review'.</t>
         </is>
       </c>
-      <c r="J29" s="9" t="inlineStr">
+      <c r="J29" s="10" t="inlineStr">
         <is>
           <t>Rating, favourite and reread save on click with a 'Saved.' note; unsaved review text is kept.</t>
         </is>
       </c>
-      <c r="K29" s="9" t="inlineStr">
+      <c r="K29" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/reviews/ReviewPanel.tsx</t>
         </is>
       </c>
-      <c r="L29" s="9" t="inlineStr"/>
-      <c r="M29" s="9" t="inlineStr">
+      <c r="L29" s="10" t="inlineStr"/>
+      <c r="M29" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N29" s="9" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="n">
+      <c r="A30" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>R2-11</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" s="10" t="inlineStr">
         <is>
           <t>Speed reliability</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D30" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E30" s="10" t="inlineStr">
         <is>
           <t>Logged out on refresh mid-session</t>
         </is>
       </c>
-      <c r="F30" s="9" t="inlineStr">
+      <c r="F30" s="10" t="inlineStr">
         <is>
           <t>~6 min after sign-in, refreshed the reader.</t>
         </is>
       </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="G30" s="10" t="inlineStr">
         <is>
           <t>Stay signed in.</t>
         </is>
       </c>
-      <c r="H30" s="9" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>Sent to /login, then landed on Library.</t>
         </is>
       </c>
-      <c r="I30" s="9" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>Refresh tokens rotate on every use; two refreshes with the same cookie (StrictMode's double restore, parallel 401s, several tabs reloading) made the loser look like token reuse and signed the reader out.</t>
         </is>
       </c>
-      <c r="J30" s="9" t="inlineStr">
+      <c r="J30" s="10" t="inlineStr">
         <is>
           <t>One refresh at a time: shared within a tab and serialised across tabs with a Web Lock; a failed refresh never clears a newer token.</t>
         </is>
       </c>
-      <c r="K30" s="9" t="inlineStr">
+      <c r="K30" s="10" t="inlineStr">
         <is>
           <t>frontend/src/lib/api/client.ts, frontend/src/lib/auth-context.tsx</t>
         </is>
       </c>
-      <c r="L30" s="9" t="inlineStr"/>
-      <c r="M30" s="9" t="inlineStr">
+      <c r="L30" s="10" t="inlineStr"/>
+      <c r="M30" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N30" s="9" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="n">
+      <c r="A31" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>R2-12</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C31" s="10" t="inlineStr">
         <is>
           <t>Reading experience</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
+      <c r="E31" s="10" t="inlineStr">
         <is>
           <t>Changing font size resets to the start</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr">
+      <c r="F31" s="10" t="inlineStr">
         <is>
           <t>Page 2 of 8 &gt; font +2.</t>
         </is>
       </c>
-      <c r="G31" s="9" t="inlineStr">
+      <c r="G31" s="10" t="inlineStr">
         <is>
           <t>Same passage.</t>
         </is>
       </c>
-      <c r="H31" s="9" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>'Page 1 of 10', back at chapter 1.</t>
         </is>
       </c>
-      <c r="I31" s="9" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>Re-pagination re-anchored to the chapter's first page, and the flipbook wasn't remounted at the new index.</t>
         </is>
       </c>
-      <c r="J31" s="9" t="inlineStr">
+      <c r="J31" s="10" t="inlineStr">
         <is>
           <t>Position is chapter + character offset; after any re-layout the reader lands on the page holding that passage.</t>
         </is>
       </c>
-      <c r="K31" s="9" t="inlineStr">
+      <c r="K31" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/reader/flow-layout.ts</t>
         </is>
       </c>
-      <c r="L31" s="9" t="inlineStr"/>
-      <c r="M31" s="9" t="inlineStr">
+      <c r="L31" s="10" t="inlineStr"/>
+      <c r="M31" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N31" s="9" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="n">
+      <c r="A32" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>R2-13</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C32" s="10" t="inlineStr">
         <is>
           <t>Reading experience</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="E32" s="10" t="inlineStr">
         <is>
           <t>'View Original' loses your place and has no way back</t>
         </is>
       </c>
-      <c r="F32" s="9" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t>At 67% &gt; View Original.</t>
         </is>
       </c>
-      <c r="G32" s="9" t="inlineStr">
+      <c r="G32" s="10" t="inlineStr">
         <is>
           <t>Same position; toggle back.</t>
         </is>
       </c>
-      <c r="H32" s="9" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>Opens at chapter 1, 0%; no side padding, default Times; only Close.</t>
         </is>
       </c>
-      <c r="I32" s="9" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>The original view ignored the reading view's position (epub.js only finds an idref with '#') and had only Close.</t>
         </is>
       </c>
-      <c r="J32" s="9" t="inlineStr">
+      <c r="J32" s="10" t="inlineStr">
         <is>
           <t>Opens at the chapter you were on; 'Back to reading view' button.</t>
         </is>
       </c>
-      <c r="K32" s="9" t="inlineStr">
+      <c r="K32" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/reader/ReaderPage.tsx, frontend/src/features/reader/EpubReader.tsx</t>
         </is>
       </c>
-      <c r="L32" s="9" t="inlineStr"/>
-      <c r="M32" s="9" t="inlineStr">
+      <c r="L32" s="10" t="inlineStr"/>
+      <c r="M32" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N32" s="9" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="n">
+      <c r="A33" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>R2-14</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>Reading experience</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="D33" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="E33" s="10" t="inlineStr">
         <is>
           <t>Reader renders shrunken after closing a session</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>X &gt; Session ended &gt; Skip.</t>
         </is>
       </c>
-      <c r="G33" s="9" t="inlineStr">
+      <c r="G33" s="10" t="inlineStr">
         <is>
           <t>Back to the library, or a normal reader.</t>
         </is>
       </c>
-      <c r="H33" s="9" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>A small card mid-screen; X vs Skip inconsistent.</t>
         </is>
       </c>
-      <c r="I33" s="9" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>The reflection prompt replaced the reader, and Save/Skip went 'back' in history, sometimes into the reading view of the ended session.</t>
         </is>
       </c>
-      <c r="J33" s="9" t="inlineStr">
+      <c r="J33" s="10" t="inlineStr">
         <is>
           <t>The prompt sits over the book; both readers return to the book page afterwards.</t>
         </is>
       </c>
-      <c r="K33" s="9" t="inlineStr">
+      <c r="K33" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/reader/ReaderPage.tsx</t>
         </is>
       </c>
-      <c r="L33" s="9" t="inlineStr"/>
-      <c r="M33" s="9" t="inlineStr">
+      <c r="L33" s="10" t="inlineStr"/>
+      <c r="M33" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N33" s="9" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="n">
+      <c r="A34" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>R2-15</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C34" s="10" t="inlineStr">
         <is>
           <t>Reading experience</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="D34" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="E34" s="10" t="inlineStr">
         <is>
           <t>Pages half empty; first spread's left page blank</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr">
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t>Read the first spreads on desktop.</t>
         </is>
       </c>
-      <c r="G34" s="9" t="inlineStr">
+      <c r="G34" s="10" t="inlineStr">
         <is>
           <t>Pages fill.</t>
         </is>
       </c>
-      <c r="H34" s="9" t="inlineStr">
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>Text stops two-thirds down; next spread has one line then a new chapter.</t>
         </is>
       </c>
-      <c r="I34" s="9" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <t>Pagination estimated characters per page (deliberately conservative) and the first page was laid out as a lone 'cover'.</t>
         </is>
       </c>
-      <c r="J34" s="9" t="inlineStr">
+      <c r="J34" s="10" t="inlineStr">
         <is>
           <t>Pages are measured with the real fonts in an offscreen copy of the page (about 97% full, nothing clipped); the cover slot is used only for a real cover.</t>
         </is>
       </c>
-      <c r="K34" s="9" t="inlineStr">
+      <c r="K34" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/reader/flow-layout.ts, frontend/src/features/reader/FlowReaderPage.tsx</t>
         </is>
       </c>
-      <c r="L34" s="9" t="inlineStr"/>
-      <c r="M34" s="9" t="inlineStr">
+      <c r="L34" s="10" t="inlineStr"/>
+      <c r="M34" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N34" s="9" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="n">
+      <c r="A35" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>R2-16</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>Reading experience</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="D35" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E35" s="10" t="inlineStr">
         <is>
           <t>'mins left' estimate depends on layout</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
+      <c r="F35" s="10" t="inlineStr">
         <is>
           <t>Changed font size, chapter list, mobile.</t>
         </is>
       </c>
-      <c r="G35" s="9" t="inlineStr">
+      <c r="G35" s="10" t="inlineStr">
         <is>
           <t>Stable estimate.</t>
         </is>
       </c>
-      <c r="H35" s="9" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>~32, ~40, ~68, ~50 at the same spot.</t>
         </is>
       </c>
-      <c r="I35" s="9" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <t>'mins left' was pages left x 4.</t>
         </is>
       </c>
-      <c r="J35" s="9" t="inlineStr">
+      <c r="J35" s="10" t="inlineStr">
         <is>
           <t>Progress and time left come from characters read (about 230 words a minute), the same at any font size.</t>
         </is>
       </c>
-      <c r="K35" s="9" t="inlineStr">
+      <c r="K35" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/reader/ReaderProgressScrubber.tsx</t>
         </is>
       </c>
-      <c r="L35" s="9" t="inlineStr"/>
-      <c r="M35" s="9" t="inlineStr">
+      <c r="L35" s="10" t="inlineStr"/>
+      <c r="M35" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N35" s="9" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="n">
+      <c r="A36" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>R2-17</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>Reading experience</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="E36" s="10" t="inlineStr">
         <is>
           <t>Arrow keys don't turn pages</t>
         </is>
       </c>
-      <c r="F36" s="9" t="inlineStr">
+      <c r="F36" s="10" t="inlineStr">
         <is>
           <t>Right arrow in the reader.</t>
         </is>
       </c>
-      <c r="G36" s="9" t="inlineStr">
+      <c r="G36" s="10" t="inlineStr">
         <is>
           <t>Next page.</t>
         </is>
       </c>
-      <c r="H36" s="9" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>Nothing.</t>
         </is>
       </c>
-      <c r="I36" s="9" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>No keyboard handling in the reading view.</t>
         </is>
       </c>
-      <c r="J36" s="9" t="inlineStr">
+      <c r="J36" s="10" t="inlineStr">
         <is>
           <t>Left/Right arrows and Page Up/Down turn pages (not while typing or in a dialog).</t>
         </is>
       </c>
-      <c r="K36" s="9" t="inlineStr">
+      <c r="K36" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/reader/FlowReaderPage.tsx</t>
         </is>
       </c>
-      <c r="L36" s="9" t="inlineStr"/>
-      <c r="M36" s="9" t="inlineStr">
+      <c r="L36" s="10" t="inlineStr"/>
+      <c r="M36" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N36" s="9" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="n">
+      <c r="A37" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>R2-18</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>Notes highlights reviews</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="D37" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr">
+      <c r="E37" s="10" t="inlineStr">
         <is>
           <t>Reader highlights/notes absent from the book page; no central notes view</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="F37" s="10" t="inlineStr">
         <is>
           <t>Highlight with a margin note &gt; book page.</t>
         </is>
       </c>
-      <c r="G37" s="9" t="inlineStr">
+      <c r="G37" s="10" t="inlineStr">
         <is>
           <t>Listed on the book page.</t>
         </is>
       </c>
-      <c r="H37" s="9" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>'Notes: No notes yet.'</t>
         </is>
       </c>
-      <c r="I37" s="9" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>The book page listed notes only; highlights lived in the reader.</t>
         </is>
       </c>
-      <c r="J37" s="9" t="inlineStr">
+      <c r="J37" s="10" t="inlineStr">
         <is>
           <t>'Highlights &amp; quotes' on the book page, newest first, with colour, margin note and a link back into the book. (A separate all-books notes page isn't built.)</t>
         </is>
       </c>
-      <c r="K37" s="9" t="inlineStr">
+      <c r="K37" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/notes/BookHighlights.tsx, frontend/src/features/library/BookDetailPage.tsx</t>
         </is>
       </c>
-      <c r="L37" s="9" t="inlineStr"/>
-      <c r="M37" s="9" t="inlineStr">
+      <c r="L37" s="10" t="inlineStr"/>
+      <c r="M37" s="10" t="inlineStr">
         <is>
           <t>Partly fixed</t>
         </is>
       </c>
-      <c r="N37" s="9" t="inlineStr"/>
+      <c r="N37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="n">
+      <c r="A38" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>R2-19</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>Assistant chat</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="D38" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E38" s="9" t="inlineStr">
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>Natural follow-ups and phrasing variants fail</t>
         </is>
       </c>
-      <c r="F38" s="9" t="inlineStr">
+      <c r="F38" s="10" t="inlineStr">
         <is>
           <t>'finsihed circe, 4 stars and put it on comfort reads', 'put it on comfort reads', 'put circe on comfort reads', 'actually undo that'.</t>
         </is>
       </c>
-      <c r="G38" s="9" t="inlineStr">
+      <c r="G38" s="10" t="inlineStr">
         <is>
           <t>Handled, or each simple command.</t>
         </is>
       </c>
-      <c r="H38" s="9" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>The same canned 'not set up' reply each time; a message typed while pending wasn't sent on Enter.</t>
         </is>
       </c>
-      <c r="I38" s="9" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>'put X on Y' needed the word 'shelf'; 'it' was bound to the previous turn's subject; 'actually undo that' wasn't recognised.</t>
         </is>
       </c>
-      <c r="J38" s="9" t="inlineStr">
+      <c r="J38" s="10" t="inlineStr">
         <is>
           <t>Shelves named without 'shelf' (and 'add X to Y' when Y is a shelf or X is theirs); 'it' is the book named in the same message; undo accepts fillers. The tester's sentence now does status, rating and shelf without a model.</t>
         </is>
       </c>
-      <c r="K38" s="9" t="inlineStr">
+      <c r="K38" s="10" t="inlineStr">
         <is>
           <t>backend/src/modules/assistant/domains/books/conversation/quickCommands.ts, backend/src/modules/assistant/domains/books/pipeline/preRoute.ts, backend/src/modules/assistant/domains/books/pipeline/undo.ts</t>
         </is>
       </c>
-      <c r="L38" s="9" t="inlineStr"/>
-      <c r="M38" s="9" t="inlineStr">
+      <c r="L38" s="10" t="inlineStr"/>
+      <c r="M38" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N38" s="9" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="n">
+      <c r="A39" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>R2-20</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>Tracking journal statistics</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr">
+      <c r="D39" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr">
+      <c r="E39" s="10" t="inlineStr">
         <is>
           <t>No finish dates, so 'this year' can't be answered</t>
         </is>
       </c>
-      <c r="F39" s="9" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>Marked books Finished; asked 'how many books did i read this year'.</t>
         </is>
       </c>
-      <c r="G39" s="9" t="inlineStr">
+      <c r="G39" s="10" t="inlineStr">
         <is>
           <t>Finish dates; yearly count.</t>
         </is>
       </c>
-      <c r="H39" s="9" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>'Bunko can only tell which were this year from logged reading sessions...'</t>
         </is>
       </c>
-      <c r="I39" s="9" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>No completion date was stored.</t>
         </is>
       </c>
-      <c r="J39" s="9" t="inlineStr">
+      <c r="J39" s="10" t="inlineStr">
         <is>
           <t>UserWork.finishedAt (SRS §18.2), set when marked Finished, backfilled from the last session; shown on the book page; 'this year' uses it.</t>
         </is>
       </c>
-      <c r="K39" s="9" t="inlineStr">
+      <c r="K39" s="10" t="inlineStr">
         <is>
           <t>backend/prisma/schema.prisma, backend/src/modules/library/library.service.ts, backend/src/modules/assistant/domains/books/conversation/libraryAnswers.ts, frontend/src/features/library/BookDetailPage.tsx</t>
         </is>
       </c>
-      <c r="L39" s="9" t="inlineStr"/>
-      <c r="M39" s="9" t="inlineStr">
+      <c r="L39" s="10" t="inlineStr"/>
+      <c r="M39" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N39" s="9" t="inlineStr"/>
+      <c r="N39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="n">
+      <c r="A40" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>R2-21</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="C40" s="10" t="inlineStr">
         <is>
           <t>Library adding finding books</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
+      <c r="D40" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr">
+      <c r="E40" s="10" t="inlineStr">
         <is>
           <t>Book search slow and typo-intolerant</t>
         </is>
       </c>
-      <c r="F40" s="9" t="inlineStr">
+      <c r="F40" s="10" t="inlineStr">
         <is>
           <t>'tomorow and tomorrow and tomorrow'.</t>
         </is>
       </c>
-      <c r="G40" s="9" t="inlineStr">
+      <c r="G40" s="10" t="inlineStr">
         <is>
           <t>Right book within a couple of seconds.</t>
         </is>
       </c>
-      <c r="H40" s="9" t="inlineStr">
+      <c r="H40" s="10" t="inlineStr">
         <is>
           <t>10-15s spinner, unrelated results.</t>
         </is>
       </c>
-      <c r="I40" s="9" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>Catalogue providers are slow on a cold query and have no fuzzy matching; results are cached for an hour after the first search.</t>
         </is>
       </c>
-      <c r="J40" s="9" t="inlineStr">
+      <c r="J40" s="10" t="inlineStr">
         <is>
           <t>Not changed this round (needs a provider-side change).</t>
         </is>
       </c>
-      <c r="K40" s="9" t="inlineStr"/>
-      <c r="L40" s="9" t="inlineStr"/>
-      <c r="M40" s="9" t="inlineStr">
+      <c r="K40" s="10" t="inlineStr"/>
+      <c r="L40" s="10" t="inlineStr"/>
+      <c r="M40" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="N40" s="9" t="inlineStr"/>
+      <c r="N40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="n">
+      <c r="A41" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>R2-22</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C41" s="10" t="inlineStr">
         <is>
           <t>Library adding finding books</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="D41" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr">
+      <c r="E41" s="10" t="inlineStr">
         <is>
           <t>Status doesn't follow reading; no progress shown</t>
         </is>
       </c>
-      <c r="F41" s="9" t="inlineStr">
+      <c r="F41" s="10" t="inlineStr">
         <is>
           <t>Read to 67%, back to Library.</t>
         </is>
       </c>
-      <c r="G41" s="9" t="inlineStr">
+      <c r="G41" s="10" t="inlineStr">
         <is>
           <t>Status Reading; progress on the card.</t>
         </is>
       </c>
-      <c r="H41" s="9" t="inlineStr">
+      <c r="H41" s="10" t="inlineStr">
         <is>
           <t>Still Want to Read; no progress; 'Continue Reading' before ever opening.</t>
         </is>
       </c>
-      <c r="I41" s="9" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>Opening a book never changed its status; the button always said 'Continue Reading'.</t>
         </is>
       </c>
-      <c r="J41" s="9" t="inlineStr">
+      <c r="J41" s="10" t="inlineStr">
         <is>
           <t>Starting or logging a session moves Want to Read to Reading (never Finished/DNF); 'Start reading' until the first session. (Progress on cards not built.)</t>
         </is>
       </c>
-      <c r="K41" s="9" t="inlineStr">
+      <c r="K41" s="10" t="inlineStr">
         <is>
           <t>backend/src/modules/library/library.service.ts, backend/src/modules/reading-sessions/reading-sessions.service.ts, frontend/src/features/library/ContinueReadingButton.tsx</t>
         </is>
       </c>
-      <c r="L41" s="9" t="inlineStr"/>
-      <c r="M41" s="9" t="inlineStr">
+      <c r="L41" s="10" t="inlineStr"/>
+      <c r="M41" s="10" t="inlineStr">
         <is>
           <t>Partly fixed</t>
         </is>
       </c>
-      <c r="N41" s="9" t="inlineStr"/>
+      <c r="N41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="n">
+      <c r="A42" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>R2-23</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C42" s="10" t="inlineStr">
         <is>
           <t>Tracking journal statistics</t>
         </is>
       </c>
-      <c r="D42" s="9" t="inlineStr">
+      <c r="D42" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E42" s="9" t="inlineStr">
+      <c r="E42" s="10" t="inlineStr">
         <is>
           <t>Languages 'Unknown 6' and lowercase 'english'; EPUB reading added no pages</t>
         </is>
       </c>
-      <c r="F42" s="9" t="inlineStr">
+      <c r="F42" s="10" t="inlineStr">
         <is>
           <t>Statistics &gt; Languages.</t>
         </is>
       </c>
-      <c r="G42" s="9" t="inlineStr">
+      <c r="G42" s="10" t="inlineStr">
         <is>
           <t>'English'; EPUB pages counted.</t>
         </is>
       </c>
-      <c r="H42" s="9" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>'Unknown 6 books', 'english 1 book'; pages read only from the manual log.</t>
         </is>
       </c>
-      <c r="I42" s="9" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>The page passed language names through Intl.DisplayNames, which reads 'english' as a valid code and returns it lowercased; books with no language said 'Unknown'.</t>
         </is>
       </c>
-      <c r="J42" s="9" t="inlineStr">
+      <c r="J42" s="10" t="inlineStr">
         <is>
           <t>Only codes are looked up, names are capitalised; missing language reads 'Not recorded'. (EPUB pages need a start position; unchanged.)</t>
         </is>
       </c>
-      <c r="K42" s="9" t="inlineStr">
+      <c r="K42" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/statistics/chart-format.ts, frontend/src/features/statistics/StatisticsPage.tsx</t>
         </is>
       </c>
-      <c r="L42" s="9" t="inlineStr"/>
-      <c r="M42" s="9" t="inlineStr">
+      <c r="L42" s="10" t="inlineStr"/>
+      <c r="M42" s="10" t="inlineStr">
         <is>
           <t>Partly fixed</t>
         </is>
       </c>
-      <c r="N42" s="9" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="n">
+      <c r="A43" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>R2-24</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t>Shelves organizing</t>
         </is>
       </c>
-      <c r="D43" s="9" t="inlineStr">
+      <c r="D43" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E43" s="9" t="inlineStr">
+      <c r="E43" s="10" t="inlineStr">
         <is>
           <t>An empty shelf offers no way to add books</t>
         </is>
       </c>
-      <c r="F43" s="9" t="inlineStr">
+      <c r="F43" s="10" t="inlineStr">
         <is>
           <t>New shelf '2026 faves'.</t>
         </is>
       </c>
-      <c r="G43" s="9" t="inlineStr">
+      <c r="G43" s="10" t="inlineStr">
         <is>
           <t>An 'Add books' picker.</t>
         </is>
       </c>
-      <c r="H43" s="9" t="inlineStr">
+      <c r="H43" s="10" t="inlineStr">
         <is>
           <t>Text only, no button.</t>
         </is>
       </c>
-      <c r="I43" s="9" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>No way to add books from a shelf.</t>
         </is>
       </c>
-      <c r="J43" s="9" t="inlineStr">
+      <c r="J43" s="10" t="inlineStr">
         <is>
           <t>'Add books' on custom shelves and in the empty state: a searchable picker of library books.</t>
         </is>
       </c>
-      <c r="K43" s="9" t="inlineStr">
+      <c r="K43" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/shelves/AddToShelfDialog.tsx, frontend/src/features/shelves/ShelvesPage.tsx</t>
         </is>
       </c>
-      <c r="L43" s="9" t="inlineStr"/>
-      <c r="M43" s="9" t="inlineStr">
+      <c r="L43" s="10" t="inlineStr"/>
+      <c r="M43" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N43" s="9" t="inlineStr"/>
+      <c r="N43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="n">
+      <c r="A44" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>R2-25</t>
         </is>
       </c>
-      <c r="C44" s="9" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>Shelves organizing</t>
         </is>
       </c>
-      <c r="D44" s="9" t="inlineStr">
+      <c r="D44" s="10" t="inlineStr">
         <is>
           <t>polish</t>
         </is>
       </c>
-      <c r="E44" s="9" t="inlineStr">
+      <c r="E44" s="10" t="inlineStr">
         <is>
           <t>Low-contrast toggle and unlabeled shelf tabs</t>
         </is>
       </c>
-      <c r="F44" s="9" t="inlineStr">
+      <c r="F44" s="10" t="inlineStr">
         <is>
           <t>Shelves page.</t>
         </is>
       </c>
-      <c r="G44" s="9" t="inlineStr">
+      <c r="G44" s="10" t="inlineStr">
         <is>
           <t>Readable toggle; named tabs.</t>
         </is>
       </c>
-      <c r="H44" s="9" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
         <is>
           <t>'Covers' dark brown on near-black; tabs read as unnamed buttons; odd brown scrollbar strip.</t>
         </is>
       </c>
-      <c r="I44" s="9" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>Inactive toggle text at 70% opacity on near-black; dark wood scrollbar on the paper background.</t>
         </is>
       </c>
-      <c r="J44" s="9" t="inlineStr">
+      <c r="J44" s="10" t="inlineStr">
         <is>
           <t>Full-strength toggle text; shelf tabs say their name and count and report pressed state; light paper scrollbar.</t>
         </is>
       </c>
-      <c r="K44" s="9" t="inlineStr">
+      <c r="K44" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/shelves/ShelvesPage.tsx, frontend/src/index.css</t>
         </is>
       </c>
-      <c r="L44" s="9" t="inlineStr"/>
-      <c r="M44" s="9" t="inlineStr">
+      <c r="L44" s="10" t="inlineStr"/>
+      <c r="M44" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N44" s="9" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="n">
+      <c r="A45" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>R2-26</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>Tracking journal statistics</t>
         </is>
       </c>
-      <c r="D45" s="9" t="inlineStr">
+      <c r="D45" s="10" t="inlineStr">
         <is>
           <t>polish</t>
         </is>
       </c>
-      <c r="E45" s="9" t="inlineStr">
+      <c r="E45" s="10" t="inlineStr">
         <is>
           <t>Journal order wrong; entries can't be edited</t>
         </is>
       </c>
-      <c r="F45" s="9" t="inlineStr">
+      <c r="F45" s="10" t="inlineStr">
         <is>
           <t>Logged a session after another the same day.</t>
         </is>
       </c>
-      <c r="G45" s="9" t="inlineStr">
+      <c r="G45" s="10" t="inlineStr">
         <is>
           <t>Newest first; edit/delete.</t>
         </is>
       </c>
-      <c r="H45" s="9" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
         <is>
           <t>Newer entry below the older; clicking opens the book.</t>
         </is>
       </c>
-      <c r="I45" s="9" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>Journal sorted by start time, so a session logged after the fact sorted by when it began.</t>
         </is>
       </c>
-      <c r="J45" s="9" t="inlineStr">
+      <c r="J45" s="10" t="inlineStr">
         <is>
           <t>Sorted by when sessions ended. (Editing an entry isn't built.)</t>
         </is>
       </c>
-      <c r="K45" s="9" t="inlineStr">
+      <c r="K45" s="10" t="inlineStr">
         <is>
           <t>backend/src/modules/journal/journal.service.ts</t>
         </is>
       </c>
-      <c r="L45" s="9" t="inlineStr"/>
-      <c r="M45" s="9" t="inlineStr">
+      <c r="L45" s="10" t="inlineStr"/>
+      <c r="M45" s="10" t="inlineStr">
         <is>
           <t>Partly fixed</t>
         </is>
       </c>
-      <c r="N45" s="9" t="inlineStr"/>
+      <c r="N45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="n">
+      <c r="A46" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B46" s="9" t="inlineStr">
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t>R2-27</t>
         </is>
       </c>
-      <c r="C46" s="9" t="inlineStr">
+      <c r="C46" s="10" t="inlineStr">
         <is>
           <t>Book page and details</t>
         </is>
       </c>
-      <c r="D46" s="9" t="inlineStr">
+      <c r="D46" s="10" t="inlineStr">
         <is>
           <t>polish</t>
         </is>
       </c>
-      <c r="E46" s="9" t="inlineStr">
+      <c r="E46" s="10" t="inlineStr">
         <is>
           <t>Duplicate status, marketing-blurb synopsis, small icon issues</t>
         </is>
       </c>
-      <c r="F46" s="9" t="inlineStr">
+      <c r="F46" s="10" t="inlineStr">
         <is>
           <t>Book pages and reader toolbar.</t>
         </is>
       </c>
-      <c r="G46" s="9" t="inlineStr">
+      <c r="G46" s="10" t="inlineStr">
         <is>
           <t>One status control, clean synopsis, labelled icons.</t>
         </is>
       </c>
-      <c r="H46" s="9" t="inlineStr">
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>Pill plus dropdown; synopsis starts with press quotes; unlabeled icon; bookmark icon never fills.</t>
         </is>
       </c>
-      <c r="I46" s="9" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>Status showed as a pill and a dropdown; catalogue copy opens with press quotes; bookmark icon never reflected state.</t>
         </is>
       </c>
-      <c r="J46" s="9" t="inlineStr">
+      <c r="J46" s="10" t="inlineStr">
         <is>
           <t>One labelled status control; leading press quotes and ALL-CAPS banners trimmed for display; the bookmark fills when the chapter is bookmarked.</t>
         </is>
       </c>
-      <c r="K46" s="9" t="inlineStr">
+      <c r="K46" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/library/BookDetailPage.tsx, frontend/src/features/library/synopsis.ts, frontend/src/features/reader/FlowReaderPage.tsx</t>
         </is>
       </c>
-      <c r="L46" s="9" t="inlineStr"/>
-      <c r="M46" s="9" t="inlineStr">
+      <c r="L46" s="10" t="inlineStr"/>
+      <c r="M46" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N46" s="9" t="inlineStr"/>
+      <c r="N46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="n">
+      <c r="A47" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B47" s="9" t="inlineStr">
+      <c r="B47" s="10" t="inlineStr">
         <is>
           <t>R2-28</t>
         </is>
       </c>
-      <c r="C47" s="9" t="inlineStr">
+      <c r="C47" s="10" t="inlineStr">
         <is>
           <t>First impression onboarding</t>
         </is>
       </c>
-      <c r="D47" s="9" t="inlineStr">
+      <c r="D47" s="10" t="inlineStr">
         <is>
           <t>polish</t>
         </is>
       </c>
-      <c r="E47" s="9" t="inlineStr">
+      <c r="E47" s="10" t="inlineStr">
         <is>
           <t>No import or account basics for switchers</t>
         </is>
       </c>
-      <c r="F47" s="9" t="inlineStr">
+      <c r="F47" s="10" t="inlineStr">
         <is>
           <t>Welcome screen and Settings.</t>
         </is>
       </c>
-      <c r="G47" s="9" t="inlineStr">
+      <c r="G47" s="10" t="inlineStr">
         <is>
           <t>Import, yearly goal, export, change password.</t>
         </is>
       </c>
-      <c r="H47" s="9" t="inlineStr">
+      <c r="H47" s="10" t="inlineStr">
         <is>
           <t>None present.</t>
         </is>
       </c>
-      <c r="I47" s="9" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>Import (SRS §37), reading goals, export and password change aren't in the MVP scope.</t>
         </is>
       </c>
-      <c r="J47" s="9" t="inlineStr">
+      <c r="J47" s="10" t="inlineStr">
         <is>
           <t>Not built; needs product approval.</t>
         </is>
       </c>
-      <c r="K47" s="9" t="inlineStr"/>
-      <c r="L47" s="9" t="inlineStr"/>
-      <c r="M47" s="9" t="inlineStr">
+      <c r="K47" s="10" t="inlineStr"/>
+      <c r="L47" s="10" t="inlineStr"/>
+      <c r="M47" s="10" t="inlineStr">
         <is>
           <t>Won't fix (needs approval)</t>
         </is>
       </c>
-      <c r="N47" s="9" t="inlineStr"/>
+      <c r="N47" s="10" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>R3-01</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>Notes highlights reviews</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>Saved review is blank after a page refresh, and Save invites wiping it</t>
+        </is>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>Write a review, Save changes ('Saved.'), refresh the page.</t>
+        </is>
+      </c>
+      <c r="G48" s="10" t="inlineStr">
+        <is>
+          <t>Review text still there.</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t>Box empty with Save enabled; in-app navigation shows it again.</t>
+        </is>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>Regression from R2-10: the panel moved its 'last saved text' marker before React ran the state update, so on a fresh load the update compared against the new text and kept the empty draft.</t>
+        </is>
+      </c>
+      <c r="J48" s="10" t="inlineStr">
+        <is>
+          <t>The previous value is captured before the marker moves; verified: text survives a refresh and Save stays disabled until edited.</t>
+        </is>
+      </c>
+      <c r="K48" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reviews/ReviewPanel.tsx</t>
+        </is>
+      </c>
+      <c r="L48" s="10" t="inlineStr"/>
+      <c r="M48" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N48" s="10" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>R3-02</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>Shelves organizing</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="inlineStr">
+        <is>
+          <t>Spine language badge reads 'JAP'</t>
+        </is>
+      </c>
+      <c r="F49" s="10" t="inlineStr">
+        <is>
+          <t>Shelves &gt; Spines, a book marked Japanese.</t>
+        </is>
+      </c>
+      <c r="G49" s="10" t="inlineStr">
+        <is>
+          <t>A neutral code or no badge.</t>
+        </is>
+      </c>
+      <c r="H49" s="10" t="inlineStr">
+        <is>
+          <t>'JAP' on the spine, an ethnic slur.</t>
+        </is>
+      </c>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>Spines printed the first three letters of the language name.</t>
+        </is>
+      </c>
+      <c r="J49" s="10" t="inlineStr">
+        <is>
+          <t>Two-letter ISO codes (JA, TA, ID); no badge when the language isn't known.</t>
+        </is>
+      </c>
+      <c r="K49" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/lib/language-code.ts, frontend/src/features/shelves/BookSpine.tsx</t>
+        </is>
+      </c>
+      <c r="L49" s="10" t="inlineStr"/>
+      <c r="M49" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N49" s="10" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>R3-03</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>Library adding finding books</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>Original language wrong in search results and on the book</t>
+        </is>
+      </c>
+      <c r="F50" s="10" t="inlineStr">
+        <is>
+          <t>Add a book &gt; search 'piranesi', 'Convenience Store Woman'.</t>
+        </is>
+      </c>
+      <c r="G50" s="10" t="inlineStr">
+        <is>
+          <t>Piranesi original English; Murata original Japanese.</t>
+        </is>
+      </c>
+      <c r="H50" s="10" t="inlineStr">
+        <is>
+          <t>Every Open Library result 'Orig: Japanese'; Google Books Murata 'Orig: English'; carried into Shelves and Statistics.</t>
+        </is>
+      </c>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>Book search filled in 'Japanese' as the original language whenever a catalogue didn't give one (Google's edition language was also used as the original).</t>
+        </is>
+      </c>
+      <c r="J50" s="10" t="inlineStr">
+        <is>
+          <t>Original language is left empty unless known; a migration clears the guessed value on existing books (where the edition isn't Japanese and the title has no Japanese script).</t>
+        </is>
+      </c>
+      <c r="K50" s="10" t="inlineStr">
+        <is>
+          <t>backend/src/modules/metadata/metadata.service.ts, backend/prisma/migrations/20261023090000_clear_guessed_original_language</t>
+        </is>
+      </c>
+      <c r="L50" s="10" t="inlineStr"/>
+      <c r="M50" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N50" s="10" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>R3-04</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>Assistant chat</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>Assistant added a foreign-language edition of Circe</t>
+        </is>
+      </c>
+      <c r="F51" s="10" t="inlineStr">
+        <is>
+          <t>'I just finished Circe by Madeline Miller, 4 stars'.</t>
+        </is>
+      </c>
+      <c r="G51" s="10" t="inlineStr">
+        <is>
+          <t>The English edition.</t>
+        </is>
+      </c>
+      <c r="H51" s="10" t="inlineStr">
+        <is>
+          <t>Indonesian description, 'IND' spine, Indonesian in Statistics.</t>
+        </is>
+      </c>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>Two editions with the same title and author were de-duplicated first-come, and the Indonesian one arrived first.</t>
+        </is>
+      </c>
+      <c r="J51" s="10" t="inlineStr">
+        <is>
+          <t>De-duplication and ranking prefer the reader's language for Latin-script queries (other scripts unaffected).</t>
+        </is>
+      </c>
+      <c r="K51" s="10" t="inlineStr">
+        <is>
+          <t>backend/src/modules/metadata/metadata.service.ts</t>
+        </is>
+      </c>
+      <c r="L51" s="10" t="inlineStr"/>
+      <c r="M51" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N51" s="10" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>R3-05</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>Book page and details</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>Description shows raw markdown</t>
+        </is>
+      </c>
+      <c r="F52" s="10" t="inlineStr">
+        <is>
+          <t>Piranesi's book page.</t>
+        </is>
+      </c>
+      <c r="G52" s="10" t="inlineStr">
+        <is>
+          <t>Formatted or plain text.</t>
+        </is>
+      </c>
+      <c r="H52" s="10" t="inlineStr">
+        <is>
+          <t>'**From the *New York Times* bestselling author...**' with asterisks.</t>
+        </is>
+      </c>
+      <c r="I52" s="10" t="inlineStr">
+        <is>
+          <t>Some catalogues send markdown emphasis.</t>
+        </is>
+      </c>
+      <c r="J52" s="10" t="inlineStr">
+        <is>
+          <t>Shown as plain text (bold/italic markers removed; arithmetic asterisks left alone).</t>
+        </is>
+      </c>
+      <c r="K52" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/library/synopsis.ts</t>
+        </is>
+      </c>
+      <c r="L52" s="10" t="inlineStr"/>
+      <c r="M52" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N52" s="10" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>R3-06</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>Tracking journal statistics</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="inlineStr">
+        <is>
+          <t>Active paper session disappears on refresh</t>
+        </is>
+      </c>
+      <c r="F53" s="10" t="inlineStr">
+        <is>
+          <t>Start a reading session, refresh.</t>
+        </is>
+      </c>
+      <c r="G53" s="10" t="inlineStr">
+        <is>
+          <t>Still in progress, with elapsed time.</t>
+        </is>
+      </c>
+      <c r="H53" s="10" t="inlineStr">
+        <is>
+          <t>'Start a reading session' again; no timer while running.</t>
+        </is>
+      </c>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>The paper-session panel only remembered its session in page state.</t>
+        </is>
+      </c>
+      <c r="J53" s="10" t="inlineStr">
+        <is>
+          <t>GET /reading-sessions/open restores it after a refresh; the panel shows 'Reading for N min · started 4:05 PM'.</t>
+        </is>
+      </c>
+      <c r="K53" s="10" t="inlineStr">
+        <is>
+          <t>backend/src/modules/reading-sessions/*, frontend/src/lib/api/sessions.ts, frontend/src/features/library/PhysicalSessionPanel.tsx</t>
+        </is>
+      </c>
+      <c r="L53" s="10" t="inlineStr"/>
+      <c r="M53" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N53" s="10" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>R3-07</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>Assistant chat</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>Natural phrasing becomes part of the title</t>
+        </is>
+      </c>
+      <c r="F54" s="10" t="inlineStr">
+        <is>
+          <t>'gave up on Klara and the Sun around halfway, it just wasn't for me'.</t>
+        </is>
+      </c>
+      <c r="G54" s="10" t="inlineStr">
+        <is>
+          <t>Klara and the Sun marked DNF.</t>
+        </is>
+      </c>
+      <c r="H54" s="10" t="inlineStr">
+        <is>
+          <t>'I couldn't find a book called Klara and the Sun around halfway' with unrelated alternatives.</t>
+        </is>
+      </c>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>After the comma was cut, 'around halfway' stayed in the title.</t>
+        </is>
+      </c>
+      <c r="J54" s="10" t="inlineStr">
+        <is>
+          <t>How-far phrases (halfway, page 120, 40%...) are dropped, and when one of the reader's titles opens the phrase, that title is used.</t>
+        </is>
+      </c>
+      <c r="K54" s="10" t="inlineStr">
+        <is>
+          <t>backend/src/modules/assistant/domains/books/conversation/quickCommands.ts</t>
+        </is>
+      </c>
+      <c r="L54" s="10" t="inlineStr"/>
+      <c r="M54" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N54" s="10" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>R3-08</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>Shelves organizing</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>Shelf controls nearly invisible on dark wood</t>
+        </is>
+      </c>
+      <c r="F55" s="10" t="inlineStr">
+        <is>
+          <t>Shelves: Covers/Spines toggle and Add books.</t>
+        </is>
+      </c>
+      <c r="G55" s="10" t="inlineStr">
+        <is>
+          <t>Readable controls.</t>
+        </is>
+      </c>
+      <c r="H55" s="10" t="inlineStr">
+        <is>
+          <t>Dark text on dark brown.</t>
+        </is>
+      </c>
+      <c r="I55" s="10" t="inlineStr">
+        <is>
+          <t>The controls used wood-100, a colour step the palette doesn't define, so the class produced nothing; paper-600 and some moss steps (used in 36 files) were missing too.</t>
+        </is>
+      </c>
+      <c r="J55" s="10" t="inlineStr">
+        <is>
+          <t>Undefined shades replaced; paper-600, moss-200/400/800 added to the palette and DESIGN.md.</t>
+        </is>
+      </c>
+      <c r="K55" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/shelves/ShelvesPage.tsx, frontend/tailwind.config.js, DESIGN.md</t>
+        </is>
+      </c>
+      <c r="L55" s="10" t="inlineStr"/>
+      <c r="M55" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N55" s="10" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>R3-09</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>Tracking journal statistics</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>Journal entries can't be edited or deleted</t>
+        </is>
+      </c>
+      <c r="F56" s="10" t="inlineStr">
+        <is>
+          <t>Try to remove an accidental 1-minute session.</t>
+        </is>
+      </c>
+      <c r="G56" s="10" t="inlineStr">
+        <is>
+          <t>Edit or delete per entry.</t>
+        </is>
+      </c>
+      <c r="H56" s="10" t="inlineStr">
+        <is>
+          <t>Entries only link to the book.</t>
+        </is>
+      </c>
+      <c r="I56" s="10" t="inlineStr">
+        <is>
+          <t>No delete for sessions.</t>
+        </is>
+      </c>
+      <c r="J56" s="10" t="inlineStr">
+        <is>
+          <t>Delete (with confirmation) on each journal entry: DELETE /reading-sessions/:id, finished sessions only; highlights and notes from it stay.</t>
+        </is>
+      </c>
+      <c r="K56" s="10" t="inlineStr">
+        <is>
+          <t>backend/src/modules/reading-sessions/*, frontend/src/features/journal/JournalPage.tsx, frontend/src/lib/api/journal.ts</t>
+        </is>
+      </c>
+      <c r="L56" s="10" t="inlineStr"/>
+      <c r="M56" s="10" t="inlineStr">
+        <is>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="N56" s="10" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>R3-10</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>First impression onboarding</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>No Goodreads/StoryGraph import</t>
+        </is>
+      </c>
+      <c r="F57" s="10" t="inlineStr">
+        <is>
+          <t>Settings and empty Library.</t>
+        </is>
+      </c>
+      <c r="G57" s="10" t="inlineStr">
+        <is>
+          <t>CSV import.</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+      <c r="I57" s="10" t="inlineStr">
+        <is>
+          <t>Importing other platforms is SRS §37 (needs product approval).</t>
+        </is>
+      </c>
+      <c r="J57" s="10" t="inlineStr">
+        <is>
+          <t>Not built.</t>
+        </is>
+      </c>
+      <c r="K57" s="10" t="inlineStr"/>
+      <c r="L57" s="10" t="inlineStr"/>
+      <c r="M57" s="10" t="inlineStr">
+        <is>
+          <t>Won't fix (needs approval)</t>
+        </is>
+      </c>
+      <c r="N57" s="10" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>R3-11</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>Assistant chat</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>polish</t>
+        </is>
+      </c>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>Contradictory status confirmation</t>
+        </is>
+      </c>
+      <c r="F58" s="10" t="inlineStr">
+        <is>
+          <t>'started The Left Hand of Darkness yesterday'.</t>
+        </is>
+      </c>
+      <c r="G58" s="10" t="inlineStr">
+        <is>
+          <t>'Added as Reading.'</t>
+        </is>
+      </c>
+      <c r="H58" s="10" t="inlineStr">
+        <is>
+          <t>'I've added ... as Want to Read. I've marked ... as Reading.'</t>
+        </is>
+      </c>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>The merged 'added as X' reply didn't match authors with initials ('Ursula K. Le Guin').</t>
+        </is>
+      </c>
+      <c r="J58" s="10" t="inlineStr">
+        <is>
+          <t>The author part may contain periods; one sentence now.</t>
+        </is>
+      </c>
+      <c r="K58" s="10" t="inlineStr">
+        <is>
+          <t>backend/src/modules/assistant/domains/books/pipeline/replies.ts</t>
+        </is>
+      </c>
+      <c r="L58" s="10" t="inlineStr"/>
+      <c r="M58" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N58" s="10" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>R3-12</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>Look and feel</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>polish</t>
+        </is>
+      </c>
+      <c r="E59" s="10" t="inlineStr">
+        <is>
+          <t>Developer-ish or inconsistent wording</t>
+        </is>
+      </c>
+      <c r="F59" s="10" t="inlineStr">
+        <is>
+          <t>Shelves, Add book, Settings.</t>
+        </is>
+      </c>
+      <c r="G59" s="10" t="inlineStr">
+        <is>
+          <t>Consistent reader language.</t>
+        </is>
+      </c>
+      <c r="H59" s="10" t="inlineStr">
+        <is>
+          <t>'Catalog Racks &amp; Collections:', 'All Volumes' vs 'All Books', 'To Read', 'Parts Count', 'Your Added Language', source badges, 'search vectors', consent named differently on two pages.</t>
+        </is>
+      </c>
+      <c r="I59" s="10" t="inlineStr">
+        <is>
+          <t>Labels written from the code's point of view.</t>
+        </is>
+      </c>
+      <c r="J59" s="10" t="inlineStr">
+        <is>
+          <t>'Your shelves', 'All books', 'Want to Read', 'Parts'/'Chapters', 'Language you read it in', no source badges, 'a private search index', and the setting renamed 'Assistant and book summaries' to match the Assistant page.</t>
+        </is>
+      </c>
+      <c r="K59" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/shelves/ShelvesPage.tsx, frontend/src/features/library/AddBookDialog.tsx, frontend/src/features/ai/ai-disclosure.ts, frontend/src/features/ai/AiSettingsCard.tsx</t>
+        </is>
+      </c>
+      <c r="L59" s="10" t="inlineStr"/>
+      <c r="M59" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N59" s="10" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>R3-13</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>Library adding finding books</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>polish</t>
+        </is>
+      </c>
+      <c r="E60" s="10" t="inlineStr">
+        <is>
+          <t>Manual add lacks status; adding a copy gives no feedback</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>Add custom book manually; Add a copy &gt; Physical copy.</t>
+        </is>
+      </c>
+      <c r="G60" s="10" t="inlineStr">
+        <is>
+          <t>Status choice; confirmation.</t>
+        </is>
+      </c>
+      <c r="H60" s="10" t="inlineStr">
+        <is>
+          <t>Silently Want to Read; no feedback.</t>
+        </is>
+      </c>
+      <c r="I60" s="10" t="inlineStr">
+        <is>
+          <t>The manual form had no status choice; adding a copy closed silently.</t>
+        </is>
+      </c>
+      <c r="J60" s="10" t="inlineStr">
+        <is>
+          <t>'Add it as' on the manual form too; 'Copy added. You can start reading it now.' (Page count isn't stored on a work.)</t>
+        </is>
+      </c>
+      <c r="K60" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/library/AddBookDialog.tsx, frontend/src/features/library/BookQuickActionModal.tsx</t>
+        </is>
+      </c>
+      <c r="L60" s="10" t="inlineStr"/>
+      <c r="M60" s="10" t="inlineStr">
+        <is>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="N60" s="10" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>R3-14</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>Tracking journal statistics</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>polish</t>
+        </is>
+      </c>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>Statistics filler</t>
+        </is>
+      </c>
+      <c r="F61" s="10" t="inlineStr">
+        <is>
+          <t>Statistics with no EPUBs and no genres.</t>
+        </is>
+      </c>
+      <c r="G61" s="10" t="inlineStr">
+        <is>
+          <t>Caveats only when relevant.</t>
+        </is>
+      </c>
+      <c r="H61" s="10" t="inlineStr">
+        <is>
+          <t>'EPUB pages are estimated' with no EPUBs; a lone 'No genre: 5' bar.</t>
+        </is>
+      </c>
+      <c r="I61" s="10" t="inlineStr">
+        <is>
+          <t>Caveat always shown; an all-unknown breakdown drew one bar.</t>
+        </is>
+      </c>
+      <c r="J61" s="10" t="inlineStr">
+        <is>
+          <t>The EPUB caveat appears only with EPUB reading; 'None of your books has a genre recorded yet.' (Yearly goals and a ratings chart aren't in the SRS.)</t>
+        </is>
+      </c>
+      <c r="K61" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/statistics/StatisticsPage.tsx, frontend/src/features/statistics/BreakdownList.tsx</t>
+        </is>
+      </c>
+      <c r="L61" s="10" t="inlineStr"/>
+      <c r="M61" s="10" t="inlineStr">
+        <is>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="N61" s="10" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>R3-15</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>Book page and details</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>polish</t>
+        </is>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>Review buttons shown with only a rating</t>
+        </is>
+      </c>
+      <c r="F62" s="10" t="inlineStr">
+        <is>
+          <t>Rate a book with no review text.</t>
+        </is>
+      </c>
+      <c r="G62" s="10" t="inlineStr">
+        <is>
+          <t>'Remove review' hidden until a review exists.</t>
+        </is>
+      </c>
+      <c r="H62" s="10" t="inlineStr">
+        <is>
+          <t>Both buttons present.</t>
+        </is>
+      </c>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>The review buttons showed whenever a review row existed, including rating-only.</t>
+        </is>
+      </c>
+      <c r="J62" s="10" t="inlineStr">
+        <is>
+          <t>They appear only once there is review text.</t>
+        </is>
+      </c>
+      <c r="K62" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reviews/ReviewPanel.tsx</t>
+        </is>
+      </c>
+      <c r="L62" s="10" t="inlineStr"/>
+      <c r="M62" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N62" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N47"/>
+  <autoFilter ref="A1:N62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3642,7 +4634,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Round 1</t>
         </is>
@@ -3684,172 +4676,172 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>First impression onboarding</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Calm, bookish login with a clear error, but no forgot-password, onboarding or import, and the first library screen shows wrong covers.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Library adding finding books</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Exact search works and doesn't duplicate, but a single typo gives junk, search takes 6-8s, covers are wrong, there's no sort and no status choice when adding.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Book page and details</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Tidy single screen, but no description, pages or publication info, no way to fix a cover, and modal buttons that do nothing.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Reading experience</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>The sample EPUB couldn't be opened from any path.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Tracking journal statistics</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Timer-only sessions, pages not counted, journal entries don't name the book, stats contradict themselves.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Shelves organizing</t>
         </is>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B11" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>Charming bookcase and inline shelf creation, but odd one-book rows, per-row scrollbars, an inverted toggle and overlapping arrows on mobile.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Notes highlights reviews</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>Fast and pleasant, but whole stars only, notes undated, and highlights impossible without the reader.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Assistant chat</t>
         </is>
       </c>
-      <c r="B13" s="11" t="n">
+      <c r="B13" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>Good when phrased exactly, but about half the messages failed with 'An unexpected error occurred'; it can't handle 'it' or typos, and it invented 'Dune II'.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Look and feel</t>
         </is>
       </c>
-      <c r="B14" s="11" t="n">
+      <c r="B14" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>Feels made by book people; wrong covers undercut it.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Speed reliability</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n">
+      <c r="B15" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>Slow covers and search, status changes take ~3s with no feedback, assistant failures, remove seemed to do nothing.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Overall</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n">
+      <c r="B16" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>Good bones and taste, but I can't read a book, covers are wrong, the journal doesn't name books, and the assistant fails half the time.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Issues and fixes</t>
         </is>
@@ -3928,1061 +4920,1061 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="n">
+      <c r="A20" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>R1-01</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>Reading experience</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>blocker</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>No way to open the digital reader, even for a book with an EPUB</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>Library &gt; 'A Bunko Sample Book' &gt; 'Open Digital Reader'; clicked the EPUB edition row; tried status Reading, reload, and 'Start / Resume Reading Session'.</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>The EPUB opens in the reader.</t>
         </is>
       </c>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>Every path lands on the book details page; the EPUB edition row has no read button.</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>QA seed attached the EPUB with the upload id instead of the stored file id, so no copy existed; and the app gave a digital edition without its file no way forward.</t>
         </is>
       </c>
-      <c r="J20" s="9" t="inlineStr">
+      <c r="J20" s="10" t="inlineStr">
         <is>
           <t>Seed fixed (uses the id /files/:id/confirm returns) and now ships an original 5-chapter novella. A digital edition with no file shows 'Upload file'; the quick-action modal only offers actions that work.</t>
         </is>
       </c>
-      <c r="K20" s="9" t="inlineStr">
+      <c r="K20" s="10" t="inlineStr">
         <is>
           <t>backend/scripts/seed-qa-reader.ts, backend/scripts/qa-sample-book.ts, frontend/src/features/library/BookDetailPage.tsx, frontend/src/features/library/AddEditionDialog.tsx, frontend/src/features/library/BookQuickActionModal.tsx</t>
         </is>
       </c>
-      <c r="L20" s="9" t="inlineStr"/>
-      <c r="M20" s="9" t="inlineStr">
+      <c r="L20" s="10" t="inlineStr"/>
+      <c r="M20" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N20" s="9" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="n">
+      <c r="A21" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>R1-02</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>Library adding finding books</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>Most covers are for completely different books</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>Open Library (also Shelves, modal, book page).</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>The real cover for each book.</t>
         </is>
       </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>The Left Hand of Darkness and the sample book show 'Their Eyes Were Watching God'; Circe, Piranesi and Klara show unrelated books; a hand-added zine got a random cover. There's no way to change or remove a cover.</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>Three code paths took the first search result with any cover regardless of title; the seed also used guessed cover ids. Wikidata series discovery filed books under their own title.</t>
         </is>
       </c>
-      <c r="J21" s="9" t="inlineStr">
+      <c r="J21" s="10" t="inlineStr">
         <is>
           <t>Covers only from a result with the same main title and a shared author surname (pickMatchingCover), looked up in the background; self-named series ignored and cleared. Changing/removing a cover by hand is not built yet (covers live on the shared catalogue entry).</t>
         </is>
       </c>
-      <c r="K21" s="9" t="inlineStr">
+      <c r="K21" s="10" t="inlineStr">
         <is>
           <t>backend/src/modules/library/library.service.ts, backend/scripts/seed-qa-reader.ts</t>
         </is>
       </c>
-      <c r="L21" s="9" t="inlineStr"/>
-      <c r="M21" s="9" t="inlineStr">
+      <c r="L21" s="10" t="inlineStr"/>
+      <c r="M21" s="10" t="inlineStr">
         <is>
           <t>Partly fixed</t>
         </is>
       </c>
-      <c r="N21" s="9" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="n">
+      <c r="A22" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>R1-03</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>Assistant chat</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>Many assistant messages fail with a generic error</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F22" s="10" t="inlineStr">
         <is>
           <t>'no i meant the zevin one...', 'I started Tomorrow, and Tomorrow, and Tomorrow' (the app's own example), 'ok i started the first one. and dnf'd circe tbh', 'and add it to my comfort reads shelf', 'rate it 5 stars actually'.</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>The change is made, or a clarifying question.</t>
         </is>
       </c>
-      <c r="H22" s="9" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>'An unexpected error occurred' each time, no reason, no retry. Short single-book commands worked.</t>
         </is>
       </c>
-      <c r="I22" s="9" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>No NVIDIA key on the test server: NIM's 401 became a plain Error and surfaced as a 500. Separately, titles with commas, filler words ('ok', 'and', 'tbh', 'actually') and 'it' defeated the fast paths, so those messages needed the model.</t>
         </is>
       </c>
-      <c r="J22" s="9" t="inlineStr">
+      <c r="J22" s="10" t="inlineStr">
         <is>
           <t>Rejected key / rate limit are 'unavailable'; a missing key is detected at startup and answered with a plain message; any other failure is a friendly logged reply. Owned titles with commas are masked before clause splitting; filler words stripped.</t>
         </is>
       </c>
-      <c r="K22" s="9" t="inlineStr">
+      <c r="K22" s="10" t="inlineStr">
         <is>
           <t>backend/src/modules/assistant/clients/NvidiaNimClient.ts, backend/src/modules/assistant/aiController.ts, backend/src/modules/assistant/domains/books/conversation/quickCommands.ts</t>
         </is>
       </c>
-      <c r="L22" s="9" t="inlineStr"/>
-      <c r="M22" s="9" t="inlineStr">
+      <c r="L22" s="10" t="inlineStr"/>
+      <c r="M22" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N22" s="9" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="n">
+      <c r="A23" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>R1-04</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>Assistant chat</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E23" s="10" t="inlineStr">
         <is>
           <t>A typo in an owned title makes it search the catalogue for junk</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F23" s="10" t="inlineStr">
         <is>
           <t>'started tomorow and tomorrow last night, its so good already' (the book is in the library).</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>It matches the owned book.</t>
         </is>
       </c>
-      <c r="H23" s="9" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>"I couldn't find a book called \"tomorow\". The closest were \"Notes on the History of Fort George\"..."</t>
         </is>
       </c>
-      <c r="I23" s="9" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>Title matching needed exact words; the list splitter split 'tomorow and tomorrow' into two books.</t>
         </is>
       </c>
-      <c r="J23" s="9" t="inlineStr">
+      <c r="J23" s="10" t="inlineStr">
         <is>
           <t>Typo-tolerant word matching on owned titles; lists split only into books the reader owns.</t>
         </is>
       </c>
-      <c r="K23" s="9" t="inlineStr">
+      <c r="K23" s="10" t="inlineStr">
         <is>
           <t>backend/src/modules/assistant/domains/books/text/match.ts, backend/src/modules/assistant/domains/books/conversation/quickCommands.ts</t>
         </is>
       </c>
-      <c r="L23" s="9" t="inlineStr"/>
-      <c r="M23" s="9" t="inlineStr">
+      <c r="L23" s="10" t="inlineStr"/>
+      <c r="M23" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N23" s="9" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="n">
+      <c r="A24" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>R1-05</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>Assistant chat</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>Recommendations made up a sequel and ignored 'something like Piranesi'</t>
         </is>
       </c>
-      <c r="F24" s="9" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>'what should i read next? something like piranesi'</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>Books like Piranesi, and accurate facts.</t>
         </is>
       </c>
-      <c r="H24" s="9" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>Listed the Want to Read list only, and said 'the series continues with Dune II by Frank Herbert' (no such book).</t>
         </is>
       </c>
-      <c r="I24" s="9" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>The 'series continues' line came from a Wikidata lookup that returned non-books ('Dune II'); 'like X' wasn't used.</t>
         </is>
       </c>
-      <c r="J24" s="9" t="inlineStr">
+      <c r="J24" s="10" t="inlineStr">
         <is>
           <t>Series continuation removed; 'something like X' ranks the list by X's authors and genres with reasons, and asks the model for books beyond the list.</t>
         </is>
       </c>
-      <c r="K24" s="9" t="inlineStr">
+      <c r="K24" s="10" t="inlineStr">
         <is>
           <t>backend/src/modules/assistant/domains/books/actions/readTools.ts, backend/src/modules/assistant/domains/books/pipeline/preRoute.ts, backend/src/modules/assistant/domains/books/prompts/answerPrompt.ts</t>
         </is>
       </c>
-      <c r="L24" s="9" t="inlineStr"/>
-      <c r="M24" s="9" t="inlineStr">
+      <c r="L24" s="10" t="inlineStr"/>
+      <c r="M24" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N24" s="9" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="n">
+      <c r="A25" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>R1-06</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>Tracking journal statistics</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="E25" s="10" t="inlineStr">
         <is>
           <t>Journal entries don't say which book</t>
         </is>
       </c>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>Piranesi &gt; physical edition &gt; session &gt; end with 'p 112' and a reflection &gt; Journal.</t>
         </is>
       </c>
-      <c r="G25" s="9" t="inlineStr">
+      <c r="G25" s="10" t="inlineStr">
         <is>
           <t>Entry shows the book, page and time, and links to it.</t>
         </is>
       </c>
-      <c r="H25" s="9" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>'Oct 23, 2026 · 0 min · “the other is kinda sus now”': no title, no page, not clickable; no way to add an entry from the Journal.</t>
         </is>
       </c>
-      <c r="I25" s="9" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>Journal entries carried no book.</t>
         </is>
       </c>
-      <c r="J25" s="9" t="inlineStr">
+      <c r="J25" s="10" t="inlineStr">
         <is>
           <t>Each entry names and links its book with its cover and format; 'Log reading' on the Journal.</t>
         </is>
       </c>
-      <c r="K25" s="9" t="inlineStr">
+      <c r="K25" s="10" t="inlineStr">
         <is>
           <t>backend/src/modules/journal/journal.service.ts, frontend/src/features/journal/JournalPage.tsx</t>
         </is>
       </c>
-      <c r="L25" s="9" t="inlineStr"/>
-      <c r="M25" s="9" t="inlineStr">
+      <c r="L25" s="10" t="inlineStr"/>
+      <c r="M25" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N25" s="9" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="n">
+      <c r="A26" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>R1-07</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>Tracking journal statistics</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E26" s="10" t="inlineStr">
         <is>
           <t>Reading can only be logged live, and pages aren't counted</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>Started and immediately ended a session with 'p 112'.</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>Log a past session (time, date, page), and pages count.</t>
         </is>
       </c>
-      <c r="H26" s="9" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>'Session saved — 0 min. Nice reading.' Stats: 'Pages read 0'. No manual duration/date, no progress on the book, no finish date.</t>
         </is>
       </c>
-      <c r="I26" s="9" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>Only live timed sessions existed; a physical session with only an end page can't count pages.</t>
         </is>
       </c>
-      <c r="J26" s="9" t="inlineStr">
+      <c r="J26" s="10" t="inlineStr">
         <is>
           <t>POST /reading-sessions/log and a 'Log reading' form (book, day, minutes, from/to page, reflection) on the Journal and book page; both pages make them count.</t>
         </is>
       </c>
-      <c r="K26" s="9" t="inlineStr">
+      <c r="K26" s="10" t="inlineStr">
         <is>
           <t>backend/src/modules/reading-sessions/*, frontend/src/features/journal/LogSessionDialog.tsx</t>
         </is>
       </c>
-      <c r="L26" s="9" t="inlineStr"/>
-      <c r="M26" s="9" t="inlineStr">
+      <c r="L26" s="10" t="inlineStr"/>
+      <c r="M26" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N26" s="9" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="n">
+      <c r="A27" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>R1-08</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>Book page and details</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E27" s="10" t="inlineStr">
         <is>
           <t>Modal buttons silently do nothing without a matching edition</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>Circe (no editions) &gt; 'Start / Resume Reading Session'; Piranesi (physical only) &gt; 'Open Digital Reader'.</t>
         </is>
       </c>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="G27" s="10" t="inlineStr">
         <is>
           <t>Hidden, disabled, or explained.</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>Both silently go to the book page.</t>
         </is>
       </c>
-      <c r="I27" s="9" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>Modal buttons fell back to navigating to the book page.</t>
         </is>
       </c>
-      <c r="J27" s="9" t="inlineStr">
+      <c r="J27" s="10" t="inlineStr">
         <is>
           <t>Modal shows only working actions and explains/offers to add a copy otherwise.</t>
         </is>
       </c>
-      <c r="K27" s="9" t="inlineStr">
+      <c r="K27" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/library/BookQuickActionModal.tsx</t>
         </is>
       </c>
-      <c r="L27" s="9" t="inlineStr"/>
-      <c r="M27" s="9" t="inlineStr">
+      <c r="L27" s="10" t="inlineStr"/>
+      <c r="M27" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N27" s="9" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="n">
+      <c r="A28" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>R1-09</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>Tracking journal statistics</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D28" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E28" s="10" t="inlineStr">
         <is>
           <t>Statistics contradict themselves; language data messy</t>
         </is>
       </c>
-      <c r="F28" s="9" t="inlineStr">
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>Statistics &gt; Daily.</t>
         </is>
       </c>
-      <c r="G28" s="9" t="inlineStr">
+      <c r="G28" s="10" t="inlineStr">
         <is>
           <t>Consistent numbers.</t>
         </is>
       </c>
-      <c r="H28" s="9" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>Summary counts 1 session while the chart says 'No reading sessions in this period yet'; languages 'Unknown 6' and lowercase 'english 2'; 'Bunko' listed as an author.</t>
         </is>
       </c>
-      <c r="I28" s="9" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>The chart's empty state keyed on minutes, not sessions; language labels weren't normalised.</t>
         </is>
       </c>
-      <c r="J28" s="9" t="inlineStr">
+      <c r="J28" s="10" t="inlineStr">
         <is>
           <t>Chart distinguishes 'no sessions' from 'sessions under a minute'; languages shown as names. ('Bunko' as author was seed data; reading goals aren't in the SRS.)</t>
         </is>
       </c>
-      <c r="K28" s="9" t="inlineStr">
+      <c r="K28" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/statistics/ActivityChart.tsx, backend/src/modules/statistics/statistics.service.ts</t>
         </is>
       </c>
-      <c r="L28" s="9" t="inlineStr"/>
-      <c r="M28" s="9" t="inlineStr">
+      <c r="L28" s="10" t="inlineStr"/>
+      <c r="M28" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N28" s="9" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="n">
+      <c r="A29" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>R1-10</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>Library adding finding books</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E29" s="10" t="inlineStr">
         <is>
           <t>Catalogue search isn't typo-tolerant and is slow; no status on add</t>
         </is>
       </c>
-      <c r="F29" s="9" t="inlineStr">
+      <c r="F29" s="10" t="inlineStr">
         <is>
           <t>Add a book &gt; 'tomorow and tomorrow and tomorrow'.</t>
         </is>
       </c>
-      <c r="G29" s="9" t="inlineStr">
+      <c r="G29" s="10" t="inlineStr">
         <is>
           <t>The right book near the top.</t>
         </is>
       </c>
-      <c r="H29" s="9" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>After 6-8s: unrelated results. Confusing language chips; manual form lacks page count/cover; always added as Want to Read.</t>
         </is>
       </c>
-      <c r="I29" s="9" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>Google Books answered first with poor relevance; the universe check could hijack results; no caching; original language defaulted to 'Japanese'.</t>
         </is>
       </c>
-      <c r="J29" s="9" t="inlineStr">
+      <c r="J29" s="10" t="inlineStr">
         <is>
           <t>Open Library title search merged in; results ranked by title match; universe check only for named universes; searches cached an hour; choose Want to read / Reading now / Already read when adding; calm metadata line replaces off-palette chips. (Catalogue-side typo tolerance depends on the providers.)</t>
         </is>
       </c>
-      <c r="K29" s="9" t="inlineStr">
+      <c r="K29" s="10" t="inlineStr">
         <is>
           <t>backend/src/modules/metadata/metadata.service.ts, frontend/src/features/library/AddBookDialog.tsx</t>
         </is>
       </c>
-      <c r="L29" s="9" t="inlineStr"/>
-      <c r="M29" s="9" t="inlineStr">
+      <c r="L29" s="10" t="inlineStr"/>
+      <c r="M29" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N29" s="9" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="n">
+      <c r="A30" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>R1-11</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" s="10" t="inlineStr">
         <is>
           <t>Library adding finding books</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D30" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E30" s="10" t="inlineStr">
         <is>
           <t>'Remove from library' gave no visible response</t>
         </is>
       </c>
-      <c r="F30" s="9" t="inlineStr">
+      <c r="F30" s="10" t="inlineStr">
         <is>
           <t>Book page &gt; 'Remove from library'.</t>
         </is>
       </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="G30" s="10" t="inlineStr">
         <is>
           <t>A confirmation, then the book is gone.</t>
         </is>
       </c>
-      <c r="H30" s="9" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>Nothing visible; the book stayed.</t>
         </is>
       </c>
-      <c r="I30" s="9" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>Used the browser's native confirm(), which the tester never saw.</t>
         </is>
       </c>
-      <c r="J30" s="9" t="inlineStr">
+      <c r="J30" s="10" t="inlineStr">
         <is>
           <t>In-app confirmation dialog that says what's kept.</t>
         </is>
       </c>
-      <c r="K30" s="9" t="inlineStr">
+      <c r="K30" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/library/BookDetailPage.tsx</t>
         </is>
       </c>
-      <c r="L30" s="9" t="inlineStr"/>
-      <c r="M30" s="9" t="inlineStr">
+      <c r="L30" s="10" t="inlineStr"/>
+      <c r="M30" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N30" s="9" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="n">
+      <c r="A31" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>R1-12</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C31" s="10" t="inlineStr">
         <is>
           <t>Shelves organizing</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
+      <c r="E31" s="10" t="inlineStr">
         <is>
           <t>Odd shelf grouping, per-row scrollbars, inverted toggle</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr">
+      <c r="F31" s="10" t="inlineStr">
         <is>
           <t>Shelves &gt; All Volumes; Covers/Spines toggle; mobile.</t>
         </is>
       </c>
-      <c r="G31" s="9" t="inlineStr">
+      <c r="G31" s="10" t="inlineStr">
         <is>
           <t>Books share shelves; the active view is clear.</t>
         </is>
       </c>
-      <c r="H31" s="9" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>One book per tall row under its own title; every row has a scrollbar; the active toggle option is the dim one; the choice doesn't stick; arrows cover art on mobile.</t>
         </is>
       </c>
-      <c r="I31" s="9" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>Rows per one-book series/genre; overflow-x-auto made rows scroll vertically; active toggle was the dark pill; arrows forced visible on mobile.</t>
         </is>
       </c>
-      <c r="J31" s="9" t="inlineStr">
+      <c r="J31" s="10" t="inlineStr">
         <is>
           <t>Rows need two books; overflow-y hidden with a thin themed scrollbar; light active pill with aria-pressed, remembered; arrows on focus/hover only.</t>
         </is>
       </c>
-      <c r="K31" s="9" t="inlineStr">
+      <c r="K31" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/shelves/*</t>
         </is>
       </c>
-      <c r="L31" s="9" t="inlineStr"/>
-      <c r="M31" s="9" t="inlineStr">
+      <c r="L31" s="10" t="inlineStr"/>
+      <c r="M31" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N31" s="9" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="n">
+      <c r="A32" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>R1-13</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C32" s="10" t="inlineStr">
         <is>
           <t>Speed reliability</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="E32" s="10" t="inlineStr">
         <is>
           <t>Slow loads with little feedback</t>
         </is>
       </c>
-      <c r="F32" s="9" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t>Library, Shelves, book pages; status dropdown.</t>
         </is>
       </c>
-      <c r="G32" s="9" t="inlineStr">
+      <c r="G32" s="10" t="inlineStr">
         <is>
           <t>Fast, with placeholders.</t>
         </is>
       </c>
-      <c r="H32" s="9" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>Covers blank for 3-5s on every visit; a big modal spinner; status change ~3s while the old value still shows.</t>
         </is>
       </c>
-      <c r="I32" s="9" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>Opening a book ran series discovery and a cover search synchronously (2-3s); covers had no placeholder; status change waited for the server.</t>
         </is>
       </c>
-      <c r="J32" s="9" t="inlineStr">
+      <c r="J32" s="10" t="inlineStr">
         <is>
           <t>Both moved to the background (book fetch ~72 ms); lazy covers on a paper tint; skeleton in the modal; optimistic status updates.</t>
         </is>
       </c>
-      <c r="K32" s="9" t="inlineStr">
+      <c r="K32" s="10" t="inlineStr">
         <is>
           <t>backend/src/modules/library/library.service.ts, frontend/src/features/library/BookCover.tsx, frontend/src/lib/api/works.ts</t>
         </is>
       </c>
-      <c r="L32" s="9" t="inlineStr"/>
-      <c r="M32" s="9" t="inlineStr">
+      <c r="L32" s="10" t="inlineStr"/>
+      <c r="M32" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N32" s="9" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="n">
+      <c r="A33" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>R1-14</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>Notes highlights reviews</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="D33" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="E33" s="10" t="inlineStr">
         <is>
           <t>Reviews and notes are basic</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>Rated, reviewed, added and edited a note.</t>
         </is>
       </c>
-      <c r="G33" s="9" t="inlineStr">
+      <c r="G33" s="10" t="inlineStr">
         <is>
           <t>Half stars, dated notes, spoiler/private options.</t>
         </is>
       </c>
-      <c r="H33" s="9" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>Whole stars only; notes undated with only a 'Book' tag; highlights impossible (R1-01).</t>
         </is>
       </c>
-      <c r="I33" s="9" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>Notes showed no date; ratings are whole stars by SRS §14.</t>
         </is>
       </c>
-      <c r="J33" s="9" t="inlineStr">
+      <c r="J33" s="10" t="inlineStr">
         <is>
           <t>Notes show their date (and position); the review box says reviews and notes are private. Half stars not added: SRS §14 sets whole 5-star ratings.</t>
         </is>
       </c>
-      <c r="K33" s="9" t="inlineStr">
+      <c r="K33" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/notes/NotesPanel.tsx, frontend/src/features/reviews/ReviewPanel.tsx</t>
         </is>
       </c>
-      <c r="L33" s="9" t="inlineStr"/>
-      <c r="M33" s="9" t="inlineStr">
+      <c r="L33" s="10" t="inlineStr"/>
+      <c r="M33" s="10" t="inlineStr">
         <is>
           <t>Partly fixed</t>
         </is>
       </c>
-      <c r="N33" s="9" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="n">
+      <c r="A34" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>R1-15</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C34" s="10" t="inlineStr">
         <is>
           <t>Assistant chat</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="D34" s="10" t="inlineStr">
         <is>
           <t>polish</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="E34" s="10" t="inlineStr">
         <is>
           <t>Odd reply after declining a follow-up</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr">
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t>'rate piranesi 5 stars' &gt; asked to mark Finished &gt; 'nah not yet'.</t>
         </is>
       </c>
-      <c r="G34" s="9" t="inlineStr">
+      <c r="G34" s="10" t="inlineStr">
         <is>
           <t>'Okay, I'll leave it as Reading.'</t>
         </is>
       </c>
-      <c r="H34" s="9" t="inlineStr">
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>'Okay, I kept Piranesi.' (sounds like it nearly removed it).</t>
         </is>
       </c>
-      <c r="I34" s="9" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <t>The decline message was the generic 'Okay, I kept X.'</t>
         </is>
       </c>
-      <c r="J34" s="9" t="inlineStr">
+      <c r="J34" s="10" t="inlineStr">
         <is>
           <t>Follow-up offers can say what 'no' means (general core hook): 'Okay, Piranesi stays as Reading.'</t>
         </is>
       </c>
-      <c r="K34" s="9" t="inlineStr">
+      <c r="K34" s="10" t="inlineStr">
         <is>
           <t>backend/src/modules/assistant/domain/DomainPack.ts, backend/src/modules/assistant/AIRuntime.ts, backend/src/modules/assistant/domains/books/pipeline/replies.ts</t>
         </is>
       </c>
-      <c r="L34" s="9" t="inlineStr"/>
-      <c r="M34" s="9" t="inlineStr">
+      <c r="L34" s="10" t="inlineStr"/>
+      <c r="M34" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N34" s="9" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="n">
+      <c r="A35" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>R1-16</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>First impression onboarding</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="D35" s="10" t="inlineStr">
         <is>
           <t>polish</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E35" s="10" t="inlineStr">
         <is>
           <t>No forgot-password, no import of an existing history</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
+      <c r="F35" s="10" t="inlineStr">
         <is>
           <t>Login and register pages; Settings.</t>
         </is>
       </c>
-      <c r="G35" s="9" t="inlineStr">
+      <c r="G35" s="10" t="inlineStr">
         <is>
           <t>Forgot password; Goodreads/StoryGraph import.</t>
         </is>
       </c>
-      <c r="H35" s="9" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>Neither exists.</t>
         </is>
       </c>
-      <c r="I35" s="9" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <t>Password reset needs email delivery (none configured); importing other platforms is SRS §37, which needs product approval.</t>
         </is>
       </c>
-      <c r="J35" s="9" t="inlineStr">
+      <c r="J35" s="10" t="inlineStr">
         <is>
           <t>Not built. A first-run welcome now explains the three ways to start (add, read/log, assistant).</t>
         </is>
       </c>
-      <c r="K35" s="9" t="inlineStr">
+      <c r="K35" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/library/LibraryPage.tsx</t>
         </is>
       </c>
-      <c r="L35" s="9" t="inlineStr"/>
-      <c r="M35" s="9" t="inlineStr">
+      <c r="L35" s="10" t="inlineStr"/>
+      <c r="M35" s="10" t="inlineStr">
         <is>
           <t>Won't fix (needs approval)</t>
         </is>
       </c>
-      <c r="N35" s="9" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="n">
+      <c r="A36" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>R1-17</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>Look and feel</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>polish</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="E36" s="10" t="inlineStr">
         <is>
           <t>Sidebar scrolls away on long pages</t>
         </is>
       </c>
-      <c r="F36" s="9" t="inlineStr">
+      <c r="F36" s="10" t="inlineStr">
         <is>
           <t>Scrolled a long book page on desktop.</t>
         </is>
       </c>
-      <c r="G36" s="9" t="inlineStr">
+      <c r="G36" s="10" t="inlineStr">
         <is>
           <t>Navigation and Sign out stay in reach.</t>
         </is>
       </c>
-      <c r="H36" s="9" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>The sidebar scrolls with the content.</t>
         </is>
       </c>
-      <c r="I36" s="9" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>Sidebar wasn't sticky.</t>
         </is>
       </c>
-      <c r="J36" s="9" t="inlineStr">
+      <c r="J36" s="10" t="inlineStr">
         <is>
           <t>Sticky full-height sidebar on desktop.</t>
         </is>
       </c>
-      <c r="K36" s="9" t="inlineStr">
+      <c r="K36" s="10" t="inlineStr">
         <is>
           <t>frontend/src/components/layout/AppShell.tsx</t>
         </is>
       </c>
-      <c r="L36" s="9" t="inlineStr"/>
-      <c r="M36" s="9" t="inlineStr">
+      <c r="L36" s="10" t="inlineStr"/>
+      <c r="M36" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N36" s="9" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>What the tester liked</t>
         </is>
@@ -5054,7 +6046,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Round 2</t>
         </is>
@@ -5096,172 +6088,172 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>First impression onboarding</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Calm login and a 3-step welcome for a new account; quick sign-up. No Goodreads/StoryGraph import.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Library adding finding books</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Rich results and the status choice on add are lovely, but search took 10-15s, a one-letter typo found nothing, covers slow.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Book page and details</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Clean, nice privacy line, but rating/favourite silently lost without 'Save review'; no progress, dates or highlights on the page.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Reading experience</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Strong appearance panel, search, chapter jumps, resume; but no paragraph breaks, titles printed three times, highlights not drawn, no selection in 3D Flip, font change resets position, broken phone layout.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Tracking journal statistics</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Excellent manual log; but reflection Save does nothing, raw 'epubcfi(...)' in the journal, inflated session time, a stale session blocks new ones, no finish dates.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Shelves organizing</t>
         </is>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B11" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>Charming bookcase with genre rows, instant shelf creation; empty shelf can't add books, faint 'Covers' toggle, unlabeled tabs.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Notes highlights reviews</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>Good selection popover and margin notes; highlights not drawn, reader notes absent from the book page, no central notes view, no review confirmation.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Assistant chat</t>
         </is>
       </c>
-      <c r="B13" s="11" t="n">
+      <c r="B13" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>Exact commands and undo work, honest about the missing model, excellent privacy text; brittle with natural phrasing; 'dnf'd klara' added a different book.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Look and feel</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n">
+      <c r="B14" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>Feels hand-crafted for book lovers; some developer text and low-contrast controls.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Speed reliability</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n">
+      <c r="B15" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>Slow search and covers, logged out once on refresh, dead reflection save, stuck active session, shrunken reader after closing a session.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Overall</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n">
+      <c r="B16" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>Has the soul of a reader's app; reading/highlighting and session tracking still have rough edges.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Issues and fixes</t>
         </is>
@@ -5340,1735 +6332,1735 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="n">
+      <c r="A20" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>R2-01</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>Notes highlights reviews</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>Highlights are saved but never drawn on the page text</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>Paginated mode, selected a passage, chose green; reopened the book.</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>The passage shows green highlighting.</t>
         </is>
       </c>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>Listed in the Highlights panel, but the text stays plain.</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>Highlights were stored with their text and chapter but the reflowed pages were plain strings; nothing located the saved text on a page.</t>
         </is>
       </c>
-      <c r="J20" s="9" t="inlineStr">
+      <c r="J20" s="10" t="inlineStr">
         <is>
           <t>Each page now keeps the character offsets of its text, saved highlights are found in the chapter (forgiving line breaks) and drawn in their colour, stronger on light paper.</t>
         </is>
       </c>
-      <c r="K20" s="9" t="inlineStr">
+      <c r="K20" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/reader/flow-layout.ts, frontend/src/features/reader/FlowReaderPage.tsx</t>
         </is>
       </c>
-      <c r="L20" s="9" t="inlineStr"/>
-      <c r="M20" s="9" t="inlineStr">
+      <c r="L20" s="10" t="inlineStr"/>
+      <c r="M20" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N20" s="9" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="n">
+      <c r="A21" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>R2-02</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>Reading experience</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>Reflowed text has no paragraph breaks and repeats each chapter title</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>Opened the novella and turned pages.</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>Proper paragraphs; title once.</t>
         </is>
       </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>Each chapter is one block starting 'The Last Lantern The Last Lantern Aldmere had...' under a heading saying the same.</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>EPUB extraction stripped every tag and collapsed whitespace, so &lt;title&gt; + &lt;h1&gt; + paragraphs became one run ('The Last Lantern The Last Lantern Aldmere...').</t>
         </is>
       </c>
-      <c r="J21" s="9" t="inlineStr">
+      <c r="J21" s="10" t="inlineStr">
         <is>
           <t>Body only, one paragraph per block element, entities decoded, a heading that repeats the chapter title dropped; chapter graph v4 re-indexes existing books.</t>
         </is>
       </c>
-      <c r="K21" s="9" t="inlineStr">
+      <c r="K21" s="10" t="inlineStr">
         <is>
           <t>backend/src/modules/reader/epub-indexer.ts, backend/src/modules/reader/chapter-graph.ts</t>
         </is>
       </c>
-      <c r="L21" s="9" t="inlineStr"/>
-      <c r="M21" s="9" t="inlineStr">
+      <c r="L21" s="10" t="inlineStr"/>
+      <c r="M21" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N21" s="9" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="n">
+      <c r="A22" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>R2-03</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>Assistant chat</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>'dnf'd klara' added a different book</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F22" s="10" t="inlineStr">
         <is>
           <t>'dnf'd klara, the robot pov wasnt for me' with Klara and the Sun owned.</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>Mark Klara and the Sun DNF, or ask.</t>
         </is>
       </c>
-      <c r="H22" s="9" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>'I've added Klāre by Otto Hinnerk to your library as Did Not Finish.'</t>
         </is>
       </c>
-      <c r="I22" s="9" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>'klara' covered 1 of 4 title words (score 75 &lt; 80), so it wasn't treated as the owned book and the auto-add searched the catalogue.</t>
         </is>
       </c>
-      <c r="J22" s="9" t="inlineStr">
+      <c r="J22" s="10" t="inlineStr">
         <is>
           <t>A title's opening words name it (score 88); a near match to an owned title never auto-adds a stranger's book, the tool asks instead.</t>
         </is>
       </c>
-      <c r="K22" s="9" t="inlineStr">
+      <c r="K22" s="10" t="inlineStr">
         <is>
           <t>backend/src/modules/assistant/domains/books/text/match.ts, backend/src/modules/assistant/domains/books/pipeline/planChecks.ts</t>
         </is>
       </c>
-      <c r="L22" s="9" t="inlineStr"/>
-      <c r="M22" s="9" t="inlineStr">
+      <c r="L22" s="10" t="inlineStr"/>
+      <c r="M22" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N22" s="9" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="n">
+      <c r="A23" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>R2-04</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>Tracking journal statistics</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E23" s="10" t="inlineStr">
         <is>
           <t>Reflection 'Save' after a session does nothing</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F23" s="10" t="inlineStr">
         <is>
           <t>Reader X &gt; typed a reflection &gt; Save (x3).</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>Saves and closes.</t>
         </is>
       </c>
-      <c r="H23" s="9" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>Dialog stays open, no message; the reflection never reaches the Journal.</t>
         </is>
       </c>
-      <c r="I23" s="9" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>Save sent the end call again with a reflection; the server treated the already-ended session's new reflection as 'different data' (409) and the error was swallowed.</t>
         </is>
       </c>
-      <c r="J23" s="9" t="inlineStr">
+      <c r="J23" s="10" t="inlineStr">
         <is>
           <t>A reflection can follow the end (only when none exists); errors are shown; Save/Skip return to the book page.</t>
         </is>
       </c>
-      <c r="K23" s="9" t="inlineStr">
+      <c r="K23" s="10" t="inlineStr">
         <is>
           <t>backend/src/modules/reading-sessions/reading-sessions.service.ts, frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/reader/ReflectionPrompt.tsx</t>
         </is>
       </c>
-      <c r="L23" s="9" t="inlineStr"/>
-      <c r="M23" s="9" t="inlineStr">
+      <c r="L23" s="10" t="inlineStr"/>
+      <c r="M23" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N23" s="9" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="n">
+      <c r="A24" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>R2-05</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>Tracking journal statistics</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>A stale reader session blocks new sessions with a developer-style error</t>
         </is>
       </c>
-      <c r="F24" s="9" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>Left the reader by navigating away; later 'Start a reading session' on another book.</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>Start a timer, or offer to end the old one.</t>
         </is>
       </c>
-      <c r="H24" s="9" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>'Another session is already active for this user' and nothing shows or ends it.</t>
         </is>
       </c>
-      <c r="I24" s="9" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>Leaving the reader without closing it left the session ACTIVE; the 409 text was developer wording with no way out.</t>
         </is>
       </c>
-      <c r="J24" s="9" t="inlineStr">
+      <c r="J24" s="10" t="inlineStr">
         <is>
           <t>Leaving the reader pauses its session; the clash names the book ('You're still in a reading session for ...') and offers 'Pause that one and start here'.</t>
         </is>
       </c>
-      <c r="K24" s="9" t="inlineStr">
+      <c r="K24" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/library/SessionConflict.tsx, backend/src/modules/reading-sessions/reading-sessions.service.ts</t>
         </is>
       </c>
-      <c r="L24" s="9" t="inlineStr"/>
-      <c r="M24" s="9" t="inlineStr">
+      <c r="L24" s="10" t="inlineStr"/>
+      <c r="M24" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N24" s="9" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="n">
+      <c r="A25" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>R2-06</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>Tracking journal statistics</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="E25" s="10" t="inlineStr">
         <is>
           <t>Session time includes time away from the reader</t>
         </is>
       </c>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>Left the reader open in the background, came back, closed it.</t>
         </is>
       </c>
-      <c r="G25" s="9" t="inlineStr">
+      <c r="G25" s="10" t="inlineStr">
         <is>
           <t>Only active reading time.</t>
         </is>
       </c>
-      <c r="H25" s="9" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>'6 min of reading' for about a minute.</t>
         </is>
       </c>
-      <c r="I25" s="9" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>Duration was end minus start, including time away.</t>
         </is>
       </c>
-      <c r="J25" s="9" t="inlineStr">
+      <c r="J25" s="10" t="inlineStr">
         <is>
           <t>Sessions record paused time (pausedAt, pausedSeconds); a hidden tab pauses and resumes; the idle sweep pauses from the last page turn; paused time is subtracted.</t>
         </is>
       </c>
-      <c r="K25" s="9" t="inlineStr">
+      <c r="K25" s="10" t="inlineStr">
         <is>
           <t>backend/prisma/schema.prisma, backend/src/modules/reading-sessions/*, frontend/src/features/reader/FlowReaderPage.tsx</t>
         </is>
       </c>
-      <c r="L25" s="9" t="inlineStr"/>
-      <c r="M25" s="9" t="inlineStr">
+      <c r="L25" s="10" t="inlineStr"/>
+      <c r="M25" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N25" s="9" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="n">
+      <c r="A26" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>R2-07</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>Tracking journal statistics</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E26" s="10" t="inlineStr">
         <is>
           <t>Journal shows a raw internal position</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>Journal after a reader session.</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>'Chapter 4, 67%'.</t>
         </is>
       </c>
-      <c r="H26" s="9" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>'6 min · EPUB · epubcfi(/6/2!/4/2/1:0) → ch4'</t>
         </is>
       </c>
-      <c r="I26" s="9" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>The journal printed stored positions (CFI, chapter ids) as-is.</t>
         </is>
       </c>
-      <c r="J26" s="9" t="inlineStr">
+      <c r="J26" s="10" t="inlineStr">
         <is>
           <t>Entries carry startLabel/endLabel: chapter titles (from the chapter graph, CFIs by spine step), 'p. N' for pages.</t>
         </is>
       </c>
-      <c r="K26" s="9" t="inlineStr">
+      <c r="K26" s="10" t="inlineStr">
         <is>
           <t>backend/src/modules/journal/journal.service.ts, frontend/src/features/journal/JournalPage.tsx</t>
         </is>
       </c>
-      <c r="L26" s="9" t="inlineStr"/>
-      <c r="M26" s="9" t="inlineStr">
+      <c r="L26" s="10" t="inlineStr"/>
+      <c r="M26" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N26" s="9" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="n">
+      <c r="A27" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>R2-08</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>Reading experience</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E27" s="10" t="inlineStr">
         <is>
           <t>Can't select text in the default 3D Flip mode</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>Drag-select and double-click in 3D Flip.</t>
         </is>
       </c>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="G27" s="10" t="inlineStr">
         <is>
           <t>Text selects; highlight popover appears.</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>Dragging starts a page curl; only works after switching to Paginated, with no hint.</t>
         </is>
       </c>
-      <c r="I27" s="9" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>react-pageflip took mouse and touch input in 3D Flip mode, so a drag curled the page instead of selecting.</t>
         </is>
       </c>
-      <c r="J27" s="9" t="inlineStr">
+      <c r="J27" s="10" t="inlineStr">
         <is>
           <t>The flipbook no longer takes pointer input: text selects in every mode; pages turn with the buttons, arrow keys or a swipe.</t>
         </is>
       </c>
-      <c r="K27" s="9" t="inlineStr">
+      <c r="K27" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/reader/FlowReaderPage.tsx</t>
         </is>
       </c>
-      <c r="L27" s="9" t="inlineStr"/>
-      <c r="M27" s="9" t="inlineStr">
+      <c r="L27" s="10" t="inlineStr"/>
+      <c r="M27" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N27" s="9" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="n">
+      <c r="A28" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>R2-09</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>Reading experience</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D28" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E28" s="10" t="inlineStr">
         <is>
           <t>Phone reader shows ~6 lines in a tiny inset card</t>
         </is>
       </c>
-      <c r="F28" s="9" t="inlineStr">
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>Mobile 375x812, reader.</t>
         </is>
       </c>
-      <c r="G28" s="9" t="inlineStr">
+      <c r="G28" s="10" t="inlineStr">
         <is>
           <t>Text fills the screen.</t>
         </is>
       </c>
-      <c r="H28" s="9" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>Small inner card, ~6 lines per page; bookmark and View Original missing from the toolbar.</t>
         </is>
       </c>
-      <c r="I28" s="9" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>Pages were always A4 halves of a two-page spread, tiny on a phone; ten toolbar icons overflowed.</t>
         </is>
       </c>
-      <c r="J28" s="9" t="inlineStr">
+      <c r="J28" s="10" t="inlineStr">
         <is>
           <t>Below 768px one page fills the screen; Note, Translate, Music, View Original and 'Not where you left off?' move into a More menu.</t>
         </is>
       </c>
-      <c r="K28" s="9" t="inlineStr">
+      <c r="K28" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/ai/TranslatePanel.tsx</t>
         </is>
       </c>
-      <c r="L28" s="9" t="inlineStr"/>
-      <c r="M28" s="9" t="inlineStr">
+      <c r="L28" s="10" t="inlineStr"/>
+      <c r="M28" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N28" s="9" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="n">
+      <c r="A29" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>R2-10</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>Book page and details</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E29" s="10" t="inlineStr">
         <is>
           <t>Rating and Favourite silently lost without 'Save review'</t>
         </is>
       </c>
-      <c r="F29" s="9" t="inlineStr">
+      <c r="F29" s="10" t="inlineStr">
         <is>
           <t>Clicked 5 stars and Favourite, refreshed.</t>
         </is>
       </c>
-      <c r="G29" s="9" t="inlineStr">
+      <c r="G29" s="10" t="inlineStr">
         <is>
           <t>Saved instantly or warned.</t>
         </is>
       </c>
-      <c r="H29" s="9" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>All empty after refresh; no 'Saved' confirmation even when saving works.</t>
         </is>
       </c>
-      <c r="I29" s="9" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>Stars and Favourite only changed the form; nothing saved until 'Save review'.</t>
         </is>
       </c>
-      <c r="J29" s="9" t="inlineStr">
+      <c r="J29" s="10" t="inlineStr">
         <is>
           <t>Rating, favourite and reread save on click with a 'Saved.' note; unsaved review text is kept.</t>
         </is>
       </c>
-      <c r="K29" s="9" t="inlineStr">
+      <c r="K29" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/reviews/ReviewPanel.tsx</t>
         </is>
       </c>
-      <c r="L29" s="9" t="inlineStr"/>
-      <c r="M29" s="9" t="inlineStr">
+      <c r="L29" s="10" t="inlineStr"/>
+      <c r="M29" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N29" s="9" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="n">
+      <c r="A30" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>R2-11</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" s="10" t="inlineStr">
         <is>
           <t>Speed reliability</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D30" s="10" t="inlineStr">
         <is>
           <t>major</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E30" s="10" t="inlineStr">
         <is>
           <t>Logged out on refresh mid-session</t>
         </is>
       </c>
-      <c r="F30" s="9" t="inlineStr">
+      <c r="F30" s="10" t="inlineStr">
         <is>
           <t>~6 min after sign-in, refreshed the reader.</t>
         </is>
       </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="G30" s="10" t="inlineStr">
         <is>
           <t>Stay signed in.</t>
         </is>
       </c>
-      <c r="H30" s="9" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>Sent to /login, then landed on Library.</t>
         </is>
       </c>
-      <c r="I30" s="9" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>Refresh tokens rotate on every use; two refreshes with the same cookie (StrictMode's double restore, parallel 401s, several tabs reloading) made the loser look like token reuse and signed the reader out.</t>
         </is>
       </c>
-      <c r="J30" s="9" t="inlineStr">
+      <c r="J30" s="10" t="inlineStr">
         <is>
           <t>One refresh at a time: shared within a tab and serialised across tabs with a Web Lock; a failed refresh never clears a newer token.</t>
         </is>
       </c>
-      <c r="K30" s="9" t="inlineStr">
+      <c r="K30" s="10" t="inlineStr">
         <is>
           <t>frontend/src/lib/api/client.ts, frontend/src/lib/auth-context.tsx</t>
         </is>
       </c>
-      <c r="L30" s="9" t="inlineStr"/>
-      <c r="M30" s="9" t="inlineStr">
+      <c r="L30" s="10" t="inlineStr"/>
+      <c r="M30" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N30" s="9" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="n">
+      <c r="A31" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>R2-12</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C31" s="10" t="inlineStr">
         <is>
           <t>Reading experience</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
+      <c r="E31" s="10" t="inlineStr">
         <is>
           <t>Changing font size resets to the start</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr">
+      <c r="F31" s="10" t="inlineStr">
         <is>
           <t>Page 2 of 8 &gt; font +2.</t>
         </is>
       </c>
-      <c r="G31" s="9" t="inlineStr">
+      <c r="G31" s="10" t="inlineStr">
         <is>
           <t>Same passage.</t>
         </is>
       </c>
-      <c r="H31" s="9" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>'Page 1 of 10', back at chapter 1.</t>
         </is>
       </c>
-      <c r="I31" s="9" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>Re-pagination re-anchored to the chapter's first page, and the flipbook wasn't remounted at the new index.</t>
         </is>
       </c>
-      <c r="J31" s="9" t="inlineStr">
+      <c r="J31" s="10" t="inlineStr">
         <is>
           <t>Position is chapter + character offset; after any re-layout the reader lands on the page holding that passage.</t>
         </is>
       </c>
-      <c r="K31" s="9" t="inlineStr">
+      <c r="K31" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/reader/flow-layout.ts</t>
         </is>
       </c>
-      <c r="L31" s="9" t="inlineStr"/>
-      <c r="M31" s="9" t="inlineStr">
+      <c r="L31" s="10" t="inlineStr"/>
+      <c r="M31" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N31" s="9" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="n">
+      <c r="A32" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>R2-13</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C32" s="10" t="inlineStr">
         <is>
           <t>Reading experience</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="E32" s="10" t="inlineStr">
         <is>
           <t>'View Original' loses your place and has no way back</t>
         </is>
       </c>
-      <c r="F32" s="9" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t>At 67% &gt; View Original.</t>
         </is>
       </c>
-      <c r="G32" s="9" t="inlineStr">
+      <c r="G32" s="10" t="inlineStr">
         <is>
           <t>Same position; toggle back.</t>
         </is>
       </c>
-      <c r="H32" s="9" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>Opens at chapter 1, 0%; no side padding, default Times; only Close.</t>
         </is>
       </c>
-      <c r="I32" s="9" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>The original view ignored the reading view's position (epub.js only finds an idref with '#') and had only Close.</t>
         </is>
       </c>
-      <c r="J32" s="9" t="inlineStr">
+      <c r="J32" s="10" t="inlineStr">
         <is>
           <t>Opens at the chapter you were on; 'Back to reading view' button.</t>
         </is>
       </c>
-      <c r="K32" s="9" t="inlineStr">
+      <c r="K32" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/reader/ReaderPage.tsx, frontend/src/features/reader/EpubReader.tsx</t>
         </is>
       </c>
-      <c r="L32" s="9" t="inlineStr"/>
-      <c r="M32" s="9" t="inlineStr">
+      <c r="L32" s="10" t="inlineStr"/>
+      <c r="M32" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N32" s="9" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="n">
+      <c r="A33" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>R2-14</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>Reading experience</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="D33" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="E33" s="10" t="inlineStr">
         <is>
           <t>Reader renders shrunken after closing a session</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>X &gt; Session ended &gt; Skip.</t>
         </is>
       </c>
-      <c r="G33" s="9" t="inlineStr">
+      <c r="G33" s="10" t="inlineStr">
         <is>
           <t>Back to the library, or a normal reader.</t>
         </is>
       </c>
-      <c r="H33" s="9" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>A small card mid-screen; X vs Skip inconsistent.</t>
         </is>
       </c>
-      <c r="I33" s="9" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>The reflection prompt replaced the reader, and Save/Skip went 'back' in history, sometimes into the reading view of the ended session.</t>
         </is>
       </c>
-      <c r="J33" s="9" t="inlineStr">
+      <c r="J33" s="10" t="inlineStr">
         <is>
           <t>The prompt sits over the book; both readers return to the book page afterwards.</t>
         </is>
       </c>
-      <c r="K33" s="9" t="inlineStr">
+      <c r="K33" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/reader/ReaderPage.tsx</t>
         </is>
       </c>
-      <c r="L33" s="9" t="inlineStr"/>
-      <c r="M33" s="9" t="inlineStr">
+      <c r="L33" s="10" t="inlineStr"/>
+      <c r="M33" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N33" s="9" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="n">
+      <c r="A34" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>R2-15</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C34" s="10" t="inlineStr">
         <is>
           <t>Reading experience</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="D34" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="E34" s="10" t="inlineStr">
         <is>
           <t>Pages half empty; first spread's left page blank</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr">
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t>Read the first spreads on desktop.</t>
         </is>
       </c>
-      <c r="G34" s="9" t="inlineStr">
+      <c r="G34" s="10" t="inlineStr">
         <is>
           <t>Pages fill.</t>
         </is>
       </c>
-      <c r="H34" s="9" t="inlineStr">
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>Text stops two-thirds down; next spread has one line then a new chapter.</t>
         </is>
       </c>
-      <c r="I34" s="9" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <t>Pagination estimated characters per page (deliberately conservative) and the first page was laid out as a lone 'cover'.</t>
         </is>
       </c>
-      <c r="J34" s="9" t="inlineStr">
+      <c r="J34" s="10" t="inlineStr">
         <is>
           <t>Pages are measured with the real fonts in an offscreen copy of the page (about 97% full, nothing clipped); the cover slot is used only for a real cover.</t>
         </is>
       </c>
-      <c r="K34" s="9" t="inlineStr">
+      <c r="K34" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/reader/flow-layout.ts, frontend/src/features/reader/FlowReaderPage.tsx</t>
         </is>
       </c>
-      <c r="L34" s="9" t="inlineStr"/>
-      <c r="M34" s="9" t="inlineStr">
+      <c r="L34" s="10" t="inlineStr"/>
+      <c r="M34" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N34" s="9" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="n">
+      <c r="A35" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>R2-16</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>Reading experience</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="D35" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E35" s="10" t="inlineStr">
         <is>
           <t>'mins left' estimate depends on layout</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
+      <c r="F35" s="10" t="inlineStr">
         <is>
           <t>Changed font size, chapter list, mobile.</t>
         </is>
       </c>
-      <c r="G35" s="9" t="inlineStr">
+      <c r="G35" s="10" t="inlineStr">
         <is>
           <t>Stable estimate.</t>
         </is>
       </c>
-      <c r="H35" s="9" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>~32, ~40, ~68, ~50 at the same spot.</t>
         </is>
       </c>
-      <c r="I35" s="9" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <t>'mins left' was pages left x 4.</t>
         </is>
       </c>
-      <c r="J35" s="9" t="inlineStr">
+      <c r="J35" s="10" t="inlineStr">
         <is>
           <t>Progress and time left come from characters read (about 230 words a minute), the same at any font size.</t>
         </is>
       </c>
-      <c r="K35" s="9" t="inlineStr">
+      <c r="K35" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/reader/ReaderProgressScrubber.tsx</t>
         </is>
       </c>
-      <c r="L35" s="9" t="inlineStr"/>
-      <c r="M35" s="9" t="inlineStr">
+      <c r="L35" s="10" t="inlineStr"/>
+      <c r="M35" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N35" s="9" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="n">
+      <c r="A36" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>R2-17</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>Reading experience</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="E36" s="10" t="inlineStr">
         <is>
           <t>Arrow keys don't turn pages</t>
         </is>
       </c>
-      <c r="F36" s="9" t="inlineStr">
+      <c r="F36" s="10" t="inlineStr">
         <is>
           <t>Right arrow in the reader.</t>
         </is>
       </c>
-      <c r="G36" s="9" t="inlineStr">
+      <c r="G36" s="10" t="inlineStr">
         <is>
           <t>Next page.</t>
         </is>
       </c>
-      <c r="H36" s="9" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>Nothing.</t>
         </is>
       </c>
-      <c r="I36" s="9" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>No keyboard handling in the reading view.</t>
         </is>
       </c>
-      <c r="J36" s="9" t="inlineStr">
+      <c r="J36" s="10" t="inlineStr">
         <is>
           <t>Left/Right arrows and Page Up/Down turn pages (not while typing or in a dialog).</t>
         </is>
       </c>
-      <c r="K36" s="9" t="inlineStr">
+      <c r="K36" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/reader/FlowReaderPage.tsx</t>
         </is>
       </c>
-      <c r="L36" s="9" t="inlineStr"/>
-      <c r="M36" s="9" t="inlineStr">
+      <c r="L36" s="10" t="inlineStr"/>
+      <c r="M36" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N36" s="9" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="n">
+      <c r="A37" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>R2-18</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>Notes highlights reviews</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="D37" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr">
+      <c r="E37" s="10" t="inlineStr">
         <is>
           <t>Reader highlights/notes absent from the book page; no central notes view</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="F37" s="10" t="inlineStr">
         <is>
           <t>Highlight with a margin note &gt; book page.</t>
         </is>
       </c>
-      <c r="G37" s="9" t="inlineStr">
+      <c r="G37" s="10" t="inlineStr">
         <is>
           <t>Listed on the book page.</t>
         </is>
       </c>
-      <c r="H37" s="9" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>'Notes: No notes yet.'</t>
         </is>
       </c>
-      <c r="I37" s="9" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>The book page listed notes only; highlights lived in the reader.</t>
         </is>
       </c>
-      <c r="J37" s="9" t="inlineStr">
+      <c r="J37" s="10" t="inlineStr">
         <is>
           <t>'Highlights &amp; quotes' on the book page, newest first, with colour, margin note and a link back into the book. (A separate all-books notes page isn't built.)</t>
         </is>
       </c>
-      <c r="K37" s="9" t="inlineStr">
+      <c r="K37" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/notes/BookHighlights.tsx, frontend/src/features/library/BookDetailPage.tsx</t>
         </is>
       </c>
-      <c r="L37" s="9" t="inlineStr"/>
-      <c r="M37" s="9" t="inlineStr">
+      <c r="L37" s="10" t="inlineStr"/>
+      <c r="M37" s="10" t="inlineStr">
         <is>
           <t>Partly fixed</t>
         </is>
       </c>
-      <c r="N37" s="9" t="inlineStr"/>
+      <c r="N37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="n">
+      <c r="A38" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>R2-19</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>Assistant chat</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="D38" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E38" s="9" t="inlineStr">
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>Natural follow-ups and phrasing variants fail</t>
         </is>
       </c>
-      <c r="F38" s="9" t="inlineStr">
+      <c r="F38" s="10" t="inlineStr">
         <is>
           <t>'finsihed circe, 4 stars and put it on comfort reads', 'put it on comfort reads', 'put circe on comfort reads', 'actually undo that'.</t>
         </is>
       </c>
-      <c r="G38" s="9" t="inlineStr">
+      <c r="G38" s="10" t="inlineStr">
         <is>
           <t>Handled, or each simple command.</t>
         </is>
       </c>
-      <c r="H38" s="9" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>The same canned 'not set up' reply each time; a message typed while pending wasn't sent on Enter.</t>
         </is>
       </c>
-      <c r="I38" s="9" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>'put X on Y' needed the word 'shelf'; 'it' was bound to the previous turn's subject; 'actually undo that' wasn't recognised.</t>
         </is>
       </c>
-      <c r="J38" s="9" t="inlineStr">
+      <c r="J38" s="10" t="inlineStr">
         <is>
           <t>Shelves named without 'shelf' (and 'add X to Y' when Y is a shelf or X is theirs); 'it' is the book named in the same message; undo accepts fillers. The tester's sentence now does status, rating and shelf without a model.</t>
         </is>
       </c>
-      <c r="K38" s="9" t="inlineStr">
+      <c r="K38" s="10" t="inlineStr">
         <is>
           <t>backend/src/modules/assistant/domains/books/conversation/quickCommands.ts, backend/src/modules/assistant/domains/books/pipeline/preRoute.ts, backend/src/modules/assistant/domains/books/pipeline/undo.ts</t>
         </is>
       </c>
-      <c r="L38" s="9" t="inlineStr"/>
-      <c r="M38" s="9" t="inlineStr">
+      <c r="L38" s="10" t="inlineStr"/>
+      <c r="M38" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N38" s="9" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="n">
+      <c r="A39" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>R2-20</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>Tracking journal statistics</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr">
+      <c r="D39" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr">
+      <c r="E39" s="10" t="inlineStr">
         <is>
           <t>No finish dates, so 'this year' can't be answered</t>
         </is>
       </c>
-      <c r="F39" s="9" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>Marked books Finished; asked 'how many books did i read this year'.</t>
         </is>
       </c>
-      <c r="G39" s="9" t="inlineStr">
+      <c r="G39" s="10" t="inlineStr">
         <is>
           <t>Finish dates; yearly count.</t>
         </is>
       </c>
-      <c r="H39" s="9" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>'Bunko can only tell which were this year from logged reading sessions...'</t>
         </is>
       </c>
-      <c r="I39" s="9" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>No completion date was stored.</t>
         </is>
       </c>
-      <c r="J39" s="9" t="inlineStr">
+      <c r="J39" s="10" t="inlineStr">
         <is>
           <t>UserWork.finishedAt (SRS §18.2), set when marked Finished, backfilled from the last session; shown on the book page; 'this year' uses it.</t>
         </is>
       </c>
-      <c r="K39" s="9" t="inlineStr">
+      <c r="K39" s="10" t="inlineStr">
         <is>
           <t>backend/prisma/schema.prisma, backend/src/modules/library/library.service.ts, backend/src/modules/assistant/domains/books/conversation/libraryAnswers.ts, frontend/src/features/library/BookDetailPage.tsx</t>
         </is>
       </c>
-      <c r="L39" s="9" t="inlineStr"/>
-      <c r="M39" s="9" t="inlineStr">
+      <c r="L39" s="10" t="inlineStr"/>
+      <c r="M39" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N39" s="9" t="inlineStr"/>
+      <c r="N39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="n">
+      <c r="A40" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>R2-21</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="C40" s="10" t="inlineStr">
         <is>
           <t>Library adding finding books</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
+      <c r="D40" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr">
+      <c r="E40" s="10" t="inlineStr">
         <is>
           <t>Book search slow and typo-intolerant</t>
         </is>
       </c>
-      <c r="F40" s="9" t="inlineStr">
+      <c r="F40" s="10" t="inlineStr">
         <is>
           <t>'tomorow and tomorrow and tomorrow'.</t>
         </is>
       </c>
-      <c r="G40" s="9" t="inlineStr">
+      <c r="G40" s="10" t="inlineStr">
         <is>
           <t>Right book within a couple of seconds.</t>
         </is>
       </c>
-      <c r="H40" s="9" t="inlineStr">
+      <c r="H40" s="10" t="inlineStr">
         <is>
           <t>10-15s spinner, unrelated results.</t>
         </is>
       </c>
-      <c r="I40" s="9" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>Catalogue providers are slow on a cold query and have no fuzzy matching; results are cached for an hour after the first search.</t>
         </is>
       </c>
-      <c r="J40" s="9" t="inlineStr">
+      <c r="J40" s="10" t="inlineStr">
         <is>
           <t>Not changed this round (needs a provider-side change).</t>
         </is>
       </c>
-      <c r="K40" s="9" t="inlineStr"/>
-      <c r="L40" s="9" t="inlineStr"/>
-      <c r="M40" s="9" t="inlineStr">
+      <c r="K40" s="10" t="inlineStr"/>
+      <c r="L40" s="10" t="inlineStr"/>
+      <c r="M40" s="10" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="N40" s="9" t="inlineStr"/>
+      <c r="N40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="n">
+      <c r="A41" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>R2-22</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C41" s="10" t="inlineStr">
         <is>
           <t>Library adding finding books</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="D41" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr">
+      <c r="E41" s="10" t="inlineStr">
         <is>
           <t>Status doesn't follow reading; no progress shown</t>
         </is>
       </c>
-      <c r="F41" s="9" t="inlineStr">
+      <c r="F41" s="10" t="inlineStr">
         <is>
           <t>Read to 67%, back to Library.</t>
         </is>
       </c>
-      <c r="G41" s="9" t="inlineStr">
+      <c r="G41" s="10" t="inlineStr">
         <is>
           <t>Status Reading; progress on the card.</t>
         </is>
       </c>
-      <c r="H41" s="9" t="inlineStr">
+      <c r="H41" s="10" t="inlineStr">
         <is>
           <t>Still Want to Read; no progress; 'Continue Reading' before ever opening.</t>
         </is>
       </c>
-      <c r="I41" s="9" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>Opening a book never changed its status; the button always said 'Continue Reading'.</t>
         </is>
       </c>
-      <c r="J41" s="9" t="inlineStr">
+      <c r="J41" s="10" t="inlineStr">
         <is>
           <t>Starting or logging a session moves Want to Read to Reading (never Finished/DNF); 'Start reading' until the first session. (Progress on cards not built.)</t>
         </is>
       </c>
-      <c r="K41" s="9" t="inlineStr">
+      <c r="K41" s="10" t="inlineStr">
         <is>
           <t>backend/src/modules/library/library.service.ts, backend/src/modules/reading-sessions/reading-sessions.service.ts, frontend/src/features/library/ContinueReadingButton.tsx</t>
         </is>
       </c>
-      <c r="L41" s="9" t="inlineStr"/>
-      <c r="M41" s="9" t="inlineStr">
+      <c r="L41" s="10" t="inlineStr"/>
+      <c r="M41" s="10" t="inlineStr">
         <is>
           <t>Partly fixed</t>
         </is>
       </c>
-      <c r="N41" s="9" t="inlineStr"/>
+      <c r="N41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="n">
+      <c r="A42" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>R2-23</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C42" s="10" t="inlineStr">
         <is>
           <t>Tracking journal statistics</t>
         </is>
       </c>
-      <c r="D42" s="9" t="inlineStr">
+      <c r="D42" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E42" s="9" t="inlineStr">
+      <c r="E42" s="10" t="inlineStr">
         <is>
           <t>Languages 'Unknown 6' and lowercase 'english'; EPUB reading added no pages</t>
         </is>
       </c>
-      <c r="F42" s="9" t="inlineStr">
+      <c r="F42" s="10" t="inlineStr">
         <is>
           <t>Statistics &gt; Languages.</t>
         </is>
       </c>
-      <c r="G42" s="9" t="inlineStr">
+      <c r="G42" s="10" t="inlineStr">
         <is>
           <t>'English'; EPUB pages counted.</t>
         </is>
       </c>
-      <c r="H42" s="9" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>'Unknown 6 books', 'english 1 book'; pages read only from the manual log.</t>
         </is>
       </c>
-      <c r="I42" s="9" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>The page passed language names through Intl.DisplayNames, which reads 'english' as a valid code and returns it lowercased; books with no language said 'Unknown'.</t>
         </is>
       </c>
-      <c r="J42" s="9" t="inlineStr">
+      <c r="J42" s="10" t="inlineStr">
         <is>
           <t>Only codes are looked up, names are capitalised; missing language reads 'Not recorded'. (EPUB pages need a start position; unchanged.)</t>
         </is>
       </c>
-      <c r="K42" s="9" t="inlineStr">
+      <c r="K42" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/statistics/chart-format.ts, frontend/src/features/statistics/StatisticsPage.tsx</t>
         </is>
       </c>
-      <c r="L42" s="9" t="inlineStr"/>
-      <c r="M42" s="9" t="inlineStr">
+      <c r="L42" s="10" t="inlineStr"/>
+      <c r="M42" s="10" t="inlineStr">
         <is>
           <t>Partly fixed</t>
         </is>
       </c>
-      <c r="N42" s="9" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="n">
+      <c r="A43" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>R2-24</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t>Shelves organizing</t>
         </is>
       </c>
-      <c r="D43" s="9" t="inlineStr">
+      <c r="D43" s="10" t="inlineStr">
         <is>
           <t>minor</t>
         </is>
       </c>
-      <c r="E43" s="9" t="inlineStr">
+      <c r="E43" s="10" t="inlineStr">
         <is>
           <t>An empty shelf offers no way to add books</t>
         </is>
       </c>
-      <c r="F43" s="9" t="inlineStr">
+      <c r="F43" s="10" t="inlineStr">
         <is>
           <t>New shelf '2026 faves'.</t>
         </is>
       </c>
-      <c r="G43" s="9" t="inlineStr">
+      <c r="G43" s="10" t="inlineStr">
         <is>
           <t>An 'Add books' picker.</t>
         </is>
       </c>
-      <c r="H43" s="9" t="inlineStr">
+      <c r="H43" s="10" t="inlineStr">
         <is>
           <t>Text only, no button.</t>
         </is>
       </c>
-      <c r="I43" s="9" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>No way to add books from a shelf.</t>
         </is>
       </c>
-      <c r="J43" s="9" t="inlineStr">
+      <c r="J43" s="10" t="inlineStr">
         <is>
           <t>'Add books' on custom shelves and in the empty state: a searchable picker of library books.</t>
         </is>
       </c>
-      <c r="K43" s="9" t="inlineStr">
+      <c r="K43" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/shelves/AddToShelfDialog.tsx, frontend/src/features/shelves/ShelvesPage.tsx</t>
         </is>
       </c>
-      <c r="L43" s="9" t="inlineStr"/>
-      <c r="M43" s="9" t="inlineStr">
+      <c r="L43" s="10" t="inlineStr"/>
+      <c r="M43" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N43" s="9" t="inlineStr"/>
+      <c r="N43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="n">
+      <c r="A44" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>R2-25</t>
         </is>
       </c>
-      <c r="C44" s="9" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>Shelves organizing</t>
         </is>
       </c>
-      <c r="D44" s="9" t="inlineStr">
+      <c r="D44" s="10" t="inlineStr">
         <is>
           <t>polish</t>
         </is>
       </c>
-      <c r="E44" s="9" t="inlineStr">
+      <c r="E44" s="10" t="inlineStr">
         <is>
           <t>Low-contrast toggle and unlabeled shelf tabs</t>
         </is>
       </c>
-      <c r="F44" s="9" t="inlineStr">
+      <c r="F44" s="10" t="inlineStr">
         <is>
           <t>Shelves page.</t>
         </is>
       </c>
-      <c r="G44" s="9" t="inlineStr">
+      <c r="G44" s="10" t="inlineStr">
         <is>
           <t>Readable toggle; named tabs.</t>
         </is>
       </c>
-      <c r="H44" s="9" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
         <is>
           <t>'Covers' dark brown on near-black; tabs read as unnamed buttons; odd brown scrollbar strip.</t>
         </is>
       </c>
-      <c r="I44" s="9" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>Inactive toggle text at 70% opacity on near-black; dark wood scrollbar on the paper background.</t>
         </is>
       </c>
-      <c r="J44" s="9" t="inlineStr">
+      <c r="J44" s="10" t="inlineStr">
         <is>
           <t>Full-strength toggle text; shelf tabs say their name and count and report pressed state; light paper scrollbar.</t>
         </is>
       </c>
-      <c r="K44" s="9" t="inlineStr">
+      <c r="K44" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/shelves/ShelvesPage.tsx, frontend/src/index.css</t>
         </is>
       </c>
-      <c r="L44" s="9" t="inlineStr"/>
-      <c r="M44" s="9" t="inlineStr">
+      <c r="L44" s="10" t="inlineStr"/>
+      <c r="M44" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N44" s="9" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="n">
+      <c r="A45" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>R2-26</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>Tracking journal statistics</t>
         </is>
       </c>
-      <c r="D45" s="9" t="inlineStr">
+      <c r="D45" s="10" t="inlineStr">
         <is>
           <t>polish</t>
         </is>
       </c>
-      <c r="E45" s="9" t="inlineStr">
+      <c r="E45" s="10" t="inlineStr">
         <is>
           <t>Journal order wrong; entries can't be edited</t>
         </is>
       </c>
-      <c r="F45" s="9" t="inlineStr">
+      <c r="F45" s="10" t="inlineStr">
         <is>
           <t>Logged a session after another the same day.</t>
         </is>
       </c>
-      <c r="G45" s="9" t="inlineStr">
+      <c r="G45" s="10" t="inlineStr">
         <is>
           <t>Newest first; edit/delete.</t>
         </is>
       </c>
-      <c r="H45" s="9" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
         <is>
           <t>Newer entry below the older; clicking opens the book.</t>
         </is>
       </c>
-      <c r="I45" s="9" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>Journal sorted by start time, so a session logged after the fact sorted by when it began.</t>
         </is>
       </c>
-      <c r="J45" s="9" t="inlineStr">
+      <c r="J45" s="10" t="inlineStr">
         <is>
           <t>Sorted by when sessions ended. (Editing an entry isn't built.)</t>
         </is>
       </c>
-      <c r="K45" s="9" t="inlineStr">
+      <c r="K45" s="10" t="inlineStr">
         <is>
           <t>backend/src/modules/journal/journal.service.ts</t>
         </is>
       </c>
-      <c r="L45" s="9" t="inlineStr"/>
-      <c r="M45" s="9" t="inlineStr">
+      <c r="L45" s="10" t="inlineStr"/>
+      <c r="M45" s="10" t="inlineStr">
         <is>
           <t>Partly fixed</t>
         </is>
       </c>
-      <c r="N45" s="9" t="inlineStr"/>
+      <c r="N45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="n">
+      <c r="A46" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B46" s="9" t="inlineStr">
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t>R2-27</t>
         </is>
       </c>
-      <c r="C46" s="9" t="inlineStr">
+      <c r="C46" s="10" t="inlineStr">
         <is>
           <t>Book page and details</t>
         </is>
       </c>
-      <c r="D46" s="9" t="inlineStr">
+      <c r="D46" s="10" t="inlineStr">
         <is>
           <t>polish</t>
         </is>
       </c>
-      <c r="E46" s="9" t="inlineStr">
+      <c r="E46" s="10" t="inlineStr">
         <is>
           <t>Duplicate status, marketing-blurb synopsis, small icon issues</t>
         </is>
       </c>
-      <c r="F46" s="9" t="inlineStr">
+      <c r="F46" s="10" t="inlineStr">
         <is>
           <t>Book pages and reader toolbar.</t>
         </is>
       </c>
-      <c r="G46" s="9" t="inlineStr">
+      <c r="G46" s="10" t="inlineStr">
         <is>
           <t>One status control, clean synopsis, labelled icons.</t>
         </is>
       </c>
-      <c r="H46" s="9" t="inlineStr">
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>Pill plus dropdown; synopsis starts with press quotes; unlabeled icon; bookmark icon never fills.</t>
         </is>
       </c>
-      <c r="I46" s="9" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>Status showed as a pill and a dropdown; catalogue copy opens with press quotes; bookmark icon never reflected state.</t>
         </is>
       </c>
-      <c r="J46" s="9" t="inlineStr">
+      <c r="J46" s="10" t="inlineStr">
         <is>
           <t>One labelled status control; leading press quotes and ALL-CAPS banners trimmed for display; the bookmark fills when the chapter is bookmarked.</t>
         </is>
       </c>
-      <c r="K46" s="9" t="inlineStr">
+      <c r="K46" s="10" t="inlineStr">
         <is>
           <t>frontend/src/features/library/BookDetailPage.tsx, frontend/src/features/library/synopsis.ts, frontend/src/features/reader/FlowReaderPage.tsx</t>
         </is>
       </c>
-      <c r="L46" s="9" t="inlineStr"/>
-      <c r="M46" s="9" t="inlineStr">
+      <c r="L46" s="10" t="inlineStr"/>
+      <c r="M46" s="10" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="N46" s="9" t="inlineStr"/>
+      <c r="N46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="n">
+      <c r="A47" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B47" s="9" t="inlineStr">
+      <c r="B47" s="10" t="inlineStr">
         <is>
           <t>R2-28</t>
         </is>
       </c>
-      <c r="C47" s="9" t="inlineStr">
+      <c r="C47" s="10" t="inlineStr">
         <is>
           <t>First impression onboarding</t>
         </is>
       </c>
-      <c r="D47" s="9" t="inlineStr">
+      <c r="D47" s="10" t="inlineStr">
         <is>
           <t>polish</t>
         </is>
       </c>
-      <c r="E47" s="9" t="inlineStr">
+      <c r="E47" s="10" t="inlineStr">
         <is>
           <t>No import or account basics for switchers</t>
         </is>
       </c>
-      <c r="F47" s="9" t="inlineStr">
+      <c r="F47" s="10" t="inlineStr">
         <is>
           <t>Welcome screen and Settings.</t>
         </is>
       </c>
-      <c r="G47" s="9" t="inlineStr">
+      <c r="G47" s="10" t="inlineStr">
         <is>
           <t>Import, yearly goal, export, change password.</t>
         </is>
       </c>
-      <c r="H47" s="9" t="inlineStr">
+      <c r="H47" s="10" t="inlineStr">
         <is>
           <t>None present.</t>
         </is>
       </c>
-      <c r="I47" s="9" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>Import (SRS §37), reading goals, export and password change aren't in the MVP scope.</t>
         </is>
       </c>
-      <c r="J47" s="9" t="inlineStr">
+      <c r="J47" s="10" t="inlineStr">
         <is>
           <t>Not built; needs product approval.</t>
         </is>
       </c>
-      <c r="K47" s="9" t="inlineStr"/>
-      <c r="L47" s="9" t="inlineStr"/>
-      <c r="M47" s="9" t="inlineStr">
+      <c r="K47" s="10" t="inlineStr"/>
+      <c r="L47" s="10" t="inlineStr"/>
+      <c r="M47" s="10" t="inlineStr">
         <is>
           <t>Won't fix (needs approval)</t>
         </is>
       </c>
-      <c r="N47" s="9" t="inlineStr"/>
+      <c r="N47" s="10" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>What the tester liked</t>
         </is>
@@ -7106,6 +8098,1299 @@
       <c r="A54" t="inlineStr">
         <is>
           <t>The assistant does what it can reliably and reversibly, with a working undo.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="52" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Round 3</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Meera, book-lover persona (code-blind agent; browser only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Local: frontend :5174, API :3100; assistant model not configured (no NVIDIA_API_KEY). The seeded account's password reached the tester in a follow-up message, which its safety check refused to type, so it tested with a fresh account that had no EPUB: the reader was not tested this round.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Tester's reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>First impression onboarding</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Quick, warm sign-up and a helpful 3-step welcome; no Goodreads/StoryGraph import and wrong metadata in the first search.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Library adding finding books</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Own-library search and filters work; catalogue search ~5s and original language plainly wrong (Piranesi 'Written in Japanese').</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Book page and details</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Rating, favourite, shelves, notes, editions work; saved review blank after a refresh; description shows raw markdown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>not tested</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Not tested: no readable EPUB on the tester's account.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Tracking journal statistics</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Paper logging pleasant and validated, clean journal and stats; a timed session vanished on refresh, entries can't be edited or deleted, 'No genre: 5'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Shelves organizing</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Charming bookcase and add-books works; 'JAP' spine badge, nearly invisible Covers/Spines and Add books controls, no rename.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Notes highlights reviews</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Notes persist; a review that disappears on reload (with Save enabled) breaks trust.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Assistant chat</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Plain commands, undo, history all work; natural phrasing misread, odd alternatives, added an Indonesian edition of Circe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Look and feel</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Crafted for readers with good mobile nav; developer-ish copy and low-contrast controls.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Speed reliability</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>No errors or sign-outs; state that only appears after in-app navigation and 5-10s searches/replies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Bones and taste are there; data vanishing on refresh and wrong metadata stop a recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Issues and fixes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Round</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Root cause</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Fix</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Verified in round</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>R3-01</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Notes highlights reviews</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>Saved review is blank after a page refresh, and Save invites wiping it</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>Write a review, Save changes ('Saved.'), refresh the page.</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>Review text still there.</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>Box empty with Save enabled; in-app navigation shows it again.</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Regression from R2-10: the panel moved its 'last saved text' marker before React ran the state update, so on a fresh load the update compared against the new text and kept the empty draft.</t>
+        </is>
+      </c>
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>The previous value is captured before the marker moves; verified: text survives a refresh and Save stays disabled until edited.</t>
+        </is>
+      </c>
+      <c r="K20" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reviews/ReviewPanel.tsx</t>
+        </is>
+      </c>
+      <c r="L20" s="10" t="inlineStr"/>
+      <c r="M20" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>R3-02</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Shelves organizing</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>Spine language badge reads 'JAP'</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>Shelves &gt; Spines, a book marked Japanese.</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>A neutral code or no badge.</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>'JAP' on the spine, an ethnic slur.</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Spines printed the first three letters of the language name.</t>
+        </is>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>Two-letter ISO codes (JA, TA, ID); no badge when the language isn't known.</t>
+        </is>
+      </c>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/lib/language-code.ts, frontend/src/features/shelves/BookSpine.tsx</t>
+        </is>
+      </c>
+      <c r="L21" s="10" t="inlineStr"/>
+      <c r="M21" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N21" s="10" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>R3-03</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Library adding finding books</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>Original language wrong in search results and on the book</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>Add a book &gt; search 'piranesi', 'Convenience Store Woman'.</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>Piranesi original English; Murata original Japanese.</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>Every Open Library result 'Orig: Japanese'; Google Books Murata 'Orig: English'; carried into Shelves and Statistics.</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Book search filled in 'Japanese' as the original language whenever a catalogue didn't give one (Google's edition language was also used as the original).</t>
+        </is>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>Original language is left empty unless known; a migration clears the guessed value on existing books (where the edition isn't Japanese and the title has no Japanese script).</t>
+        </is>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
+        <is>
+          <t>backend/src/modules/metadata/metadata.service.ts, backend/prisma/migrations/20261023090000_clear_guessed_original_language</t>
+        </is>
+      </c>
+      <c r="L22" s="10" t="inlineStr"/>
+      <c r="M22" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N22" s="10" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>R3-04</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Assistant chat</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>Assistant added a foreign-language edition of Circe</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>'I just finished Circe by Madeline Miller, 4 stars'.</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>The English edition.</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>Indonesian description, 'IND' spine, Indonesian in Statistics.</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Two editions with the same title and author were de-duplicated first-come, and the Indonesian one arrived first.</t>
+        </is>
+      </c>
+      <c r="J23" s="10" t="inlineStr">
+        <is>
+          <t>De-duplication and ranking prefer the reader's language for Latin-script queries (other scripts unaffected).</t>
+        </is>
+      </c>
+      <c r="K23" s="10" t="inlineStr">
+        <is>
+          <t>backend/src/modules/metadata/metadata.service.ts</t>
+        </is>
+      </c>
+      <c r="L23" s="10" t="inlineStr"/>
+      <c r="M23" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>R3-05</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Book page and details</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>Description shows raw markdown</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>Piranesi's book page.</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>Formatted or plain text.</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>'**From the *New York Times* bestselling author...**' with asterisks.</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Some catalogues send markdown emphasis.</t>
+        </is>
+      </c>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>Shown as plain text (bold/italic markers removed; arithmetic asterisks left alone).</t>
+        </is>
+      </c>
+      <c r="K24" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/library/synopsis.ts</t>
+        </is>
+      </c>
+      <c r="L24" s="10" t="inlineStr"/>
+      <c r="M24" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>R3-06</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Tracking journal statistics</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>Active paper session disappears on refresh</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>Start a reading session, refresh.</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>Still in progress, with elapsed time.</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>'Start a reading session' again; no timer while running.</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>The paper-session panel only remembered its session in page state.</t>
+        </is>
+      </c>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>GET /reading-sessions/open restores it after a refresh; the panel shows 'Reading for N min · started 4:05 PM'.</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t>backend/src/modules/reading-sessions/*, frontend/src/lib/api/sessions.ts, frontend/src/features/library/PhysicalSessionPanel.tsx</t>
+        </is>
+      </c>
+      <c r="L25" s="10" t="inlineStr"/>
+      <c r="M25" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N25" s="10" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>R3-07</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Assistant chat</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>Natural phrasing becomes part of the title</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>'gave up on Klara and the Sun around halfway, it just wasn't for me'.</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>Klara and the Sun marked DNF.</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>'I couldn't find a book called Klara and the Sun around halfway' with unrelated alternatives.</t>
+        </is>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>After the comma was cut, 'around halfway' stayed in the title.</t>
+        </is>
+      </c>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>How-far phrases (halfway, page 120, 40%...) are dropped, and when one of the reader's titles opens the phrase, that title is used.</t>
+        </is>
+      </c>
+      <c r="K26" s="10" t="inlineStr">
+        <is>
+          <t>backend/src/modules/assistant/domains/books/conversation/quickCommands.ts</t>
+        </is>
+      </c>
+      <c r="L26" s="10" t="inlineStr"/>
+      <c r="M26" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N26" s="10" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>R3-08</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Shelves organizing</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>Shelf controls nearly invisible on dark wood</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>Shelves: Covers/Spines toggle and Add books.</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>Readable controls.</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>Dark text on dark brown.</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>The controls used wood-100, a colour step the palette doesn't define, so the class produced nothing; paper-600 and some moss steps (used in 36 files) were missing too.</t>
+        </is>
+      </c>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>Undefined shades replaced; paper-600, moss-200/400/800 added to the palette and DESIGN.md.</t>
+        </is>
+      </c>
+      <c r="K27" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/shelves/ShelvesPage.tsx, frontend/tailwind.config.js, DESIGN.md</t>
+        </is>
+      </c>
+      <c r="L27" s="10" t="inlineStr"/>
+      <c r="M27" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N27" s="10" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>R3-09</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Tracking journal statistics</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>Journal entries can't be edited or deleted</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>Try to remove an accidental 1-minute session.</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>Edit or delete per entry.</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>Entries only link to the book.</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>No delete for sessions.</t>
+        </is>
+      </c>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>Delete (with confirmation) on each journal entry: DELETE /reading-sessions/:id, finished sessions only; highlights and notes from it stay.</t>
+        </is>
+      </c>
+      <c r="K28" s="10" t="inlineStr">
+        <is>
+          <t>backend/src/modules/reading-sessions/*, frontend/src/features/journal/JournalPage.tsx, frontend/src/lib/api/journal.ts</t>
+        </is>
+      </c>
+      <c r="L28" s="10" t="inlineStr"/>
+      <c r="M28" s="10" t="inlineStr">
+        <is>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="N28" s="10" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>R3-10</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>First impression onboarding</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>No Goodreads/StoryGraph import</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>Settings and empty Library.</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>CSV import.</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Importing other platforms is SRS §37 (needs product approval).</t>
+        </is>
+      </c>
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>Not built.</t>
+        </is>
+      </c>
+      <c r="K29" s="10" t="inlineStr"/>
+      <c r="L29" s="10" t="inlineStr"/>
+      <c r="M29" s="10" t="inlineStr">
+        <is>
+          <t>Won't fix (needs approval)</t>
+        </is>
+      </c>
+      <c r="N29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>R3-11</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Assistant chat</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>polish</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>Contradictory status confirmation</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>'started The Left Hand of Darkness yesterday'.</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>'Added as Reading.'</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>'I've added ... as Want to Read. I've marked ... as Reading.'</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>The merged 'added as X' reply didn't match authors with initials ('Ursula K. Le Guin').</t>
+        </is>
+      </c>
+      <c r="J30" s="10" t="inlineStr">
+        <is>
+          <t>The author part may contain periods; one sentence now.</t>
+        </is>
+      </c>
+      <c r="K30" s="10" t="inlineStr">
+        <is>
+          <t>backend/src/modules/assistant/domains/books/pipeline/replies.ts</t>
+        </is>
+      </c>
+      <c r="L30" s="10" t="inlineStr"/>
+      <c r="M30" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N30" s="10" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>R3-12</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Look and feel</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>polish</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>Developer-ish or inconsistent wording</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>Shelves, Add book, Settings.</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>Consistent reader language.</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>'Catalog Racks &amp; Collections:', 'All Volumes' vs 'All Books', 'To Read', 'Parts Count', 'Your Added Language', source badges, 'search vectors', consent named differently on two pages.</t>
+        </is>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>Labels written from the code's point of view.</t>
+        </is>
+      </c>
+      <c r="J31" s="10" t="inlineStr">
+        <is>
+          <t>'Your shelves', 'All books', 'Want to Read', 'Parts'/'Chapters', 'Language you read it in', no source badges, 'a private search index', and the setting renamed 'Assistant and book summaries' to match the Assistant page.</t>
+        </is>
+      </c>
+      <c r="K31" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/shelves/ShelvesPage.tsx, frontend/src/features/library/AddBookDialog.tsx, frontend/src/features/ai/ai-disclosure.ts, frontend/src/features/ai/AiSettingsCard.tsx</t>
+        </is>
+      </c>
+      <c r="L31" s="10" t="inlineStr"/>
+      <c r="M31" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N31" s="10" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>R3-13</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Library adding finding books</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>polish</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>Manual add lacks status; adding a copy gives no feedback</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>Add custom book manually; Add a copy &gt; Physical copy.</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>Status choice; confirmation.</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>Silently Want to Read; no feedback.</t>
+        </is>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>The manual form had no status choice; adding a copy closed silently.</t>
+        </is>
+      </c>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>'Add it as' on the manual form too; 'Copy added. You can start reading it now.' (Page count isn't stored on a work.)</t>
+        </is>
+      </c>
+      <c r="K32" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/library/AddBookDialog.tsx, frontend/src/features/library/BookQuickActionModal.tsx</t>
+        </is>
+      </c>
+      <c r="L32" s="10" t="inlineStr"/>
+      <c r="M32" s="10" t="inlineStr">
+        <is>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="N32" s="10" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>R3-14</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Tracking journal statistics</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>polish</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>Statistics filler</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>Statistics with no EPUBs and no genres.</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>Caveats only when relevant.</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>'EPUB pages are estimated' with no EPUBs; a lone 'No genre: 5' bar.</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>Caveat always shown; an all-unknown breakdown drew one bar.</t>
+        </is>
+      </c>
+      <c r="J33" s="10" t="inlineStr">
+        <is>
+          <t>The EPUB caveat appears only with EPUB reading; 'None of your books has a genre recorded yet.' (Yearly goals and a ratings chart aren't in the SRS.)</t>
+        </is>
+      </c>
+      <c r="K33" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/statistics/StatisticsPage.tsx, frontend/src/features/statistics/BreakdownList.tsx</t>
+        </is>
+      </c>
+      <c r="L33" s="10" t="inlineStr"/>
+      <c r="M33" s="10" t="inlineStr">
+        <is>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="N33" s="10" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>R3-15</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>Book page and details</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>polish</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>Review buttons shown with only a rating</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>Rate a book with no review text.</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>'Remove review' hidden until a review exists.</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>Both buttons present.</t>
+        </is>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>The review buttons showed whenever a review row existed, including rating-only.</t>
+        </is>
+      </c>
+      <c r="J34" s="10" t="inlineStr">
+        <is>
+          <t>They appear only once there is review text.</t>
+        </is>
+      </c>
+      <c r="K34" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reviews/ReviewPanel.tsx</t>
+        </is>
+      </c>
+      <c r="L34" s="10" t="inlineStr"/>
+      <c r="M34" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N34" s="10" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>What the tester liked</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>The paper-reading flow: friendly page-order check, 'Logged 30 min of Piranesi, pages 1-42', 'Session saved - 1 min. Nice reading.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>The Shelves bookcase: wooden racks, serif spines, drag and keyboard rearranging.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>The Assistant's plain commands, a clear undo that says what it reversed, history that survives a refresh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Warm, calm design that adapts well to a phone: bottom tab bar, no horizontal scroll.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Honest privacy copy ('Private: only you can see your ratings, reviews and notes, so spoil away.').</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>The first-run three-step welcome.</t>
         </is>
       </c>
     </row>

--- a/docs/qa/blackbox-test-log.xlsx
+++ b/docs/qa/blackbox-test-log.xlsx
@@ -12,9 +12,10 @@
     <sheet name="Round 1" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Round 2" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Round 3" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Round 4" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All issues'!$A$1:$N$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All issues'!$A$1:$N$79</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -490,13 +491,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -527,6 +529,11 @@
           <t>Round 3</t>
         </is>
       </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Round 4</t>
+        </is>
+      </c>
     </row>
     <row r="4"/>
     <row r="5">
@@ -544,6 +551,9 @@
       <c r="D5" s="4" t="n">
         <v>7</v>
       </c>
+      <c r="E5" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -560,6 +570,9 @@
       <c r="D6" s="4" t="n">
         <v>5</v>
       </c>
+      <c r="E6" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -576,6 +589,9 @@
       <c r="D7" s="4" t="n">
         <v>5</v>
       </c>
+      <c r="E7" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -594,6 +610,9 @@
           <t>not tested</t>
         </is>
       </c>
+      <c r="E8" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -610,6 +629,9 @@
       <c r="D9" s="4" t="n">
         <v>7</v>
       </c>
+      <c r="E9" s="5" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -626,6 +648,9 @@
       <c r="D10" s="4" t="n">
         <v>6</v>
       </c>
+      <c r="E10" s="5" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -642,6 +667,9 @@
       <c r="D11" s="4" t="n">
         <v>5</v>
       </c>
+      <c r="E11" s="4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -658,6 +686,9 @@
       <c r="D12" s="4" t="n">
         <v>6</v>
       </c>
+      <c r="E12" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -674,6 +705,9 @@
       <c r="D13" s="4" t="n">
         <v>7</v>
       </c>
+      <c r="E13" s="5" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -690,6 +724,9 @@
       <c r="D14" s="4" t="n">
         <v>6</v>
       </c>
+      <c r="E14" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -706,6 +743,9 @@
       <c r="D15" s="4" t="n">
         <v>6</v>
       </c>
+      <c r="E15" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -722,6 +762,9 @@
       <c r="D16" s="3" t="n">
         <v>5</v>
       </c>
+      <c r="E16" s="3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -738,6 +781,9 @@
       <c r="D17" s="3" t="n">
         <v>15</v>
       </c>
+      <c r="E17" s="3" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -754,6 +800,9 @@
       <c r="D18" s="3" t="n">
         <v>11</v>
       </c>
+      <c r="E18" s="3" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -788,6 +837,18 @@
       <c r="B22" s="9" t="inlineStr">
         <is>
           <t>Local: frontend :5174, API :3100; assistant model not configured (no NVIDIA_API_KEY). The seeded account's password reached the tester in a follow-up message, which its safety check refused to type, so it tested with a fresh account that had no EPUB: the reader was not tested this round.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Round 4 (2026-10-23)</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Local: frontend :5174, API :3100; assistant model not configured (no NVIDIA_API_KEY). Browser pane already signed in to the seeded account with the readable EPUB; desktop (800px pane) and phone 375x812.</t>
         </is>
       </c>
     </row>
@@ -802,7 +863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N62"/>
+  <dimension ref="A1:N79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4602,8 +4663,1058 @@
       </c>
       <c r="N62" s="10" t="inlineStr"/>
     </row>
+    <row r="63">
+      <c r="A63" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>R4-01</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>Notes highlights reviews</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E63" s="10" t="inlineStr">
+        <is>
+          <t>Deleting one highlight also deleted another and its margin note</t>
+        </is>
+      </c>
+      <c r="F63" s="10" t="inlineStr">
+        <is>
+          <t>Reader &gt; Highlights (3) &gt; trash on the Quote, no feedback, click again.</t>
+        </is>
+      </c>
+      <c r="G63" s="10" t="inlineStr">
+        <is>
+          <t>Only the Quote deleted, with confirm or undo.</t>
+        </is>
+      </c>
+      <c r="H63" s="10" t="inlineStr">
+        <is>
+          <t>The Quote and the yellow highlight with its margin note both gone; no confirmation or feedback.</t>
+        </is>
+      </c>
+      <c r="I63" s="10" t="inlineStr">
+        <is>
+          <t>Deleting waited for the server before the list changed, so a second click landed on the next highlight as it slid up.</t>
+        </is>
+      </c>
+      <c r="J63" s="10" t="inlineStr">
+        <is>
+          <t>Highlights leave the list at once (restored if the delete fails), and deleting asks in place: Delete / Keep.</t>
+        </is>
+      </c>
+      <c r="K63" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/AnnotationsDrawer.tsx, frontend/src/lib/api/annotations.ts</t>
+        </is>
+      </c>
+      <c r="L63" s="10" t="inlineStr"/>
+      <c r="M63" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N63" s="10" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>R4-02</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>Current chapter wrong: footer, chapter list, bookmarks, notes</t>
+        </is>
+      </c>
+      <c r="F64" s="10" t="inlineStr">
+        <is>
+          <t>Turn pages with arrows in 3D Flip / scroll; bookmark in The Customs House; 'This chapter' note in A Ledger in Salt.</t>
+        </is>
+      </c>
+      <c r="G64" s="10" t="inlineStr">
+        <is>
+          <t>Everything names the chapter being read.</t>
+        </is>
+      </c>
+      <c r="H64" s="10" t="inlineStr">
+        <is>
+          <t>Footer lags 1-2 chapters; bookmark labelled and jumping to the wrong chapter; note saved as 'Chapter · ch1'.</t>
+        </is>
+      </c>
+      <c r="I64" s="10" t="inlineStr">
+        <is>
+          <t>The page-flip handler was memoised on the first render, before chapters loaded, so the chapter name never followed page turns; notes showed the stored chapter id.</t>
+        </is>
+      </c>
+      <c r="J64" s="10" t="inlineStr">
+        <is>
+          <t>The flip handler goes through a ref to the latest code; the chapter name is derived from the current chapter; notes carry positionLabel (the chapter title).</t>
+        </is>
+      </c>
+      <c r="K64" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/FlowReaderPage.tsx, backend/src/modules/notes/notes.service.ts, backend/src/modules/reader/position-labels.ts</t>
+        </is>
+      </c>
+      <c r="L64" s="10" t="inlineStr"/>
+      <c r="M64" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N64" s="10" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>R4-03</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="inlineStr">
+        <is>
+          <t>Scroll mode doesn't reopen where you left off</t>
+        </is>
+      </c>
+      <c r="F65" s="10" t="inlineStr">
+        <is>
+          <t>Scroll mode, go to The Customs House (~58%), refresh.</t>
+        </is>
+      </c>
+      <c r="G65" s="10" t="inlineStr">
+        <is>
+          <t>Reopens there.</t>
+        </is>
+      </c>
+      <c r="H65" s="10" t="inlineStr">
+        <is>
+          <t>Top of chapter 1 at 0% while the footer says another chapter.</t>
+        </is>
+      </c>
+      <c r="I65" s="10" t="inlineStr">
+        <is>
+          <t>Scroll mode tried to scroll before its chapters were on screen, and tracked position with requestAnimationFrame, which stalls in a background tab, so offsets stayed at 0.</t>
+        </is>
+      </c>
+      <c r="J65" s="10" t="inlineStr">
+        <is>
+          <t>Position is chapter + offset in scroll mode too, restored once the chapters render; tracking uses a timer.</t>
+        </is>
+      </c>
+      <c r="K65" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/FlowReaderPage.tsx</t>
+        </is>
+      </c>
+      <c r="L65" s="10" t="inlineStr"/>
+      <c r="M65" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N65" s="10" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>R4-04</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>View Original's first chapter broken; switching views loses place</t>
+        </is>
+      </c>
+      <c r="F66" s="10" t="inlineStr">
+        <is>
+          <t>At A Ledger in Salt, View Original, then Back to reading view.</t>
+        </is>
+      </c>
+      <c r="G66" s="10" t="inlineStr">
+        <is>
+          <t>Same spot, normal layout, place kept.</t>
+        </is>
+      </c>
+      <c r="H66" s="10" t="inlineStr">
+        <is>
+          <t>Huge heading, paragraphs in 4-5 narrow columns, opens at chapter 1, 0% / '20 min left'; back in reading view at 0%; ~2s blank page per turn; no highlights.</t>
+        </is>
+      </c>
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>The original-file view treated the first section of any book as a cover (narrow columns); position loss came from R4-03; the time estimate was guessed from chapter counts.</t>
+        </is>
+      </c>
+      <c r="J66" s="10" t="inlineStr">
+        <is>
+          <t>Only a section marked as a cover is laid out as one; the place carries both ways; no time guess in the original view. (Page-turn blanking and highlights in the original view unchanged.)</t>
+        </is>
+      </c>
+      <c r="K66" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/EpubReader.tsx, frontend/src/features/reader/ReaderPage.tsx</t>
+        </is>
+      </c>
+      <c r="L66" s="10" t="inlineStr"/>
+      <c r="M66" s="10" t="inlineStr">
+        <is>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="N66" s="10" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>R4-05</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>Book page and details</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E67" s="10" t="inlineStr">
+        <is>
+          <t>Finish date can't be set or changed</t>
+        </is>
+      </c>
+      <c r="F67" s="10" t="inlineStr">
+        <is>
+          <t>Finish a book; add as 'Already read'; 'finally finished circe last night, 4 stars'.</t>
+        </is>
+      </c>
+      <c r="G67" s="10" t="inlineStr">
+        <is>
+          <t>Editable date; 'last night' = yesterday.</t>
+        </is>
+      </c>
+      <c r="H67" s="10" t="inlineStr">
+        <is>
+          <t>Plain text; 'Already read' stamps today (inflating this year's count); Circe got today.</t>
+        </is>
+      </c>
+      <c r="I67" s="10" t="inlineStr">
+        <is>
+          <t>finishedAt could only be 'now'; 'Already read' dated today; the assistant ignored 'last night'.</t>
+        </is>
+      </c>
+      <c r="J67" s="10" t="inlineStr">
+        <is>
+          <t>Editable 'Finished on' date (PATCH /works finishedAt, no future dates); 'Already read' starts undated; 'finished X last night' dates it yesterday and says so.</t>
+        </is>
+      </c>
+      <c r="K67" s="10" t="inlineStr">
+        <is>
+          <t>backend/src/modules/library/*, frontend/src/features/library/BookDetailPage.tsx, frontend/src/features/library/AddBookDialog.tsx, backend/src/modules/assistant/domains/books/actions/libraryTools.ts, backend/src/modules/assistant/domains/books/conversation/quickCommands.ts</t>
+        </is>
+      </c>
+      <c r="L67" s="10" t="inlineStr"/>
+      <c r="M67" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N67" s="10" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>R4-06</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E68" s="10" t="inlineStr">
+        <is>
+          <t>Search result jumps to the chapter, not the match</t>
+        </is>
+      </c>
+      <c r="F68" s="10" t="inlineStr">
+        <is>
+          <t>Search 'ledger', click a result.</t>
+        </is>
+      </c>
+      <c r="G68" s="10" t="inlineStr">
+        <is>
+          <t>Scroll to and mark the match; search box focused.</t>
+        </is>
+      </c>
+      <c r="H68" s="10" t="inlineStr">
+        <is>
+          <t>Top of chapter, nothing marked; first typing lost.</t>
+        </is>
+      </c>
+      <c r="I68" s="10" t="inlineStr">
+        <is>
+          <t>Search results carried only the chapter; the box wasn't focused.</t>
+        </is>
+      </c>
+      <c r="J68" s="10" t="inlineStr">
+        <is>
+          <t>Jumps to the page with the match, marks the words for a few seconds; the box is focused.</t>
+        </is>
+      </c>
+      <c r="K68" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/reader/InBookSearchDrawer.tsx</t>
+        </is>
+      </c>
+      <c r="L68" s="10" t="inlineStr"/>
+      <c r="M68" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N68" s="10" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>R4-07</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E69" s="10" t="inlineStr">
+        <is>
+          <t>No end-of-book moment</t>
+        </is>
+      </c>
+      <c r="F69" s="10" t="inlineStr">
+        <is>
+          <t>Read to 100%.</t>
+        </is>
+      </c>
+      <c r="G69" s="10" t="inlineStr">
+        <is>
+          <t>Offer to mark finished / rate.</t>
+        </is>
+      </c>
+      <c r="H69" s="10" t="inlineStr">
+        <is>
+          <t>Nothing; '1 min left' at 100%; status stays Reading.</t>
+        </is>
+      </c>
+      <c r="I69" s="10" t="inlineStr">
+        <is>
+          <t>No handling of the last page.</t>
+        </is>
+      </c>
+      <c r="J69" s="10" t="inlineStr">
+        <is>
+          <t>'The end. Finished &lt;title&gt;?' with Mark as finished; 'Last page' instead of '1 min left'.</t>
+        </is>
+      </c>
+      <c r="K69" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/reader/ReaderProgressScrubber.tsx</t>
+        </is>
+      </c>
+      <c r="L69" s="10" t="inlineStr"/>
+      <c r="M69" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N69" s="10" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B70" s="10" t="inlineStr">
+        <is>
+          <t>R4-08</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>Library adding finding books</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>Add-book search slow, labels confusing</t>
+        </is>
+      </c>
+      <c r="F70" s="10" t="inlineStr">
+        <is>
+          <t>Search 'The Housekeeper and the Professor'.</t>
+        </is>
+      </c>
+      <c r="G70" s="10" t="inlineStr">
+        <is>
+          <t>Fast results, clear labels.</t>
+        </is>
+      </c>
+      <c r="H70" s="10" t="inlineStr">
+        <is>
+          <t>~16s; 'Added: English' badge on every result; leading 'The' dropped.</t>
+        </is>
+      </c>
+      <c r="I70" s="10" t="inlineStr">
+        <is>
+          <t>Coloured chips per result ('Added: English' meant the language you'd read it in).</t>
+        </is>
+      </c>
+      <c r="J70" s="10" t="inlineStr">
+        <is>
+          <t>One quiet line ('Originally Japanese · 14 chapters'), synopsis cleaned. (Catalogue speed unchanged.)</t>
+        </is>
+      </c>
+      <c r="K70" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/library/AddBookDialog.tsx</t>
+        </is>
+      </c>
+      <c r="L70" s="10" t="inlineStr"/>
+      <c r="M70" s="10" t="inlineStr">
+        <is>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="N70" s="10" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B71" s="10" t="inlineStr">
+        <is>
+          <t>R4-09</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>Library adding finding books</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>Library search can't combine author and title; no metadata editing</t>
+        </is>
+      </c>
+      <c r="F71" s="10" t="inlineStr">
+        <is>
+          <t>Search 'ishiguro klara'; try to fix an author/cover.</t>
+        </is>
+      </c>
+      <c r="G71" s="10" t="inlineStr">
+        <is>
+          <t>Finds the book; an Edit option.</t>
+        </is>
+      </c>
+      <c r="H71" s="10" t="inlineStr">
+        <is>
+          <t>No match; no edit; inconsistent placeholder covers.</t>
+        </is>
+      </c>
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t>Library search matched the whole phrase against title or author.</t>
+        </is>
+      </c>
+      <c r="J71" s="10" t="inlineStr">
+        <is>
+          <t>Each word must match the title or an author. (Editing book details isn't built: works are shared catalogue entries.)</t>
+        </is>
+      </c>
+      <c r="K71" s="10" t="inlineStr">
+        <is>
+          <t>backend/src/modules/library/library.service.ts</t>
+        </is>
+      </c>
+      <c r="L71" s="10" t="inlineStr"/>
+      <c r="M71" s="10" t="inlineStr">
+        <is>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="N71" s="10" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>R4-10</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>Book page and details</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>'Open the book' on a highlight doesn't go to it</t>
+        </is>
+      </c>
+      <c r="F72" s="10" t="inlineStr">
+        <is>
+          <t>Book page &gt; Highlights &gt; Open the book.</t>
+        </is>
+      </c>
+      <c r="G72" s="10" t="inlineStr">
+        <is>
+          <t>Opens at that highlight.</t>
+        </is>
+      </c>
+      <c r="H72" s="10" t="inlineStr">
+        <is>
+          <t>Opens at the last position.</t>
+        </is>
+      </c>
+      <c r="I72" s="10" t="inlineStr">
+        <is>
+          <t>The link opened the book at the last position.</t>
+        </is>
+      </c>
+      <c r="J72" s="10" t="inlineStr">
+        <is>
+          <t>'Read it in the book' opens the reader at that highlight.</t>
+        </is>
+      </c>
+      <c r="K72" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/notes/BookHighlights.tsx, frontend/src/features/reader/FlowReaderPage.tsx</t>
+        </is>
+      </c>
+      <c r="L72" s="10" t="inlineStr"/>
+      <c r="M72" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N72" s="10" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B73" s="10" t="inlineStr">
+        <is>
+          <t>R4-11</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>Notes highlights reviews</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E73" s="10" t="inlineStr">
+        <is>
+          <t>Highlights can't be edited from the page; weak feedback</t>
+        </is>
+      </c>
+      <c r="F73" s="10" t="inlineStr">
+        <is>
+          <t>Click a highlight; save one with a note or a Quote.</t>
+        </is>
+      </c>
+      <c r="G73" s="10" t="inlineStr">
+        <is>
+          <t>Edit/recolour/delete on click; confirmation.</t>
+        </is>
+      </c>
+      <c r="H73" s="10" t="inlineStr">
+        <is>
+          <t>Nothing on click; no confirmation; toolbar covers the selection; quotes cut off; raw colour names.</t>
+        </is>
+      </c>
+      <c r="I73" s="10" t="inlineStr">
+        <is>
+          <t>Highlights on the page weren't interactive; saving was silent.</t>
+        </is>
+      </c>
+      <c r="J73" s="10" t="inlineStr">
+        <is>
+          <t>Tapping a highlight opens your highlights; 'Highlight saved' / 'Quote saved' notice; colour labels replaced by a swatch.</t>
+        </is>
+      </c>
+      <c r="K73" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/reader/AnnotationsDrawer.tsx</t>
+        </is>
+      </c>
+      <c r="L73" s="10" t="inlineStr"/>
+      <c r="M73" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N73" s="10" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B74" s="10" t="inlineStr">
+        <is>
+          <t>R4-12</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>Dark theme leaves light surfaces</t>
+        </is>
+      </c>
+      <c r="F74" s="10" t="inlineStr">
+        <is>
+          <t>Appearance &gt; Dark.</t>
+        </is>
+      </c>
+      <c r="G74" s="10" t="inlineStr">
+        <is>
+          <t>Whole reader dark.</t>
+        </is>
+      </c>
+      <c r="H74" s="10" t="inlineStr">
+        <is>
+          <t>Progress bar and Appearance panel stay cream; stray horizontal scrollbar.</t>
+        </is>
+      </c>
+      <c r="I74" s="10" t="inlineStr">
+        <is>
+          <t>The progress bar used fixed cream colours.</t>
+        </is>
+      </c>
+      <c r="J74" s="10" t="inlineStr">
+        <is>
+          <t>It takes the reading theme's colours. (The Appearance panel stays light.)</t>
+        </is>
+      </c>
+      <c r="K74" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/ReaderProgressScrubber.tsx</t>
+        </is>
+      </c>
+      <c r="L74" s="10" t="inlineStr"/>
+      <c r="M74" s="10" t="inlineStr">
+        <is>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="N74" s="10" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
+          <t>R4-13</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>Menus don't close with Escape or an outside click</t>
+        </is>
+      </c>
+      <c r="F75" s="10" t="inlineStr">
+        <is>
+          <t>Open the bookmarks dropdown or the phone '...' menu.</t>
+        </is>
+      </c>
+      <c r="G75" s="10" t="inlineStr">
+        <is>
+          <t>Closes.</t>
+        </is>
+      </c>
+      <c r="H75" s="10" t="inlineStr">
+        <is>
+          <t>Stays open; two menus open at once.</t>
+        </is>
+      </c>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>No Escape or outside-click handling.</t>
+        </is>
+      </c>
+      <c r="J75" s="10" t="inlineStr">
+        <is>
+          <t>Escape closes menus and panels; clicking outside closes the dropdowns.</t>
+        </is>
+      </c>
+      <c r="K75" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/FlowReaderPage.tsx</t>
+        </is>
+      </c>
+      <c r="L75" s="10" t="inlineStr"/>
+      <c r="M75" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N75" s="10" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B76" s="10" t="inlineStr">
+        <is>
+          <t>R4-14</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>Tracking journal statistics</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>Tiny accidental sessions; inconsistent page fields</t>
+        </is>
+      </c>
+      <c r="F76" s="10" t="inlineStr">
+        <is>
+          <t>Open and close a book within a minute; compare Log reading and ending a timed session.</t>
+        </is>
+      </c>
+      <c r="G76" s="10" t="inlineStr">
+        <is>
+          <t>Very short visits not logged; same page fields.</t>
+        </is>
+      </c>
+      <c r="H76" s="10" t="inlineStr">
+        <is>
+          <t>'Under a minute' sessions counted; free-text vs numeric page fields.</t>
+        </is>
+      </c>
+      <c r="I76" s="10" t="inlineStr">
+        <is>
+          <t>Every opened reader session was kept.</t>
+        </is>
+      </c>
+      <c r="J76" s="10" t="inlineStr">
+        <is>
+          <t>Closing a book within a minute leaves no journal entry. (The paper-session form still asks for a chapter or page as text, which SRS §12.9 requires.)</t>
+        </is>
+      </c>
+      <c r="K76" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/FlowReaderPage.tsx</t>
+        </is>
+      </c>
+      <c r="L76" s="10" t="inlineStr"/>
+      <c r="M76" s="10" t="inlineStr">
+        <is>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="N76" s="10" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B77" s="10" t="inlineStr">
+        <is>
+          <t>R4-15</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>Assistant chat</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E77" s="10" t="inlineStr">
+        <is>
+          <t>Natural shelf request answered with a list</t>
+        </is>
+      </c>
+      <c r="F77" s="10" t="inlineStr">
+        <is>
+          <t>'can you put klara on my comfort reads shelf'.</t>
+        </is>
+      </c>
+      <c r="G77" s="10" t="inlineStr">
+        <is>
+          <t>Adds it or asks.</t>
+        </is>
+      </c>
+      <c r="H77" s="10" t="inlineStr">
+        <is>
+          <t>Listed the shelf; 'something like piranesi' ignored.</t>
+        </is>
+      </c>
+      <c r="I77" s="10" t="inlineStr">
+        <is>
+          <t>'can you ...' read as a question, so it was answered from the library.</t>
+        </is>
+      </c>
+      <c r="J77" s="10" t="inlineStr">
+        <is>
+          <t>Polite requests ('can you put ...?') are commands.</t>
+        </is>
+      </c>
+      <c r="K77" s="10" t="inlineStr">
+        <is>
+          <t>backend/src/modules/assistant/domains/books/pipeline/preRoute.ts</t>
+        </is>
+      </c>
+      <c r="L77" s="10" t="inlineStr"/>
+      <c r="M77" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N77" s="10" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B78" s="10" t="inlineStr">
+        <is>
+          <t>R4-16</t>
+        </is>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>Look and feel</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>polish</t>
+        </is>
+      </c>
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>Developer-ish text and cramped phone layouts</t>
+        </is>
+      </c>
+      <c r="F78" s="10" t="inlineStr">
+        <is>
+          <t>Desktop and phone.</t>
+        </is>
+      </c>
+      <c r="G78" s="10" t="inlineStr">
+        <is>
+          <t>Reader wording, tidy phone layouts.</t>
+        </is>
+      </c>
+      <c r="H78" s="10" t="inlineStr">
+        <is>
+          <t>'CHAPTERS / TOC', 'Chapter · ch1', 'Drag, or use the keyboard' on phone, small chapter titles, cramped Editions header and Journal dates, full-screen Appearance sheet.</t>
+        </is>
+      </c>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>Leftover technical labels; fixed heading size; dates squeezing journal entries on phones.</t>
+        </is>
+      </c>
+      <c r="J78" s="10" t="inlineStr">
+        <is>
+          <t>'Chapters', plainer shelves subtitle, chapter titles a step above body text, journal dates above the title on phones.</t>
+        </is>
+      </c>
+      <c r="K78" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/ReaderPage.tsx, frontend/src/features/shelves/ShelvesPage.tsx, frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/journal/JournalPage.tsx</t>
+        </is>
+      </c>
+      <c r="L78" s="10" t="inlineStr"/>
+      <c r="M78" s="10" t="inlineStr">
+        <is>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="N78" s="10" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>R4-17</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>Speed reliability</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>polish</t>
+        </is>
+      </c>
+      <c r="E79" s="10" t="inlineStr">
+        <is>
+          <t>Blank spinner on every full page load</t>
+        </is>
+      </c>
+      <c r="F79" s="10" t="inlineStr">
+        <is>
+          <t>Refresh any page.</t>
+        </is>
+      </c>
+      <c r="G79" s="10" t="inlineStr">
+        <is>
+          <t>App shell immediately.</t>
+        </is>
+      </c>
+      <c r="H79" s="10" t="inlineStr">
+        <is>
+          <t>1-2s blank page; typing lost; 'Maximum update depth exceeded' and some 404s in the console.</t>
+        </is>
+      </c>
+      <c r="I79" s="10" t="inlineStr">
+        <is>
+          <t>The app waits for the session to be restored before drawing anything.</t>
+        </is>
+      </c>
+      <c r="J79" s="10" t="inlineStr">
+        <is>
+          <t>Not changed this round.</t>
+        </is>
+      </c>
+      <c r="K79" s="10" t="inlineStr"/>
+      <c r="L79" s="10" t="inlineStr"/>
+      <c r="M79" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N79" s="10" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N62"/>
+  <autoFilter ref="A1:N79"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9397,4 +10508,1419 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="52" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Round 4</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Meera, book-lover persona (code-blind agent; browser only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Local: frontend :5174, API :3100; assistant model not configured (no NVIDIA_API_KEY). Browser pane already signed in to the seeded account with the readable EPUB; desktop (800px pane) and phone 375x812.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Tester's reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>First impression onboarding</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Warm and calm with clear empty states; onboarding not seen (already signed in); the Assistant asks to turn AI on before saying what it does.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Library adding finding books</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Adding works and results look great; ~16s search, confusing labels, 'Already read' stamps today, no way to edit metadata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Book page and details</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Rating, favourite, review, shelves, status save nicely; finish date not editable, 'Bunko Sample Press' as author, 'Chapter · ch1' labels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Lovely typography, 3D curl and phone layout; wrong current chapter (footer, bookmarks, notes), scroll and View Original lose your place, View Original's first chapter broken.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Tracking journal statistics</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>The journal is the best part; timer survived a refresh; paper logging easy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Shelves organizing</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Charming bookcase, multi-add works, shelf toggles on the book page; adding a bit slow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Notes highlights reviews</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Highlights show on page and book page and persist; deleting one deleted another with its note; chapter notes on the wrong chapter; tapping a highlight does nothing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Assistant chat</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Honest about the missing model; commands, undo and questions work; 'can you put klara on my comfort reads shelf' listed the shelf; 'last night' ignored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Look and feel</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Made for readers; a few developer-ish labels and cramped phone layouts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Speed reliability</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Never signed out, nothing lost; blank spinner on every load, slow search and shelf adds, View Original blanks each page turn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Would track reading here today, but can't yet trust the reader with place and highlights.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Issues and fixes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Round</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Root cause</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Fix</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Verified in round</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>R4-01</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Notes highlights reviews</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>Deleting one highlight also deleted another and its margin note</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>Reader &gt; Highlights (3) &gt; trash on the Quote, no feedback, click again.</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>Only the Quote deleted, with confirm or undo.</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>The Quote and the yellow highlight with its margin note both gone; no confirmation or feedback.</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Deleting waited for the server before the list changed, so a second click landed on the next highlight as it slid up.</t>
+        </is>
+      </c>
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>Highlights leave the list at once (restored if the delete fails), and deleting asks in place: Delete / Keep.</t>
+        </is>
+      </c>
+      <c r="K20" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/AnnotationsDrawer.tsx, frontend/src/lib/api/annotations.ts</t>
+        </is>
+      </c>
+      <c r="L20" s="10" t="inlineStr"/>
+      <c r="M20" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>R4-02</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>Current chapter wrong: footer, chapter list, bookmarks, notes</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>Turn pages with arrows in 3D Flip / scroll; bookmark in The Customs House; 'This chapter' note in A Ledger in Salt.</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>Everything names the chapter being read.</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>Footer lags 1-2 chapters; bookmark labelled and jumping to the wrong chapter; note saved as 'Chapter · ch1'.</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>The page-flip handler was memoised on the first render, before chapters loaded, so the chapter name never followed page turns; notes showed the stored chapter id.</t>
+        </is>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>The flip handler goes through a ref to the latest code; the chapter name is derived from the current chapter; notes carry positionLabel (the chapter title).</t>
+        </is>
+      </c>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/FlowReaderPage.tsx, backend/src/modules/notes/notes.service.ts, backend/src/modules/reader/position-labels.ts</t>
+        </is>
+      </c>
+      <c r="L21" s="10" t="inlineStr"/>
+      <c r="M21" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N21" s="10" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>R4-03</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>Scroll mode doesn't reopen where you left off</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>Scroll mode, go to The Customs House (~58%), refresh.</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>Reopens there.</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>Top of chapter 1 at 0% while the footer says another chapter.</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Scroll mode tried to scroll before its chapters were on screen, and tracked position with requestAnimationFrame, which stalls in a background tab, so offsets stayed at 0.</t>
+        </is>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>Position is chapter + offset in scroll mode too, restored once the chapters render; tracking uses a timer.</t>
+        </is>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/FlowReaderPage.tsx</t>
+        </is>
+      </c>
+      <c r="L22" s="10" t="inlineStr"/>
+      <c r="M22" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N22" s="10" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>R4-04</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>View Original's first chapter broken; switching views loses place</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>At A Ledger in Salt, View Original, then Back to reading view.</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>Same spot, normal layout, place kept.</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>Huge heading, paragraphs in 4-5 narrow columns, opens at chapter 1, 0% / '20 min left'; back in reading view at 0%; ~2s blank page per turn; no highlights.</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>The original-file view treated the first section of any book as a cover (narrow columns); position loss came from R4-03; the time estimate was guessed from chapter counts.</t>
+        </is>
+      </c>
+      <c r="J23" s="10" t="inlineStr">
+        <is>
+          <t>Only a section marked as a cover is laid out as one; the place carries both ways; no time guess in the original view. (Page-turn blanking and highlights in the original view unchanged.)</t>
+        </is>
+      </c>
+      <c r="K23" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/EpubReader.tsx, frontend/src/features/reader/ReaderPage.tsx</t>
+        </is>
+      </c>
+      <c r="L23" s="10" t="inlineStr"/>
+      <c r="M23" s="10" t="inlineStr">
+        <is>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="N23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>R4-05</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Book page and details</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>Finish date can't be set or changed</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>Finish a book; add as 'Already read'; 'finally finished circe last night, 4 stars'.</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>Editable date; 'last night' = yesterday.</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>Plain text; 'Already read' stamps today (inflating this year's count); Circe got today.</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>finishedAt could only be 'now'; 'Already read' dated today; the assistant ignored 'last night'.</t>
+        </is>
+      </c>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>Editable 'Finished on' date (PATCH /works finishedAt, no future dates); 'Already read' starts undated; 'finished X last night' dates it yesterday and says so.</t>
+        </is>
+      </c>
+      <c r="K24" s="10" t="inlineStr">
+        <is>
+          <t>backend/src/modules/library/*, frontend/src/features/library/BookDetailPage.tsx, frontend/src/features/library/AddBookDialog.tsx, backend/src/modules/assistant/domains/books/actions/libraryTools.ts, backend/src/modules/assistant/domains/books/conversation/quickCommands.ts</t>
+        </is>
+      </c>
+      <c r="L24" s="10" t="inlineStr"/>
+      <c r="M24" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>R4-06</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>Search result jumps to the chapter, not the match</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>Search 'ledger', click a result.</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>Scroll to and mark the match; search box focused.</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>Top of chapter, nothing marked; first typing lost.</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>Search results carried only the chapter; the box wasn't focused.</t>
+        </is>
+      </c>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>Jumps to the page with the match, marks the words for a few seconds; the box is focused.</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/reader/InBookSearchDrawer.tsx</t>
+        </is>
+      </c>
+      <c r="L25" s="10" t="inlineStr"/>
+      <c r="M25" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N25" s="10" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>R4-07</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>No end-of-book moment</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>Read to 100%.</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>Offer to mark finished / rate.</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>Nothing; '1 min left' at 100%; status stays Reading.</t>
+        </is>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>No handling of the last page.</t>
+        </is>
+      </c>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>'The end. Finished &lt;title&gt;?' with Mark as finished; 'Last page' instead of '1 min left'.</t>
+        </is>
+      </c>
+      <c r="K26" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/reader/ReaderProgressScrubber.tsx</t>
+        </is>
+      </c>
+      <c r="L26" s="10" t="inlineStr"/>
+      <c r="M26" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N26" s="10" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>R4-08</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Library adding finding books</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>Add-book search slow, labels confusing</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>Search 'The Housekeeper and the Professor'.</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>Fast results, clear labels.</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>~16s; 'Added: English' badge on every result; leading 'The' dropped.</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>Coloured chips per result ('Added: English' meant the language you'd read it in).</t>
+        </is>
+      </c>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>One quiet line ('Originally Japanese · 14 chapters'), synopsis cleaned. (Catalogue speed unchanged.)</t>
+        </is>
+      </c>
+      <c r="K27" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/library/AddBookDialog.tsx</t>
+        </is>
+      </c>
+      <c r="L27" s="10" t="inlineStr"/>
+      <c r="M27" s="10" t="inlineStr">
+        <is>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="N27" s="10" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>R4-09</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Library adding finding books</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>Library search can't combine author and title; no metadata editing</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>Search 'ishiguro klara'; try to fix an author/cover.</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>Finds the book; an Edit option.</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>No match; no edit; inconsistent placeholder covers.</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Library search matched the whole phrase against title or author.</t>
+        </is>
+      </c>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>Each word must match the title or an author. (Editing book details isn't built: works are shared catalogue entries.)</t>
+        </is>
+      </c>
+      <c r="K28" s="10" t="inlineStr">
+        <is>
+          <t>backend/src/modules/library/library.service.ts</t>
+        </is>
+      </c>
+      <c r="L28" s="10" t="inlineStr"/>
+      <c r="M28" s="10" t="inlineStr">
+        <is>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="N28" s="10" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>R4-10</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Book page and details</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>'Open the book' on a highlight doesn't go to it</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>Book page &gt; Highlights &gt; Open the book.</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>Opens at that highlight.</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>Opens at the last position.</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>The link opened the book at the last position.</t>
+        </is>
+      </c>
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>'Read it in the book' opens the reader at that highlight.</t>
+        </is>
+      </c>
+      <c r="K29" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/notes/BookHighlights.tsx, frontend/src/features/reader/FlowReaderPage.tsx</t>
+        </is>
+      </c>
+      <c r="L29" s="10" t="inlineStr"/>
+      <c r="M29" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>R4-11</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Notes highlights reviews</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>Highlights can't be edited from the page; weak feedback</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>Click a highlight; save one with a note or a Quote.</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>Edit/recolour/delete on click; confirmation.</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>Nothing on click; no confirmation; toolbar covers the selection; quotes cut off; raw colour names.</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Highlights on the page weren't interactive; saving was silent.</t>
+        </is>
+      </c>
+      <c r="J30" s="10" t="inlineStr">
+        <is>
+          <t>Tapping a highlight opens your highlights; 'Highlight saved' / 'Quote saved' notice; colour labels replaced by a swatch.</t>
+        </is>
+      </c>
+      <c r="K30" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/reader/AnnotationsDrawer.tsx</t>
+        </is>
+      </c>
+      <c r="L30" s="10" t="inlineStr"/>
+      <c r="M30" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N30" s="10" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>R4-12</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>Dark theme leaves light surfaces</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>Appearance &gt; Dark.</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>Whole reader dark.</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>Progress bar and Appearance panel stay cream; stray horizontal scrollbar.</t>
+        </is>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>The progress bar used fixed cream colours.</t>
+        </is>
+      </c>
+      <c r="J31" s="10" t="inlineStr">
+        <is>
+          <t>It takes the reading theme's colours. (The Appearance panel stays light.)</t>
+        </is>
+      </c>
+      <c r="K31" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/ReaderProgressScrubber.tsx</t>
+        </is>
+      </c>
+      <c r="L31" s="10" t="inlineStr"/>
+      <c r="M31" s="10" t="inlineStr">
+        <is>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="N31" s="10" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>R4-13</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>Menus don't close with Escape or an outside click</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>Open the bookmarks dropdown or the phone '...' menu.</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>Closes.</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>Stays open; two menus open at once.</t>
+        </is>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>No Escape or outside-click handling.</t>
+        </is>
+      </c>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>Escape closes menus and panels; clicking outside closes the dropdowns.</t>
+        </is>
+      </c>
+      <c r="K32" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/FlowReaderPage.tsx</t>
+        </is>
+      </c>
+      <c r="L32" s="10" t="inlineStr"/>
+      <c r="M32" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N32" s="10" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>R4-14</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Tracking journal statistics</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>Tiny accidental sessions; inconsistent page fields</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>Open and close a book within a minute; compare Log reading and ending a timed session.</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>Very short visits not logged; same page fields.</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>'Under a minute' sessions counted; free-text vs numeric page fields.</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>Every opened reader session was kept.</t>
+        </is>
+      </c>
+      <c r="J33" s="10" t="inlineStr">
+        <is>
+          <t>Closing a book within a minute leaves no journal entry. (The paper-session form still asks for a chapter or page as text, which SRS §12.9 requires.)</t>
+        </is>
+      </c>
+      <c r="K33" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/FlowReaderPage.tsx</t>
+        </is>
+      </c>
+      <c r="L33" s="10" t="inlineStr"/>
+      <c r="M33" s="10" t="inlineStr">
+        <is>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="N33" s="10" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>R4-15</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>Assistant chat</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>Natural shelf request answered with a list</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>'can you put klara on my comfort reads shelf'.</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>Adds it or asks.</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>Listed the shelf; 'something like piranesi' ignored.</t>
+        </is>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>'can you ...' read as a question, so it was answered from the library.</t>
+        </is>
+      </c>
+      <c r="J34" s="10" t="inlineStr">
+        <is>
+          <t>Polite requests ('can you put ...?') are commands.</t>
+        </is>
+      </c>
+      <c r="K34" s="10" t="inlineStr">
+        <is>
+          <t>backend/src/modules/assistant/domains/books/pipeline/preRoute.ts</t>
+        </is>
+      </c>
+      <c r="L34" s="10" t="inlineStr"/>
+      <c r="M34" s="10" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="N34" s="10" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>R4-16</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Look and feel</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>polish</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>Developer-ish text and cramped phone layouts</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>Desktop and phone.</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>Reader wording, tidy phone layouts.</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
+        <is>
+          <t>'CHAPTERS / TOC', 'Chapter · ch1', 'Drag, or use the keyboard' on phone, small chapter titles, cramped Editions header and Journal dates, full-screen Appearance sheet.</t>
+        </is>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>Leftover technical labels; fixed heading size; dates squeezing journal entries on phones.</t>
+        </is>
+      </c>
+      <c r="J35" s="10" t="inlineStr">
+        <is>
+          <t>'Chapters', plainer shelves subtitle, chapter titles a step above body text, journal dates above the title on phones.</t>
+        </is>
+      </c>
+      <c r="K35" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/ReaderPage.tsx, frontend/src/features/shelves/ShelvesPage.tsx, frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/journal/JournalPage.tsx</t>
+        </is>
+      </c>
+      <c r="L35" s="10" t="inlineStr"/>
+      <c r="M35" s="10" t="inlineStr">
+        <is>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="N35" s="10" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>R4-17</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>Speed reliability</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>polish</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>Blank spinner on every full page load</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>Refresh any page.</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>App shell immediately.</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>1-2s blank page; typing lost; 'Maximum update depth exceeded' and some 404s in the console.</t>
+        </is>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>The app waits for the session to be restored before drawing anything.</t>
+        </is>
+      </c>
+      <c r="J36" s="10" t="inlineStr">
+        <is>
+          <t>Not changed this round.</t>
+        </is>
+      </c>
+      <c r="K36" s="10" t="inlineStr"/>
+      <c r="L36" s="10" t="inlineStr"/>
+      <c r="M36" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N36" s="10" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>What the tester liked</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Beautiful reading surface: serif type, spacing, sepia/paper themes, a satisfying 3D curl; font changes and refresh keep your place in Flip mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>The Journal: reflection, highlights, margin notes and chapter notes grouped per session; an honest delete dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>The 'Session ended' reflection ritual, and a paper session that survives a refresh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>The Shelves bookcase with spine/cover toggle and multi-select 'Add books'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>An honest Assistant with accurate commands, undo and library answers, and clear AI privacy text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>A good phone layout: clean icon toolbar, well-sized reading column.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/qa/blackbox-test-log.xlsx
+++ b/docs/qa/blackbox-test-log.xlsx
@@ -13,9 +13,10 @@
     <sheet name="Round 2" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Round 3" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Round 4" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Round 5" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All issues'!$A$1:$N$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All issues'!$A$1:$N$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -499,6 +500,7 @@
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -534,6 +536,11 @@
           <t>Round 4</t>
         </is>
       </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Round 5</t>
+        </is>
+      </c>
     </row>
     <row r="4"/>
     <row r="5">
@@ -554,6 +561,9 @@
       <c r="E5" s="4" t="n">
         <v>7</v>
       </c>
+      <c r="F5" s="5" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -573,6 +583,9 @@
       <c r="E6" s="4" t="n">
         <v>6</v>
       </c>
+      <c r="F6" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -592,6 +605,9 @@
       <c r="E7" s="4" t="n">
         <v>6</v>
       </c>
+      <c r="F7" s="5" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -613,6 +629,9 @@
       <c r="E8" s="4" t="n">
         <v>5</v>
       </c>
+      <c r="F8" s="5" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -632,6 +651,9 @@
       <c r="E9" s="5" t="n">
         <v>8</v>
       </c>
+      <c r="F9" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -651,6 +673,9 @@
       <c r="E10" s="5" t="n">
         <v>8</v>
       </c>
+      <c r="F10" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -670,6 +695,9 @@
       <c r="E11" s="4" t="n">
         <v>5</v>
       </c>
+      <c r="F11" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -689,6 +717,9 @@
       <c r="E12" s="4" t="n">
         <v>7</v>
       </c>
+      <c r="F12" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -708,6 +739,9 @@
       <c r="E13" s="5" t="n">
         <v>8</v>
       </c>
+      <c r="F13" s="5" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -727,6 +761,9 @@
       <c r="E14" s="4" t="n">
         <v>6</v>
       </c>
+      <c r="F14" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -746,6 +783,9 @@
       <c r="E15" s="4" t="n">
         <v>6</v>
       </c>
+      <c r="F15" s="4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -765,6 +805,9 @@
       <c r="E16" s="3" t="n">
         <v>5</v>
       </c>
+      <c r="F16" s="3" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -784,6 +827,9 @@
       <c r="E17" s="3" t="n">
         <v>17</v>
       </c>
+      <c r="F17" s="3" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -803,6 +849,9 @@
       <c r="E18" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="F18" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -849,6 +898,18 @@
       <c r="B23" s="9" t="inlineStr">
         <is>
           <t>Local: frontend :5174, API :3100; assistant model not configured (no NVIDIA_API_KEY). Browser pane already signed in to the seeded account with the readable EPUB; desktop (800px pane) and phone 375x812.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Round 5 (2026-10-28)</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Local: frontend :5174, API :3100 with AI_PROVIDER=nvidia and a real NVIDIA_API_KEY (live model calls, no mock). Seeded fresh account (qa.round5.1793127205@bunko.test) with AI consent pre-granted, a small library, two shelves, and one readable EPUB.</t>
         </is>
       </c>
     </row>
@@ -863,7 +924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N79"/>
+  <dimension ref="A1:N88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5713,8 +5774,458 @@
       </c>
       <c r="N79" s="10" t="inlineStr"/>
     </row>
+    <row r="80">
+      <c r="A80" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B80" s="10" t="inlineStr">
+        <is>
+          <t>R5-01</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>Shelves organizing</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>blocker</t>
+        </is>
+      </c>
+      <c r="E80" s="10" t="inlineStr">
+        <is>
+          <t>"Add book" button in the Shelves page's "Add books to [shelf]" dialog does not work</t>
+        </is>
+      </c>
+      <c r="F80" s="10" t="inlineStr">
+        <is>
+          <t>Shelves &gt; created a new shelf 'rainy day reads' via '+ New Shelf' &gt; clicked 'Add books' on the empty shelf &gt; checked Circe and Piranesi &gt; clicked 'Add book' (repeated with ref clicks, coordinate clicks, and Enter while focused).</t>
+        </is>
+      </c>
+      <c r="G80" s="10" t="inlineStr">
+        <is>
+          <t>Selected books get added to the shelf and the dialog closes/updates the count.</t>
+        </is>
+      </c>
+      <c r="H80" s="10" t="inlineStr">
+        <is>
+          <t>Nothing happens -- dialog stays open, shelf still shows '0 books'. Workaround: toggling the shelf tag on each book's own detail page works correctly.</t>
+        </is>
+      </c>
+      <c r="I80" s="10" t="inlineStr"/>
+      <c r="J80" s="10" t="inlineStr"/>
+      <c r="K80" s="10" t="inlineStr"/>
+      <c r="L80" s="10" t="inlineStr"/>
+      <c r="M80" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N80" s="10" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>R5-02</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>Tracking journal statistics</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>Reflection typed into the reader's "Session ended" dialog is never saved</t>
+        </is>
+      </c>
+      <c r="F81" s="10" t="inlineStr">
+        <is>
+          <t>Finished 'The Lantern Keeper of Aldmere' in the reader &gt; 'Close the book' &gt; 'Session ended / 6 min of reading. Nice work.' dialog &gt; typed a reflection &gt; Save.</t>
+        </is>
+      </c>
+      <c r="G81" s="10" t="inlineStr">
+        <is>
+          <t>The reflection text appears in the Journal entry, the book's Notes, or its Review.</t>
+        </is>
+      </c>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>The reflection text is gone entirely. The Journal entry shows an unrelated earlier highlight instead; Notes/Review stay empty even after reload.</t>
+        </is>
+      </c>
+      <c r="I81" s="10" t="inlineStr"/>
+      <c r="J81" s="10" t="inlineStr"/>
+      <c r="K81" s="10" t="inlineStr"/>
+      <c r="L81" s="10" t="inlineStr"/>
+      <c r="M81" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N81" s="10" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B82" s="10" t="inlineStr">
+        <is>
+          <t>R5-03</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>Tracking journal statistics</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E82" s="10" t="inlineStr">
+        <is>
+          <t>Logged reading session date is off by one day</t>
+        </is>
+      </c>
+      <c r="F82" s="10" t="inlineStr">
+        <is>
+          <t>Journal &gt; 'Log reading' &gt; book Piranesi, Day field showed '28-10-2026' (today), Minutes 45, From page 10, To page 55, reflection text, 'Log reading'.</t>
+        </is>
+      </c>
+      <c r="G82" s="10" t="inlineStr">
+        <is>
+          <t>Journal entry shows 'Oct 28, 2026' matching the selected date.</t>
+        </is>
+      </c>
+      <c r="H82" s="10" t="inlineStr">
+        <is>
+          <t>Entry is listed under 'Oct 27, 2026' -- one day earlier, suggesting a timezone conversion bug.</t>
+        </is>
+      </c>
+      <c r="I82" s="10" t="inlineStr"/>
+      <c r="J82" s="10" t="inlineStr"/>
+      <c r="K82" s="10" t="inlineStr"/>
+      <c r="L82" s="10" t="inlineStr"/>
+      <c r="M82" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N82" s="10" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>R5-04</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>Assistant chat</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="inlineStr">
+        <is>
+          <t>Off-topic assistant questions reliably time out (even on retry)</t>
+        </is>
+      </c>
+      <c r="F83" s="10" t="inlineStr">
+        <is>
+          <t>In Assistant chat, after several successful book-related exchanges, sent 'whats the weather like today'. Waited 30s -&gt; timeout message. Clicked 'Try again', waited another 30s.</t>
+        </is>
+      </c>
+      <c r="G83" s="10" t="inlineStr">
+        <is>
+          <t>Either a quick graceful redirect, or at least a successful retry.</t>
+        </is>
+      </c>
+      <c r="H83" s="10" t="inlineStr">
+        <is>
+          <t>Both the original attempt and the retry timed out after ~30s each with the same message. A normal on-topic question sent right after answered correctly within ~10s, so the failure seems specific to off-topic prompts.</t>
+        </is>
+      </c>
+      <c r="I83" s="10" t="inlineStr"/>
+      <c r="J83" s="10" t="inlineStr"/>
+      <c r="K83" s="10" t="inlineStr"/>
+      <c r="L83" s="10" t="inlineStr"/>
+      <c r="M83" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N83" s="10" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B84" s="10" t="inlineStr">
+        <is>
+          <t>R5-05</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>Assistant chat</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E84" s="10" t="inlineStr">
+        <is>
+          <t>Natural phrasing "i started reading circe" fails to resolve the book despite Circe being in the library and just discussed</t>
+        </is>
+      </c>
+      <c r="F84" s="10" t="inlineStr">
+        <is>
+          <t>After being recommended 'Circe by Madeline Miller' in the previous message, typed 'i started reading circe'.</t>
+        </is>
+      </c>
+      <c r="G84" s="10" t="inlineStr">
+        <is>
+          <t>The assistant recognizes 'circe' as the book just discussed and marks it Reading.</t>
+        </is>
+      </c>
+      <c r="H84" s="10" t="inlineStr">
+        <is>
+          <t>"I couldn't find a book called 'reading circe'..." -- it matched the whole phrase as a title instead of parsing 'started reading' as the verb phrase. Retyping with the full title worked.</t>
+        </is>
+      </c>
+      <c r="I84" s="10" t="inlineStr"/>
+      <c r="J84" s="10" t="inlineStr"/>
+      <c r="K84" s="10" t="inlineStr"/>
+      <c r="L84" s="10" t="inlineStr"/>
+      <c r="M84" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N84" s="10" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>R5-06</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>Speed reliability</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E85" s="10" t="inlineStr">
+        <is>
+          <t>Unexpected full session logout with no warning, not reproduced on retry</t>
+        </is>
+      </c>
+      <c r="F85" s="10" t="inlineStr">
+        <is>
+          <t>On a book detail page (The Name of the Wind), clicked 'Add note', typed a note, clicked the '+ Add note' trigger button.</t>
+        </is>
+      </c>
+      <c r="G85" s="10" t="inlineStr">
+        <is>
+          <t>Note dialog opens or note saves; if a session genuinely expired, a clear message should explain why.</t>
+        </is>
+      </c>
+      <c r="H85" s="10" t="inlineStr">
+        <is>
+          <t>The app silently navigated to /login with all session state lost, no toast or explanation. Logging back in and repeating the exact steps worked fine every subsequent time.</t>
+        </is>
+      </c>
+      <c r="I85" s="10" t="inlineStr"/>
+      <c r="J85" s="10" t="inlineStr"/>
+      <c r="K85" s="10" t="inlineStr"/>
+      <c r="L85" s="10" t="inlineStr"/>
+      <c r="M85" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N85" s="10" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B86" s="10" t="inlineStr">
+        <is>
+          <t>R5-07</t>
+        </is>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>Look and feel</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E86" s="10" t="inlineStr">
+        <is>
+          <t>Toolbar tooltip/panel overlays get stuck open and block clicks underneath</t>
+        </is>
+      </c>
+      <c r="F86" s="10" t="inlineStr">
+        <is>
+          <t>In the reader, clicked the Translate icon (shows 'isn't set up on this server yet' tooltip), then clicked other toolbar icons or chapter-list entries without first dismissing the Translate tooltip.</t>
+        </is>
+      </c>
+      <c r="G86" s="10" t="inlineStr">
+        <is>
+          <t>Clicking elsewhere should dismiss the previous tooltip automatically, or at least not intercept the click.</t>
+        </is>
+      </c>
+      <c r="H86" s="10" t="inlineStr">
+        <is>
+          <t>The tooltip stays on top, intercepting clicks meant for elements beneath it. Escape or its own close button dismisses it, but a casual user wouldn't know to do that and would think the buttons are broken.</t>
+        </is>
+      </c>
+      <c r="I86" s="10" t="inlineStr"/>
+      <c r="J86" s="10" t="inlineStr"/>
+      <c r="K86" s="10" t="inlineStr"/>
+      <c r="L86" s="10" t="inlineStr"/>
+      <c r="M86" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N86" s="10" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>R5-08</t>
+        </is>
+      </c>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
+          <t>Library adding finding books</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="inlineStr">
+        <is>
+          <t>Library grid cover art falls back to a generic placeholder even when real cover art exists</t>
+        </is>
+      </c>
+      <c r="F87" s="10" t="inlineStr">
+        <is>
+          <t>Added 'The Name of the Wind' via the Assistant, then viewed the Library grid.</t>
+        </is>
+      </c>
+      <c r="G87" s="10" t="inlineStr">
+        <is>
+          <t>Since the book's detail page and quick-view popup both show real cover art, the grid thumbnail should match.</t>
+        </is>
+      </c>
+      <c r="H87" s="10" t="inlineStr">
+        <is>
+          <t>The Library grid shows a generic orange 'T' placeholder tile, while every other metadata field is correctly enriched.</t>
+        </is>
+      </c>
+      <c r="I87" s="10" t="inlineStr"/>
+      <c r="J87" s="10" t="inlineStr"/>
+      <c r="K87" s="10" t="inlineStr"/>
+      <c r="L87" s="10" t="inlineStr"/>
+      <c r="M87" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N87" s="10" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B88" s="10" t="inlineStr">
+        <is>
+          <t>R5-09</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>Tracking journal statistics</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>polish</t>
+        </is>
+      </c>
+      <c r="E88" s="10" t="inlineStr">
+        <is>
+          <t>Settings page AI-features copy contradicts actual working behavior</t>
+        </is>
+      </c>
+      <c r="F88" s="10" t="inlineStr">
+        <is>
+          <t>Settings &gt; 'AI features' section.</t>
+        </is>
+      </c>
+      <c r="G88" s="10" t="inlineStr">
+        <is>
+          <t>Messaging consistent with the Assistant chat being clearly live and working with a real AI model.</t>
+        </is>
+      </c>
+      <c r="H88" s="10" t="inlineStr">
+        <is>
+          <t>Footer text reads "AI features aren't set up on this server yet -- your choice is saved for when they are", which is stale and could confuse a user about whether their data is actually being sent anywhere.</t>
+        </is>
+      </c>
+      <c r="I88" s="10" t="inlineStr"/>
+      <c r="J88" s="10" t="inlineStr"/>
+      <c r="K88" s="10" t="inlineStr"/>
+      <c r="L88" s="10" t="inlineStr"/>
+      <c r="M88" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N88" s="10" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N79"/>
+  <autoFilter ref="A1:N88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11923,4 +12434,812 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="52" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Round 5</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Meera, book-lover persona (code-blind agent; browser only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Local: frontend :5174, API :3100 with AI_PROVIDER=nvidia and a real NVIDIA_API_KEY (live model calls, no mock). Seeded fresh account (qa.round5.1793127205@bunko.test) with AI consent pre-granted, a small library, two shelves, and one readable EPUB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Tester's reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>First impression onboarding</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Clean, calm, book-themed login; already signed in to the seeded account so full onboarding wasn't seen, but nothing felt generic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Library adding finding books</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Adding by title/author with real metadata/cover enrichment works well, but the library grid shows a generic placeholder tile even when the book's detail page has a real cover.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Book page and details</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Rich, well-organized page (description, series, shelves, rating, review, notes, highlights); rating and notes persisted reliably on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Reading experience</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Genuinely delightful EPUB reader: 3D-flip and scroll modes, 4 legible themes, font/line/margin controls, in-book search, working highlights, bookmarks, and a thoughtful end-of-book flow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Tracking journal statistics</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Logging/viewing/deleting sessions works with a nice delete confirmation, but a logged date was off by one day and a typed session reflection was silently discarded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Shelves organizing</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>The physical bookshelf visualization is the best-looking part of the app, but the Shelves page's own 'Add books to shelf' dialog does nothing when you click Add book.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Notes highlights reviews</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Highlighting with the color picker, the Highlights sidebar, and reviews/ratings/notes all saved and persisted, but the lost session reflection and some first-attempt save fragility hold it back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Assistant chat</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Accurate and grounded on in-scope library questions with a working undo and clear loading states, but off-topic questions reliably time out even on retry, and 'i started reading circe' fails to parse despite Circe being the book just recommended.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Look and feel</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Serif typography, warm paper palette, the physical bookshelf, thoughtful copy, and a transparent AI-data-use settings page -- feels made by book people, not a generic template.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Speed reliability</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Most interactions are fast, but real reproducible bugs surfaced: the broken shelf add-books dialog, a lost session reflection, an off-by-one journal date, one unexplained mid-session logout, and tooltips that get stuck open and block clicks underneath.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>A charming, well-designed reading app with one of the best in-browser EPUB readers tested, let down by a handful of real functional bugs a careful reader would hit within a single normal session.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Issues and fixes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Round</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Root cause</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Fix</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Verified in round</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>R5-01</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Shelves organizing</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>blocker</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>"Add book" button in the Shelves page's "Add books to [shelf]" dialog does not work</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>Shelves &gt; created a new shelf 'rainy day reads' via '+ New Shelf' &gt; clicked 'Add books' on the empty shelf &gt; checked Circe and Piranesi &gt; clicked 'Add book' (repeated with ref clicks, coordinate clicks, and Enter while focused).</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>Selected books get added to the shelf and the dialog closes/updates the count.</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>Nothing happens -- dialog stays open, shelf still shows '0 books'. Workaround: toggling the shelf tag on each book's own detail page works correctly.</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="inlineStr"/>
+      <c r="J20" s="10" t="inlineStr"/>
+      <c r="K20" s="10" t="inlineStr"/>
+      <c r="L20" s="10" t="inlineStr"/>
+      <c r="M20" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>R5-02</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Tracking journal statistics</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>Reflection typed into the reader's "Session ended" dialog is never saved</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>Finished 'The Lantern Keeper of Aldmere' in the reader &gt; 'Close the book' &gt; 'Session ended / 6 min of reading. Nice work.' dialog &gt; typed a reflection &gt; Save.</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>The reflection text appears in the Journal entry, the book's Notes, or its Review.</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>The reflection text is gone entirely. The Journal entry shows an unrelated earlier highlight instead; Notes/Review stay empty even after reload.</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr"/>
+      <c r="J21" s="10" t="inlineStr"/>
+      <c r="K21" s="10" t="inlineStr"/>
+      <c r="L21" s="10" t="inlineStr"/>
+      <c r="M21" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N21" s="10" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>R5-03</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Tracking journal statistics</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>Logged reading session date is off by one day</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>Journal &gt; 'Log reading' &gt; book Piranesi, Day field showed '28-10-2026' (today), Minutes 45, From page 10, To page 55, reflection text, 'Log reading'.</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>Journal entry shows 'Oct 28, 2026' matching the selected date.</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>Entry is listed under 'Oct 27, 2026' -- one day earlier, suggesting a timezone conversion bug.</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="inlineStr"/>
+      <c r="J22" s="10" t="inlineStr"/>
+      <c r="K22" s="10" t="inlineStr"/>
+      <c r="L22" s="10" t="inlineStr"/>
+      <c r="M22" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N22" s="10" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>R5-04</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Assistant chat</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>Off-topic assistant questions reliably time out (even on retry)</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>In Assistant chat, after several successful book-related exchanges, sent 'whats the weather like today'. Waited 30s -&gt; timeout message. Clicked 'Try again', waited another 30s.</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>Either a quick graceful redirect, or at least a successful retry.</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>Both the original attempt and the retry timed out after ~30s each with the same message. A normal on-topic question sent right after answered correctly within ~10s, so the failure seems specific to off-topic prompts.</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr"/>
+      <c r="J23" s="10" t="inlineStr"/>
+      <c r="K23" s="10" t="inlineStr"/>
+      <c r="L23" s="10" t="inlineStr"/>
+      <c r="M23" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>R5-05</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Assistant chat</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>Natural phrasing "i started reading circe" fails to resolve the book despite Circe being in the library and just discussed</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>After being recommended 'Circe by Madeline Miller' in the previous message, typed 'i started reading circe'.</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>The assistant recognizes 'circe' as the book just discussed and marks it Reading.</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>"I couldn't find a book called 'reading circe'..." -- it matched the whole phrase as a title instead of parsing 'started reading' as the verb phrase. Retyping with the full title worked.</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="inlineStr"/>
+      <c r="J24" s="10" t="inlineStr"/>
+      <c r="K24" s="10" t="inlineStr"/>
+      <c r="L24" s="10" t="inlineStr"/>
+      <c r="M24" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>R5-06</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Speed reliability</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>Unexpected full session logout with no warning, not reproduced on retry</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>On a book detail page (The Name of the Wind), clicked 'Add note', typed a note, clicked the '+ Add note' trigger button.</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>Note dialog opens or note saves; if a session genuinely expired, a clear message should explain why.</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>The app silently navigated to /login with all session state lost, no toast or explanation. Logging back in and repeating the exact steps worked fine every subsequent time.</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="inlineStr"/>
+      <c r="J25" s="10" t="inlineStr"/>
+      <c r="K25" s="10" t="inlineStr"/>
+      <c r="L25" s="10" t="inlineStr"/>
+      <c r="M25" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N25" s="10" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>R5-07</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Look and feel</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>Toolbar tooltip/panel overlays get stuck open and block clicks underneath</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>In the reader, clicked the Translate icon (shows 'isn't set up on this server yet' tooltip), then clicked other toolbar icons or chapter-list entries without first dismissing the Translate tooltip.</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>Clicking elsewhere should dismiss the previous tooltip automatically, or at least not intercept the click.</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>The tooltip stays on top, intercepting clicks meant for elements beneath it. Escape or its own close button dismisses it, but a casual user wouldn't know to do that and would think the buttons are broken.</t>
+        </is>
+      </c>
+      <c r="I26" s="10" t="inlineStr"/>
+      <c r="J26" s="10" t="inlineStr"/>
+      <c r="K26" s="10" t="inlineStr"/>
+      <c r="L26" s="10" t="inlineStr"/>
+      <c r="M26" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N26" s="10" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>R5-08</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Library adding finding books</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>Library grid cover art falls back to a generic placeholder even when real cover art exists</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>Added 'The Name of the Wind' via the Assistant, then viewed the Library grid.</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>Since the book's detail page and quick-view popup both show real cover art, the grid thumbnail should match.</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>The Library grid shows a generic orange 'T' placeholder tile, while every other metadata field is correctly enriched.</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="inlineStr"/>
+      <c r="J27" s="10" t="inlineStr"/>
+      <c r="K27" s="10" t="inlineStr"/>
+      <c r="L27" s="10" t="inlineStr"/>
+      <c r="M27" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N27" s="10" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>R5-09</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Tracking journal statistics</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>polish</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>Settings page AI-features copy contradicts actual working behavior</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>Settings &gt; 'AI features' section.</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>Messaging consistent with the Assistant chat being clearly live and working with a real AI model.</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>Footer text reads "AI features aren't set up on this server yet -- your choice is saved for when they are", which is stale and could confuse a user about whether their data is actually being sent anywhere.</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="inlineStr"/>
+      <c r="J28" s="10" t="inlineStr"/>
+      <c r="K28" s="10" t="inlineStr"/>
+      <c r="L28" s="10" t="inlineStr"/>
+      <c r="M28" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="N28" s="10" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>What the tester liked</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>The 3D-flip/scroll EPUB reader is excellent: real pagination with chapter titles, 4 legible reading themes, font/line-spacing/margin controls, in-book search that jumps to the exact page, and highlights that persist across reload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>The physical bookshelf visualization on the Shelves page (wood shelf texture, genre grouping, Covers/Spines toggle, drag to rearrange) is delightful and unlike any generic tracker UI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>The Assistant correctly grounds its answers in the user's actual library (accurate counts, correct want-to-read list, sensible recommendations) and has a working, reliable undo for its last action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>The 'Session ended' flow after finishing a book (reading-time summary, 'Finished [Book]?' prompt, auto-set finish date) mirrors how a real reader thinks about wrapping up a book.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Settings' AI-features section is unusually transparent about exactly what data is sent to which third-party service and when -- genuinely trust-building rather than generic boilerplate.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/qa/blackbox-test-log.xlsx
+++ b/docs/qa/blackbox-test-log.xlsx
@@ -850,7 +850,7 @@
         <v>10</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -5813,13 +5813,25 @@
           <t>Nothing happens -- dialog stays open, shelf still shows '0 books'. Workaround: toggling the shelf tag on each book's own detail page works correctly.</t>
         </is>
       </c>
-      <c r="I80" s="10" t="inlineStr"/>
-      <c r="J80" s="10" t="inlineStr"/>
-      <c r="K80" s="10" t="inlineStr"/>
+      <c r="I80" s="10" t="inlineStr">
+        <is>
+          <t>The shelf-assign request could fail client-side (an aborted fetch) even though the server's upsert had already succeeded, leaving the dialog stuck with no feedback and the reader unsure whether it worked.</t>
+        </is>
+      </c>
+      <c r="J80" s="10" t="inlineStr">
+        <is>
+          <t>Adding a work to a shelf is retried once automatically (the server call is an idempotent upsert), multiple selected books are added with Promise.allSettled instead of a sequential loop that stopped at the first failure, and the shelves list is always refreshed afterward.</t>
+        </is>
+      </c>
+      <c r="K80" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/shelves/AddToShelfDialog.tsx, frontend/src/lib/api/shelves.ts</t>
+        </is>
+      </c>
       <c r="L80" s="10" t="inlineStr"/>
       <c r="M80" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="N80" s="10" t="inlineStr"/>
@@ -5863,13 +5875,25 @@
           <t>The reflection text is gone entirely. The Journal entry shows an unrelated earlier highlight instead; Notes/Review stay empty even after reload.</t>
         </is>
       </c>
-      <c r="I81" s="10" t="inlineStr"/>
-      <c r="J81" s="10" t="inlineStr"/>
-      <c r="K81" s="10" t="inlineStr"/>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>The position used to end a session was re-read live when the reflection was saved moments later; if it had moved in the background since the book was actually closed, the server rejected the mismatched reflection as a conflict with the session already-ended, and dismissing the prompt (Escape/X) discarded whatever had been typed without saving it.</t>
+        </is>
+      </c>
+      <c r="J81" s="10" t="inlineStr">
+        <is>
+          <t>The ending position is captured once when the book closes and reused for the reflection save, so it can no longer drift; dismissing the prompt now saves a typed reflection the same as clicking Save, instead of throwing it away.</t>
+        </is>
+      </c>
+      <c r="K81" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/reader/ReaderPage.tsx, frontend/src/features/reader/ReflectionPrompt.tsx</t>
+        </is>
+      </c>
       <c r="L81" s="10" t="inlineStr"/>
       <c r="M81" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="N81" s="10" t="inlineStr"/>
@@ -5913,13 +5937,25 @@
           <t>Entry is listed under 'Oct 27, 2026' -- one day earlier, suggesting a timezone conversion bug.</t>
         </is>
       </c>
-      <c r="I82" s="10" t="inlineStr"/>
-      <c r="J82" s="10" t="inlineStr"/>
-      <c r="K82" s="10" t="inlineStr"/>
+      <c r="I82" s="10" t="inlineStr">
+        <is>
+          <t>Logging a session for 'today' used the live clock as the end time; subtracting the session's length could roll the computed start time before local midnight, and the journal files an entry by its start time -- so a session logged for today could show up a day earlier.</t>
+        </is>
+      </c>
+      <c r="J82" s="10" t="inlineStr">
+        <is>
+          <t>The live clock is only used when the session fits entirely within the chosen day; otherwise (and for every past date) it anchors to noon on that day, same as before.</t>
+        </is>
+      </c>
+      <c r="K82" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/journal/LogSessionDialog.tsx, frontend/src/features/journal/log-session-date.ts</t>
+        </is>
+      </c>
       <c r="L82" s="10" t="inlineStr"/>
       <c r="M82" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="N82" s="10" t="inlineStr"/>
@@ -5963,13 +5999,25 @@
           <t>Both the original attempt and the retry timed out after ~30s each with the same message. A normal on-topic question sent right after answered correctly within ~10s, so the failure seems specific to off-topic prompts.</t>
         </is>
       </c>
-      <c r="I83" s="10" t="inlineStr"/>
-      <c r="J83" s="10" t="inlineStr"/>
-      <c r="K83" s="10" t="inlineStr"/>
+      <c r="I83" s="10" t="inlineStr">
+        <is>
+          <t>The fallback model (gpt-oss, used since no NVIDIA_MODEL is configured) defaults to a higher reasoning effort than the Nemotron 'thinking' switch already disabled; an off-topic question gave it the most to reason about, so it burned its whole time budget without replying, and a retry hit the same model again within its unhealthy cooldown.</t>
+        </is>
+      </c>
+      <c r="J83" s="10" t="inlineStr">
+        <is>
+          <t>Every NVIDIA NIM call now also sends reasoning_effort: low, which applies to gpt-oss independently of the Nemotron-specific switch.</t>
+        </is>
+      </c>
+      <c r="K83" s="10" t="inlineStr">
+        <is>
+          <t>backend/src/modules/assistant/clients/NvidiaNimClient.ts</t>
+        </is>
+      </c>
       <c r="L83" s="10" t="inlineStr"/>
       <c r="M83" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="N83" s="10" t="inlineStr"/>
@@ -6013,13 +6061,25 @@
           <t>"I couldn't find a book called 'reading circe'..." -- it matched the whole phrase as a title instead of parsing 'started reading' as the verb phrase. Retyping with the full title worked.</t>
         </is>
       </c>
-      <c r="I84" s="10" t="inlineStr"/>
-      <c r="J84" s="10" t="inlineStr"/>
-      <c r="K84" s="10" t="inlineStr"/>
+      <c r="I84" s="10" t="inlineStr">
+        <is>
+          <t>'started reading circe' matched 'started' as the verb and left 'reading circe' as the title text, so it searched the catalogue for a nonexistent book instead of recognising the owned title.</t>
+        </is>
+      </c>
+      <c r="J84" s="10" t="inlineStr">
+        <is>
+          <t>An optional 'reading' is now consumed as filler right after started/starting/began/begun/finished/completed, before the title is read.</t>
+        </is>
+      </c>
+      <c r="K84" s="10" t="inlineStr">
+        <is>
+          <t>backend/src/modules/assistant/domains/books/conversation/quickCommands.ts</t>
+        </is>
+      </c>
       <c r="L84" s="10" t="inlineStr"/>
       <c r="M84" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="N84" s="10" t="inlineStr"/>
@@ -6063,13 +6123,25 @@
           <t>The app silently navigated to /login with all session state lost, no toast or explanation. Logging back in and repeating the exact steps worked fine every subsequent time.</t>
         </is>
       </c>
-      <c r="I85" s="10" t="inlineStr"/>
-      <c r="J85" s="10" t="inlineStr"/>
-      <c r="K85" s="10" t="inlineStr"/>
+      <c r="I85" s="10" t="inlineStr">
+        <is>
+          <t>Refresh tokens rotate strictly on first use; two requests that both held the same token (a burst of calls right as the 15-minute access token expired) raced to rotate it, and the loser was treated as reuse and signed the reader out with no warning.</t>
+        </is>
+      </c>
+      <c r="J85" s="10" t="inlineStr">
+        <is>
+          <t>A rotated-away refresh token still works for a 10-second grace window, handing back the pair the winning request already produced instead of rotating again or rejecting it; reuse outside that window (or of any older token) is still rejected and logged as before.</t>
+        </is>
+      </c>
+      <c r="K85" s="10" t="inlineStr">
+        <is>
+          <t>backend/prisma/schema.prisma, backend/src/modules/auth/auth.service.ts, docs/DATA_MODEL.md, backend/tests/auth.spec.ts</t>
+        </is>
+      </c>
       <c r="L85" s="10" t="inlineStr"/>
       <c r="M85" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="N85" s="10" t="inlineStr"/>
@@ -6113,13 +6185,25 @@
           <t>The tooltip stays on top, intercepting clicks meant for elements beneath it. Escape or its own close button dismisses it, but a casual user wouldn't know to do that and would think the buttons are broken.</t>
         </is>
       </c>
-      <c r="I86" s="10" t="inlineStr"/>
-      <c r="J86" s="10" t="inlineStr"/>
-      <c r="K86" s="10" t="inlineStr"/>
+      <c r="I86" s="10" t="inlineStr">
+        <is>
+          <t>The reader's Escape-and-click-outside handling (added in round 4) covered the Bookmarks and More menus but was never extended to the Translate panel added afterward, so it had no way to close except its own X or Escape, and sat on top of other toolbar controls intercepting their clicks.</t>
+        </is>
+      </c>
+      <c r="J86" s="10" t="inlineStr">
+        <is>
+          <t>The same click-outside backdrop that closes Bookmarks and More now also closes the Translate panel.</t>
+        </is>
+      </c>
+      <c r="K86" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/FlowReaderPage.tsx</t>
+        </is>
+      </c>
       <c r="L86" s="10" t="inlineStr"/>
       <c r="M86" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="N86" s="10" t="inlineStr"/>
@@ -6163,13 +6247,25 @@
           <t>The Library grid shows a generic orange 'T' placeholder tile, while every other metadata field is correctly enriched.</t>
         </is>
       </c>
-      <c r="I87" s="10" t="inlineStr"/>
-      <c r="J87" s="10" t="inlineStr"/>
-      <c r="K87" s="10" t="inlineStr"/>
+      <c r="I87" s="10" t="inlineStr">
+        <is>
+          <t>A book added without a cover gets one found by the server a few seconds later in the background; nothing told the client to refetch, so the library grid kept showing the placeholder indefinitely once its initial fetch had already run, even though the book's own page (fetched fresh on each visit) already had the real cover.</t>
+        </is>
+      </c>
+      <c r="J87" s="10" t="inlineStr">
+        <is>
+          <t>Adding a book, from the dialog or through the assistant, now also refreshes the library list a few seconds later to pick up a cover the background search finds.</t>
+        </is>
+      </c>
+      <c r="K87" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/lib/api/works.ts, frontend/src/lib/api/assistant.ts</t>
+        </is>
+      </c>
       <c r="L87" s="10" t="inlineStr"/>
       <c r="M87" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="N87" s="10" t="inlineStr"/>
@@ -6213,13 +6309,25 @@
           <t>Footer text reads "AI features aren't set up on this server yet -- your choice is saved for when they are", which is stale and could confuse a user about whether their data is actually being sent anywhere.</t>
         </is>
       </c>
-      <c r="I88" s="10" t="inlineStr"/>
-      <c r="J88" s="10" t="inlineStr"/>
-      <c r="K88" s="10" t="inlineStr"/>
+      <c r="I88" s="10" t="inlineStr">
+        <is>
+          <t>'Assistant and book summaries' is one Settings toggle over two independent backends -- ai-service (Claude, for summaries/search/translation) and the assistant's own NVIDIA/Ollama client (for chat) -- but the availability check only ever looked at ai-service, so the notice said AI features weren't set up while the Assistant was demonstrably answering on NVIDIA.</t>
+        </is>
+      </c>
+      <c r="J88" s="10" t="inlineStr">
+        <is>
+          <t>Availability for the generative toggle now also counts the assistant's own provider being configured, and the notice names specifically which feature(s) -- search by meaning, the Assistant, chapter translation -- aren't set up, instead of a blanket claim.</t>
+        </is>
+      </c>
+      <c r="K88" s="10" t="inlineStr">
+        <is>
+          <t>backend/src/modules/ai/ai.service.ts, backend/src/modules/assistant/config/AIConfig.ts, frontend/src/features/ai/AiSettingsCard.tsx, backend/tests/ai.spec.ts</t>
+        </is>
+      </c>
       <c r="L88" s="10" t="inlineStr"/>
       <c r="M88" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="N88" s="10" t="inlineStr"/>
@@ -12786,13 +12894,25 @@
           <t>Nothing happens -- dialog stays open, shelf still shows '0 books'. Workaround: toggling the shelf tag on each book's own detail page works correctly.</t>
         </is>
       </c>
-      <c r="I20" s="10" t="inlineStr"/>
-      <c r="J20" s="10" t="inlineStr"/>
-      <c r="K20" s="10" t="inlineStr"/>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>The shelf-assign request could fail client-side (an aborted fetch) even though the server's upsert had already succeeded, leaving the dialog stuck with no feedback and the reader unsure whether it worked.</t>
+        </is>
+      </c>
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>Adding a work to a shelf is retried once automatically (the server call is an idempotent upsert), multiple selected books are added with Promise.allSettled instead of a sequential loop that stopped at the first failure, and the shelves list is always refreshed afterward.</t>
+        </is>
+      </c>
+      <c r="K20" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/shelves/AddToShelfDialog.tsx, frontend/src/lib/api/shelves.ts</t>
+        </is>
+      </c>
       <c r="L20" s="10" t="inlineStr"/>
       <c r="M20" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="N20" s="10" t="inlineStr"/>
@@ -12836,13 +12956,25 @@
           <t>The reflection text is gone entirely. The Journal entry shows an unrelated earlier highlight instead; Notes/Review stay empty even after reload.</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr"/>
-      <c r="J21" s="10" t="inlineStr"/>
-      <c r="K21" s="10" t="inlineStr"/>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>The position used to end a session was re-read live when the reflection was saved moments later; if it had moved in the background since the book was actually closed, the server rejected the mismatched reflection as a conflict with the session already-ended, and dismissing the prompt (Escape/X) discarded whatever had been typed without saving it.</t>
+        </is>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>The ending position is captured once when the book closes and reused for the reflection save, so it can no longer drift; dismissing the prompt now saves a typed reflection the same as clicking Save, instead of throwing it away.</t>
+        </is>
+      </c>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/FlowReaderPage.tsx, frontend/src/features/reader/ReaderPage.tsx, frontend/src/features/reader/ReflectionPrompt.tsx</t>
+        </is>
+      </c>
       <c r="L21" s="10" t="inlineStr"/>
       <c r="M21" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="N21" s="10" t="inlineStr"/>
@@ -12886,13 +13018,25 @@
           <t>Entry is listed under 'Oct 27, 2026' -- one day earlier, suggesting a timezone conversion bug.</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr"/>
-      <c r="J22" s="10" t="inlineStr"/>
-      <c r="K22" s="10" t="inlineStr"/>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Logging a session for 'today' used the live clock as the end time; subtracting the session's length could roll the computed start time before local midnight, and the journal files an entry by its start time -- so a session logged for today could show up a day earlier.</t>
+        </is>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>The live clock is only used when the session fits entirely within the chosen day; otherwise (and for every past date) it anchors to noon on that day, same as before.</t>
+        </is>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/journal/LogSessionDialog.tsx, frontend/src/features/journal/log-session-date.ts</t>
+        </is>
+      </c>
       <c r="L22" s="10" t="inlineStr"/>
       <c r="M22" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="N22" s="10" t="inlineStr"/>
@@ -12936,13 +13080,25 @@
           <t>Both the original attempt and the retry timed out after ~30s each with the same message. A normal on-topic question sent right after answered correctly within ~10s, so the failure seems specific to off-topic prompts.</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr"/>
-      <c r="J23" s="10" t="inlineStr"/>
-      <c r="K23" s="10" t="inlineStr"/>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>The fallback model (gpt-oss, used since no NVIDIA_MODEL is configured) defaults to a higher reasoning effort than the Nemotron 'thinking' switch already disabled; an off-topic question gave it the most to reason about, so it burned its whole time budget without replying, and a retry hit the same model again within its unhealthy cooldown.</t>
+        </is>
+      </c>
+      <c r="J23" s="10" t="inlineStr">
+        <is>
+          <t>Every NVIDIA NIM call now also sends reasoning_effort: low, which applies to gpt-oss independently of the Nemotron-specific switch.</t>
+        </is>
+      </c>
+      <c r="K23" s="10" t="inlineStr">
+        <is>
+          <t>backend/src/modules/assistant/clients/NvidiaNimClient.ts</t>
+        </is>
+      </c>
       <c r="L23" s="10" t="inlineStr"/>
       <c r="M23" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="N23" s="10" t="inlineStr"/>
@@ -12986,13 +13142,25 @@
           <t>"I couldn't find a book called 'reading circe'..." -- it matched the whole phrase as a title instead of parsing 'started reading' as the verb phrase. Retyping with the full title worked.</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr"/>
-      <c r="J24" s="10" t="inlineStr"/>
-      <c r="K24" s="10" t="inlineStr"/>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>'started reading circe' matched 'started' as the verb and left 'reading circe' as the title text, so it searched the catalogue for a nonexistent book instead of recognising the owned title.</t>
+        </is>
+      </c>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>An optional 'reading' is now consumed as filler right after started/starting/began/begun/finished/completed, before the title is read.</t>
+        </is>
+      </c>
+      <c r="K24" s="10" t="inlineStr">
+        <is>
+          <t>backend/src/modules/assistant/domains/books/conversation/quickCommands.ts</t>
+        </is>
+      </c>
       <c r="L24" s="10" t="inlineStr"/>
       <c r="M24" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="N24" s="10" t="inlineStr"/>
@@ -13036,13 +13204,25 @@
           <t>The app silently navigated to /login with all session state lost, no toast or explanation. Logging back in and repeating the exact steps worked fine every subsequent time.</t>
         </is>
       </c>
-      <c r="I25" s="10" t="inlineStr"/>
-      <c r="J25" s="10" t="inlineStr"/>
-      <c r="K25" s="10" t="inlineStr"/>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>Refresh tokens rotate strictly on first use; two requests that both held the same token (a burst of calls right as the 15-minute access token expired) raced to rotate it, and the loser was treated as reuse and signed the reader out with no warning.</t>
+        </is>
+      </c>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>A rotated-away refresh token still works for a 10-second grace window, handing back the pair the winning request already produced instead of rotating again or rejecting it; reuse outside that window (or of any older token) is still rejected and logged as before.</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t>backend/prisma/schema.prisma, backend/src/modules/auth/auth.service.ts, docs/DATA_MODEL.md, backend/tests/auth.spec.ts</t>
+        </is>
+      </c>
       <c r="L25" s="10" t="inlineStr"/>
       <c r="M25" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="N25" s="10" t="inlineStr"/>
@@ -13086,13 +13266,25 @@
           <t>The tooltip stays on top, intercepting clicks meant for elements beneath it. Escape or its own close button dismisses it, but a casual user wouldn't know to do that and would think the buttons are broken.</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr"/>
-      <c r="J26" s="10" t="inlineStr"/>
-      <c r="K26" s="10" t="inlineStr"/>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>The reader's Escape-and-click-outside handling (added in round 4) covered the Bookmarks and More menus but was never extended to the Translate panel added afterward, so it had no way to close except its own X or Escape, and sat on top of other toolbar controls intercepting their clicks.</t>
+        </is>
+      </c>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>The same click-outside backdrop that closes Bookmarks and More now also closes the Translate panel.</t>
+        </is>
+      </c>
+      <c r="K26" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/features/reader/FlowReaderPage.tsx</t>
+        </is>
+      </c>
       <c r="L26" s="10" t="inlineStr"/>
       <c r="M26" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="N26" s="10" t="inlineStr"/>
@@ -13136,13 +13328,25 @@
           <t>The Library grid shows a generic orange 'T' placeholder tile, while every other metadata field is correctly enriched.</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr"/>
-      <c r="J27" s="10" t="inlineStr"/>
-      <c r="K27" s="10" t="inlineStr"/>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>A book added without a cover gets one found by the server a few seconds later in the background; nothing told the client to refetch, so the library grid kept showing the placeholder indefinitely once its initial fetch had already run, even though the book's own page (fetched fresh on each visit) already had the real cover.</t>
+        </is>
+      </c>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>Adding a book, from the dialog or through the assistant, now also refreshes the library list a few seconds later to pick up a cover the background search finds.</t>
+        </is>
+      </c>
+      <c r="K27" s="10" t="inlineStr">
+        <is>
+          <t>frontend/src/lib/api/works.ts, frontend/src/lib/api/assistant.ts</t>
+        </is>
+      </c>
       <c r="L27" s="10" t="inlineStr"/>
       <c r="M27" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="N27" s="10" t="inlineStr"/>
@@ -13186,13 +13390,25 @@
           <t>Footer text reads "AI features aren't set up on this server yet -- your choice is saved for when they are", which is stale and could confuse a user about whether their data is actually being sent anywhere.</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr"/>
-      <c r="J28" s="10" t="inlineStr"/>
-      <c r="K28" s="10" t="inlineStr"/>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>'Assistant and book summaries' is one Settings toggle over two independent backends -- ai-service (Claude, for summaries/search/translation) and the assistant's own NVIDIA/Ollama client (for chat) -- but the availability check only ever looked at ai-service, so the notice said AI features weren't set up while the Assistant was demonstrably answering on NVIDIA.</t>
+        </is>
+      </c>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>Availability for the generative toggle now also counts the assistant's own provider being configured, and the notice names specifically which feature(s) -- search by meaning, the Assistant, chapter translation -- aren't set up, instead of a blanket claim.</t>
+        </is>
+      </c>
+      <c r="K28" s="10" t="inlineStr">
+        <is>
+          <t>backend/src/modules/ai/ai.service.ts, backend/src/modules/assistant/config/AIConfig.ts, frontend/src/features/ai/AiSettingsCard.tsx, backend/tests/ai.spec.ts</t>
+        </is>
+      </c>
       <c r="L28" s="10" t="inlineStr"/>
       <c r="M28" s="10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="N28" s="10" t="inlineStr"/>
